--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="239">
   <si>
     <t>Id</t>
   </si>
@@ -281,6 +281,15 @@
     <t>斗笠二四阶</t>
   </si>
   <si>
+    <t>124,4007</t>
+  </si>
+  <si>
+    <t>1,16800000</t>
+  </si>
+  <si>
+    <t>斗笠二五阶</t>
+  </si>
+  <si>
     <t>护盾</t>
   </si>
   <si>
@@ -422,6 +431,12 @@
     <t>护盾二四阶</t>
   </si>
   <si>
+    <t>224,4007</t>
+  </si>
+  <si>
+    <t>护盾二五阶</t>
+  </si>
+  <si>
     <t>神符</t>
   </si>
   <si>
@@ -563,6 +578,12 @@
     <t>神符二四阶</t>
   </si>
   <si>
+    <t>324,4007</t>
+  </si>
+  <si>
+    <t>神符二五阶</t>
+  </si>
+  <si>
     <t>魔石</t>
   </si>
   <si>
@@ -702,6 +723,12 @@
   </si>
   <si>
     <t>魔石二四阶</t>
+  </si>
+  <si>
+    <t>424,4007</t>
+  </si>
+  <si>
+    <t>魔石二五阶</t>
   </si>
   <si>
     <t>其他</t>
@@ -1712,7 +1739,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K102"/>
+  <dimension ref="C3:K110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2480,88 +2507,59 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" customHeight="1" spans="3:11">
-      <c r="C30" s="1">
-        <v>201</v>
-      </c>
-      <c r="D30" s="1" t="s">
+    <row r="29" customHeight="1" spans="3:11">
+      <c r="C29" s="1">
+        <v>124</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="G29" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="H29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="J30" s="1">
-        <v>202</v>
-      </c>
-      <c r="K30" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:11">
-      <c r="C31" s="1">
-        <v>202</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J31" s="1">
-        <v>203</v>
-      </c>
-      <c r="K31" s="1">
+      <c r="J29" s="1">
+        <v>125</v>
+      </c>
+      <c r="K29" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="J32" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
@@ -2569,28 +2567,28 @@
     </row>
     <row r="33" customHeight="1" spans="3:11">
       <c r="C33" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="J33" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K33" s="1">
         <v>2</v>
@@ -2598,28 +2596,28 @@
     </row>
     <row r="34" customHeight="1" spans="3:11">
       <c r="C34" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="J34" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K34" s="1">
         <v>2</v>
@@ -2627,28 +2625,28 @@
     </row>
     <row r="35" customHeight="1" spans="3:11">
       <c r="C35" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="J35" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K35" s="1">
         <v>2</v>
@@ -2656,28 +2654,28 @@
     </row>
     <row r="36" customHeight="1" spans="3:11">
       <c r="C36" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="J36" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K36" s="1">
         <v>2</v>
@@ -2685,28 +2683,28 @@
     </row>
     <row r="37" customHeight="1" spans="3:11">
       <c r="C37" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F37" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>100</v>
-      </c>
       <c r="J37" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K37" s="1">
         <v>2</v>
@@ -2714,28 +2712,28 @@
     </row>
     <row r="38" customHeight="1" spans="3:11">
       <c r="C38" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F38" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="J38" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K38" s="1">
         <v>2</v>
@@ -2743,28 +2741,28 @@
     </row>
     <row r="39" customHeight="1" spans="3:11">
       <c r="C39" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="J39" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K39" s="1">
         <v>2</v>
@@ -2772,28 +2770,28 @@
     </row>
     <row r="40" customHeight="1" spans="3:11">
       <c r="C40" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="J40" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2801,28 +2799,28 @@
     </row>
     <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="J41" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K41" s="1">
         <v>2</v>
@@ -2830,28 +2828,28 @@
     </row>
     <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="J42" s="1">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K42" s="1">
         <v>2</v>
@@ -2859,28 +2857,28 @@
     </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="J43" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K43" s="1">
         <v>2</v>
@@ -2888,28 +2886,28 @@
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="J44" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K44" s="1">
         <v>2</v>
@@ -2917,28 +2915,28 @@
     </row>
     <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="J45" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K45" s="1">
         <v>2</v>
@@ -2946,28 +2944,28 @@
     </row>
     <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G46" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="J46" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K46" s="1">
         <v>2</v>
@@ -2975,28 +2973,28 @@
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="J47" s="1">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K47" s="1">
         <v>2</v>
@@ -3004,28 +3002,28 @@
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="J48" s="1">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K48" s="1">
         <v>2</v>
@@ -3033,28 +3031,28 @@
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="J49" s="1">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K49" s="1">
         <v>2</v>
@@ -3062,28 +3060,28 @@
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="J50" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K50" s="1">
         <v>2</v>
@@ -3091,28 +3089,28 @@
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="J51" s="1">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K51" s="1">
         <v>2</v>
@@ -3120,39 +3118,68 @@
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
+        <v>221</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J52" s="1">
+        <v>222</v>
+      </c>
+      <c r="K52" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:11">
+      <c r="C53" s="1">
+        <v>222</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J53" s="1">
         <v>223</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J52" s="1">
-        <v>224</v>
-      </c>
-      <c r="K52" s="1">
+      <c r="K53" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>13</v>
@@ -3161,7 +3188,7 @@
         <v>132</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>16</v>
@@ -3170,7 +3197,7 @@
         <v>133</v>
       </c>
       <c r="J54" s="1">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="K54" s="1">
         <v>2</v>
@@ -3178,10 +3205,10 @@
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>302</v>
+        <v>224</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>13</v>
@@ -3190,7 +3217,7 @@
         <v>134</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>16</v>
@@ -3199,94 +3226,36 @@
         <v>135</v>
       </c>
       <c r="J55" s="1">
-        <v>303</v>
+        <v>225</v>
       </c>
       <c r="K55" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:11">
-      <c r="C56" s="1">
-        <v>303</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="J56" s="1">
-        <v>304</v>
-      </c>
-      <c r="K56" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:11">
-      <c r="C57" s="1">
-        <v>304</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J57" s="1">
-        <v>305</v>
-      </c>
-      <c r="K57" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="J58" s="1">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K58" s="1">
         <v>2</v>
@@ -3294,28 +3263,28 @@
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="J59" s="1">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="K59" s="1">
         <v>2</v>
@@ -3323,28 +3292,28 @@
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="J60" s="1">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K60" s="1">
         <v>2</v>
@@ -3352,28 +3321,28 @@
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="J61" s="1">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K61" s="1">
         <v>2</v>
@@ -3381,28 +3350,28 @@
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J62" s="1">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K62" s="1">
         <v>2</v>
@@ -3410,28 +3379,28 @@
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J63" s="1">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K63" s="1">
         <v>2</v>
@@ -3439,28 +3408,28 @@
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="J64" s="1">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K64" s="1">
         <v>2</v>
@@ -3468,28 +3437,28 @@
     </row>
     <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="J65" s="1">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K65" s="1">
         <v>2</v>
@@ -3497,28 +3466,28 @@
     </row>
     <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="J66" s="1">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K66" s="1">
         <v>2</v>
@@ -3526,28 +3495,28 @@
     </row>
     <row r="67" customHeight="1" spans="3:11">
       <c r="C67" s="1">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J67" s="1">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K67" s="1">
         <v>2</v>
@@ -3555,28 +3524,28 @@
     </row>
     <row r="68" customHeight="1" spans="3:11">
       <c r="C68" s="1">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J68" s="1">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K68" s="1">
         <v>2</v>
@@ -3584,28 +3553,28 @@
     </row>
     <row r="69" customHeight="1" spans="3:11">
       <c r="C69" s="1">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J69" s="1">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K69" s="1">
         <v>2</v>
@@ -3613,28 +3582,28 @@
     </row>
     <row r="70" customHeight="1" spans="3:11">
       <c r="C70" s="1">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H70" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J70" s="1">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K70" s="1">
         <v>2</v>
@@ -3642,28 +3611,28 @@
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="J71" s="1">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K71" s="1">
         <v>2</v>
@@ -3671,28 +3640,28 @@
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J72" s="1">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K72" s="1">
         <v>2</v>
@@ -3700,28 +3669,28 @@
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J73" s="1">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K73" s="1">
         <v>2</v>
@@ -3729,28 +3698,28 @@
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J74" s="1">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K74" s="1">
         <v>2</v>
@@ -3758,28 +3727,28 @@
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J75" s="1">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K75" s="1">
         <v>2</v>
@@ -3787,57 +3756,86 @@
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J76" s="1">
+        <v>320</v>
+      </c>
+      <c r="K76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:11">
+      <c r="C77" s="1">
+        <v>320</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J76" s="1">
-        <v>324</v>
-      </c>
-      <c r="K76" s="1">
+      <c r="J77" s="1">
+        <v>321</v>
+      </c>
+      <c r="K77" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>401</v>
+        <v>321</v>
       </c>
       <c r="D78" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I78" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="J78" s="1">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="K78" s="1">
         <v>2</v>
@@ -3845,28 +3843,28 @@
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J79" s="1">
-        <v>403</v>
+        <v>323</v>
       </c>
       <c r="K79" s="1">
         <v>2</v>
@@ -3874,28 +3872,28 @@
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>403</v>
+        <v>323</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="J80" s="1">
-        <v>404</v>
+        <v>324</v>
       </c>
       <c r="K80" s="1">
         <v>2</v>
@@ -3903,115 +3901,57 @@
     </row>
     <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
-        <v>404</v>
+        <v>324</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="J81" s="1">
-        <v>405</v>
+        <v>325</v>
       </c>
       <c r="K81" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:11">
-      <c r="C82" s="1">
-        <v>405</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E82" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="J82" s="1">
-        <v>406</v>
-      </c>
-      <c r="K82" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:11">
-      <c r="C83" s="1">
-        <v>406</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E83" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J83" s="1">
-        <v>407</v>
-      </c>
-      <c r="K83" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J84" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="K84" s="1">
         <v>2</v>
@@ -4019,28 +3959,28 @@
     </row>
     <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="J85" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="K85" s="1">
         <v>2</v>
@@ -4048,28 +3988,28 @@
     </row>
     <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J86" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="K86" s="1">
         <v>2</v>
@@ -4077,28 +4017,28 @@
     </row>
     <row r="87" customHeight="1" spans="3:11">
       <c r="C87" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="J87" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K87" s="1">
         <v>2</v>
@@ -4106,28 +4046,28 @@
     </row>
     <row r="88" customHeight="1" spans="3:11">
       <c r="C88" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="J88" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="K88" s="1">
         <v>2</v>
@@ -4135,28 +4075,28 @@
     </row>
     <row r="89" customHeight="1" spans="3:11">
       <c r="C89" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J89" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="K89" s="1">
         <v>2</v>
@@ -4164,28 +4104,28 @@
     </row>
     <row r="90" customHeight="1" spans="3:11">
       <c r="C90" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="J90" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="K90" s="1">
         <v>2</v>
@@ -4193,28 +4133,28 @@
     </row>
     <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J91" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="K91" s="1">
         <v>2</v>
@@ -4222,28 +4162,28 @@
     </row>
     <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="J92" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="K92" s="1">
         <v>2</v>
@@ -4251,28 +4191,28 @@
     </row>
     <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J93" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="K93" s="1">
         <v>2</v>
@@ -4280,28 +4220,28 @@
     </row>
     <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J94" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="K94" s="1">
         <v>2</v>
@@ -4309,28 +4249,28 @@
     </row>
     <row r="95" customHeight="1" spans="3:11">
       <c r="C95" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="J95" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="K95" s="1">
         <v>2</v>
@@ -4338,28 +4278,28 @@
     </row>
     <row r="96" customHeight="1" spans="3:11">
       <c r="C96" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J96" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="K96" s="1">
         <v>2</v>
@@ -4367,28 +4307,28 @@
     </row>
     <row r="97" customHeight="1" spans="3:11">
       <c r="C97" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J97" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="K97" s="1">
         <v>2</v>
@@ -4396,28 +4336,28 @@
     </row>
     <row r="98" customHeight="1" spans="3:11">
       <c r="C98" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="J98" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K98" s="1">
         <v>2</v>
@@ -4425,28 +4365,28 @@
     </row>
     <row r="99" customHeight="1" spans="3:11">
       <c r="C99" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="J99" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K99" s="1">
         <v>2</v>
@@ -4454,59 +4394,262 @@
     </row>
     <row r="100" customHeight="1" spans="3:11">
       <c r="C100" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J100" s="1">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="K100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:11">
+      <c r="C101" s="1">
+        <v>418</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J101" s="1">
+        <v>419</v>
+      </c>
+      <c r="K101" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
+        <v>419</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="G102" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J102" s="1">
+        <v>420</v>
+      </c>
+      <c r="K102" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:11">
+      <c r="C103" s="1">
+        <v>420</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="G103" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="J103" s="1">
+        <v>421</v>
+      </c>
+      <c r="K103" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:11">
+      <c r="C104" s="1">
+        <v>421</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G104" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H104" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="J104" s="1">
+        <v>422</v>
+      </c>
+      <c r="K104" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:11">
+      <c r="C105" s="1">
+        <v>422</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J105" s="1">
+        <v>423</v>
+      </c>
+      <c r="K105" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:11">
+      <c r="C106" s="1">
+        <v>423</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J106" s="1">
+        <v>424</v>
+      </c>
+      <c r="K106" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:11">
+      <c r="C107" s="1">
+        <v>424</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G107" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J107" s="1">
+        <v>425</v>
+      </c>
+      <c r="K107" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:11">
+      <c r="C110" s="1">
         <v>501</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E102" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="F102" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="G102" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I102" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J102" s="1">
+      <c r="D110" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="J110" s="1">
         <v>4011</v>
       </c>
-      <c r="K102" s="1">
+      <c r="K110" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="294">
   <si>
     <t>Id</t>
   </si>
@@ -290,6 +290,63 @@
     <t>斗笠二五阶</t>
   </si>
   <si>
+    <t>125,4007</t>
+  </si>
+  <si>
+    <t>1,33600000</t>
+  </si>
+  <si>
+    <t>斗笠二六阶</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>126,4007</t>
+  </si>
+  <si>
+    <t>1,67200000</t>
+  </si>
+  <si>
+    <t>斗笠二七阶</t>
+  </si>
+  <si>
+    <t>127,4007</t>
+  </si>
+  <si>
+    <t>1,134400000</t>
+  </si>
+  <si>
+    <t>斗笠二八阶</t>
+  </si>
+  <si>
+    <t>128,4007</t>
+  </si>
+  <si>
+    <t>1,268800000</t>
+  </si>
+  <si>
+    <t>斗笠二九阶</t>
+  </si>
+  <si>
+    <t>129,4007</t>
+  </si>
+  <si>
+    <t>1,537600000</t>
+  </si>
+  <si>
+    <t>斗笠三十阶</t>
+  </si>
+  <si>
+    <t>130,4007</t>
+  </si>
+  <si>
+    <t>1,1075200000</t>
+  </si>
+  <si>
+    <t>斗笠三一阶</t>
+  </si>
+  <si>
     <t>护盾</t>
   </si>
   <si>
@@ -437,6 +494,42 @@
     <t>护盾二五阶</t>
   </si>
   <si>
+    <t>225,4007</t>
+  </si>
+  <si>
+    <t>护盾二六阶</t>
+  </si>
+  <si>
+    <t>226,4007</t>
+  </si>
+  <si>
+    <t>护盾二七阶</t>
+  </si>
+  <si>
+    <t>227,4007</t>
+  </si>
+  <si>
+    <t>护盾二八阶</t>
+  </si>
+  <si>
+    <t>228,4007</t>
+  </si>
+  <si>
+    <t>护盾二九阶</t>
+  </si>
+  <si>
+    <t>229,4007</t>
+  </si>
+  <si>
+    <t>护盾三十阶</t>
+  </si>
+  <si>
+    <t>230,4007</t>
+  </si>
+  <si>
+    <t>护盾三一阶</t>
+  </si>
+  <si>
     <t>神符</t>
   </si>
   <si>
@@ -584,6 +677,42 @@
     <t>神符二五阶</t>
   </si>
   <si>
+    <t>325,4007</t>
+  </si>
+  <si>
+    <t>神符二六阶</t>
+  </si>
+  <si>
+    <t>326,4007</t>
+  </si>
+  <si>
+    <t>神符二七阶</t>
+  </si>
+  <si>
+    <t>327,4007</t>
+  </si>
+  <si>
+    <t>神符二八阶</t>
+  </si>
+  <si>
+    <t>328,4007</t>
+  </si>
+  <si>
+    <t>神符二九阶</t>
+  </si>
+  <si>
+    <t>329,4007</t>
+  </si>
+  <si>
+    <t>神符三十阶</t>
+  </si>
+  <si>
+    <t>330,4007</t>
+  </si>
+  <si>
+    <t>神符三一阶</t>
+  </si>
+  <si>
     <t>魔石</t>
   </si>
   <si>
@@ -729,6 +858,42 @@
   </si>
   <si>
     <t>魔石二五阶</t>
+  </si>
+  <si>
+    <t>425,4007</t>
+  </si>
+  <si>
+    <t>魔石二六阶</t>
+  </si>
+  <si>
+    <t>426,4007</t>
+  </si>
+  <si>
+    <t>魔石二七阶</t>
+  </si>
+  <si>
+    <t>427,4007</t>
+  </si>
+  <si>
+    <t>魔石二八阶</t>
+  </si>
+  <si>
+    <t>428,4007</t>
+  </si>
+  <si>
+    <t>魔石二九阶</t>
+  </si>
+  <si>
+    <t>429,4007</t>
+  </si>
+  <si>
+    <t>魔石三十阶</t>
+  </si>
+  <si>
+    <t>430,4007</t>
+  </si>
+  <si>
+    <t>魔石三一阶</t>
   </si>
   <si>
     <t>其他</t>
@@ -1739,7 +1904,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:K110"/>
+  <dimension ref="A3:K138"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2536,262 +2701,234 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="3:11">
+    <row r="30" customHeight="1" spans="3:11">
+      <c r="C30" s="1">
+        <v>125</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="1">
+        <v>126</v>
+      </c>
+      <c r="K30" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:11">
+      <c r="A31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="1">
+        <v>126</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J31" s="1">
+        <v>127</v>
+      </c>
+      <c r="K31" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="1:11">
+      <c r="A32" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C32" s="1">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J32" s="1">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="K32" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="33" customHeight="1" spans="3:11">
+    <row r="33" customHeight="1" spans="1:11">
+      <c r="A33" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C33" s="1">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J33" s="1">
+        <v>129</v>
+      </c>
+      <c r="K33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:11">
+      <c r="A34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J33" s="1">
-        <v>203</v>
-      </c>
-      <c r="K33" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:11">
+      <c r="B34" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C34" s="1">
-        <v>203</v>
+        <v>129</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>22</v>
+        <v>101</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J34" s="1">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K34" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="3:11">
+    <row r="35" customHeight="1" spans="1:11">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C35" s="1">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="J35" s="1">
-        <v>205</v>
+        <v>131</v>
       </c>
       <c r="K35" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:11">
-      <c r="C36" s="1">
-        <v>205</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J36" s="1">
-        <v>206</v>
-      </c>
-      <c r="K36" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:11">
-      <c r="C37" s="1">
-        <v>206</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J37" s="1">
-        <v>207</v>
-      </c>
-      <c r="K37" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:11">
-      <c r="C38" s="1">
-        <v>207</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J38" s="1">
-        <v>208</v>
-      </c>
-      <c r="K38" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:11">
-      <c r="C39" s="1">
-        <v>208</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J39" s="1">
-        <v>209</v>
-      </c>
-      <c r="K39" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="40" customHeight="1" spans="3:11">
       <c r="C40" s="1">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H40" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="J40" s="1">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="K40" s="1">
         <v>2</v>
@@ -2799,28 +2936,28 @@
     </row>
     <row r="41" customHeight="1" spans="3:11">
       <c r="C41" s="1">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="J41" s="1">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="K41" s="1">
         <v>2</v>
@@ -2828,28 +2965,28 @@
     </row>
     <row r="42" customHeight="1" spans="3:11">
       <c r="C42" s="1">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="J42" s="1">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="K42" s="1">
         <v>2</v>
@@ -2857,28 +2994,28 @@
     </row>
     <row r="43" customHeight="1" spans="3:11">
       <c r="C43" s="1">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J43" s="1">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="K43" s="1">
         <v>2</v>
@@ -2886,28 +3023,28 @@
     </row>
     <row r="44" customHeight="1" spans="3:11">
       <c r="C44" s="1">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J44" s="1">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="K44" s="1">
         <v>2</v>
@@ -2915,28 +3052,28 @@
     </row>
     <row r="45" customHeight="1" spans="3:11">
       <c r="C45" s="1">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J45" s="1">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K45" s="1">
         <v>2</v>
@@ -2944,28 +3081,28 @@
     </row>
     <row r="46" customHeight="1" spans="3:11">
       <c r="C46" s="1">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J46" s="1">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="K46" s="1">
         <v>2</v>
@@ -2973,28 +3110,28 @@
     </row>
     <row r="47" customHeight="1" spans="3:11">
       <c r="C47" s="1">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J47" s="1">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="K47" s="1">
         <v>2</v>
@@ -3002,28 +3139,28 @@
     </row>
     <row r="48" customHeight="1" spans="3:11">
       <c r="C48" s="1">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J48" s="1">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="K48" s="1">
         <v>2</v>
@@ -3031,28 +3168,28 @@
     </row>
     <row r="49" customHeight="1" spans="3:11">
       <c r="C49" s="1">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="J49" s="1">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="K49" s="1">
         <v>2</v>
@@ -3060,28 +3197,28 @@
     </row>
     <row r="50" customHeight="1" spans="3:11">
       <c r="C50" s="1">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="J50" s="1">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="K50" s="1">
         <v>2</v>
@@ -3089,28 +3226,28 @@
     </row>
     <row r="51" customHeight="1" spans="3:11">
       <c r="C51" s="1">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J51" s="1">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="K51" s="1">
         <v>2</v>
@@ -3118,28 +3255,28 @@
     </row>
     <row r="52" customHeight="1" spans="3:11">
       <c r="C52" s="1">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J52" s="1">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="K52" s="1">
         <v>2</v>
@@ -3147,28 +3284,28 @@
     </row>
     <row r="53" customHeight="1" spans="3:11">
       <c r="C53" s="1">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>79</v>
+        <v>55</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J53" s="1">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="K53" s="1">
         <v>2</v>
@@ -3176,28 +3313,28 @@
     </row>
     <row r="54" customHeight="1" spans="3:11">
       <c r="C54" s="1">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>82</v>
+        <v>58</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="J54" s="1">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="K54" s="1">
         <v>2</v>
@@ -3205,57 +3342,115 @@
     </row>
     <row r="55" customHeight="1" spans="3:11">
       <c r="C55" s="1">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="J55" s="1">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="K55" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:11">
+      <c r="C56" s="1">
+        <v>217</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J56" s="1">
+        <v>218</v>
+      </c>
+      <c r="K56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:11">
+      <c r="C57" s="1">
+        <v>218</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J57" s="1">
+        <v>219</v>
+      </c>
+      <c r="K57" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="58" customHeight="1" spans="3:11">
       <c r="C58" s="1">
-        <v>301</v>
+        <v>219</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="J58" s="1">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="K58" s="1">
         <v>2</v>
@@ -3263,28 +3458,28 @@
     </row>
     <row r="59" customHeight="1" spans="3:11">
       <c r="C59" s="1">
-        <v>302</v>
+        <v>220</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J59" s="1">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="K59" s="1">
         <v>2</v>
@@ -3292,28 +3487,28 @@
     </row>
     <row r="60" customHeight="1" spans="3:11">
       <c r="C60" s="1">
-        <v>303</v>
+        <v>221</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J60" s="1">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="K60" s="1">
         <v>2</v>
@@ -3321,28 +3516,28 @@
     </row>
     <row r="61" customHeight="1" spans="3:11">
       <c r="C61" s="1">
-        <v>304</v>
+        <v>222</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="H61" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="J61" s="1">
-        <v>305</v>
+        <v>223</v>
       </c>
       <c r="K61" s="1">
         <v>2</v>
@@ -3350,28 +3545,28 @@
     </row>
     <row r="62" customHeight="1" spans="3:11">
       <c r="C62" s="1">
-        <v>305</v>
+        <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="H62" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="J62" s="1">
-        <v>306</v>
+        <v>224</v>
       </c>
       <c r="K62" s="1">
         <v>2</v>
@@ -3379,28 +3574,28 @@
     </row>
     <row r="63" customHeight="1" spans="3:11">
       <c r="C63" s="1">
-        <v>306</v>
+        <v>224</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="H63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J63" s="1">
-        <v>307</v>
+        <v>225</v>
       </c>
       <c r="K63" s="1">
         <v>2</v>
@@ -3408,231 +3603,232 @@
     </row>
     <row r="64" customHeight="1" spans="3:11">
       <c r="C64" s="1">
-        <v>307</v>
+        <v>225</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>34</v>
+        <v>88</v>
       </c>
       <c r="H64" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J64" s="1">
-        <v>308</v>
+        <v>226</v>
       </c>
       <c r="K64" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="3:11">
+    <row r="65" customHeight="1" spans="1:11">
+      <c r="A65" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C65" s="1">
-        <v>308</v>
+        <v>226</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="J65" s="1">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="K65" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="3:11">
+    <row r="66" customHeight="1" spans="1:11">
+      <c r="A66" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C66" s="1">
-        <v>309</v>
+        <v>227</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="J66" s="1">
-        <v>310</v>
+        <v>228</v>
       </c>
       <c r="K66" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="67" customHeight="1" spans="3:11">
+    <row r="67" customHeight="1" spans="1:11">
+      <c r="A67" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C67" s="1">
-        <v>310</v>
+        <v>228</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="H67" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J67" s="1">
-        <v>311</v>
+        <v>229</v>
       </c>
       <c r="K67" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="68" customHeight="1" spans="3:11">
+    <row r="68" customHeight="1" spans="1:11">
+      <c r="A68" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C68" s="1">
-        <v>311</v>
+        <v>229</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="H68" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J68" s="1">
-        <v>312</v>
+        <v>230</v>
       </c>
       <c r="K68" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="3:11">
+    <row r="69" customHeight="1" spans="1:11">
+      <c r="A69" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C69" s="1">
-        <v>312</v>
+        <v>230</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="J69" s="1">
-        <v>313</v>
+        <v>231</v>
       </c>
       <c r="K69" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:11">
-      <c r="C70" s="1">
-        <v>313</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="J70" s="1">
-        <v>314</v>
-      </c>
-      <c r="K70" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="71" customHeight="1" spans="3:11">
       <c r="C71" s="1">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J71" s="1">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="K71" s="1">
         <v>2</v>
@@ -3640,28 +3836,28 @@
     </row>
     <row r="72" customHeight="1" spans="3:11">
       <c r="C72" s="1">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J72" s="1">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="K72" s="1">
         <v>2</v>
@@ -3669,28 +3865,28 @@
     </row>
     <row r="73" customHeight="1" spans="3:11">
       <c r="C73" s="1">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="H73" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J73" s="1">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="K73" s="1">
         <v>2</v>
@@ -3698,28 +3894,28 @@
     </row>
     <row r="74" customHeight="1" spans="3:11">
       <c r="C74" s="1">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J74" s="1">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="K74" s="1">
         <v>2</v>
@@ -3727,28 +3923,28 @@
     </row>
     <row r="75" customHeight="1" spans="3:11">
       <c r="C75" s="1">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J75" s="1">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="K75" s="1">
         <v>2</v>
@@ -3756,28 +3952,28 @@
     </row>
     <row r="76" customHeight="1" spans="3:11">
       <c r="C76" s="1">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J76" s="1">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="K76" s="1">
         <v>2</v>
@@ -3785,28 +3981,28 @@
     </row>
     <row r="77" customHeight="1" spans="3:11">
       <c r="C77" s="1">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J77" s="1">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="K77" s="1">
         <v>2</v>
@@ -3814,28 +4010,28 @@
     </row>
     <row r="78" customHeight="1" spans="3:11">
       <c r="C78" s="1">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J78" s="1">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="K78" s="1">
         <v>2</v>
@@ -3843,28 +4039,28 @@
     </row>
     <row r="79" customHeight="1" spans="3:11">
       <c r="C79" s="1">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>79</v>
+        <v>40</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J79" s="1">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="K79" s="1">
         <v>2</v>
@@ -3872,28 +4068,28 @@
     </row>
     <row r="80" customHeight="1" spans="3:11">
       <c r="C80" s="1">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J80" s="1">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="K80" s="1">
         <v>2</v>
@@ -3901,57 +4097,115 @@
     </row>
     <row r="81" customHeight="1" spans="3:11">
       <c r="C81" s="1">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J81" s="1">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="K81" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:11">
+      <c r="C82" s="1">
+        <v>312</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J82" s="1">
+        <v>313</v>
+      </c>
+      <c r="K82" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:11">
+      <c r="C83" s="1">
+        <v>313</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J83" s="1">
+        <v>314</v>
+      </c>
+      <c r="K83" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
-        <v>401</v>
+        <v>314</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="J84" s="1">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="K84" s="1">
         <v>2</v>
@@ -3959,28 +4213,28 @@
     </row>
     <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
-        <v>402</v>
+        <v>315</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="J85" s="1">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="K85" s="1">
         <v>2</v>
@@ -3988,28 +4242,28 @@
     </row>
     <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="J86" s="1">
-        <v>404</v>
+        <v>317</v>
       </c>
       <c r="K86" s="1">
         <v>2</v>
@@ -4017,28 +4271,28 @@
     </row>
     <row r="87" customHeight="1" spans="3:11">
       <c r="C87" s="1">
-        <v>404</v>
+        <v>317</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="J87" s="1">
-        <v>405</v>
+        <v>318</v>
       </c>
       <c r="K87" s="1">
         <v>2</v>
@@ -4046,28 +4300,28 @@
     </row>
     <row r="88" customHeight="1" spans="3:11">
       <c r="C88" s="1">
-        <v>405</v>
+        <v>318</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="J88" s="1">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="K88" s="1">
         <v>2</v>
@@ -4075,28 +4329,28 @@
     </row>
     <row r="89" customHeight="1" spans="3:11">
       <c r="C89" s="1">
-        <v>406</v>
+        <v>319</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="J89" s="1">
-        <v>407</v>
+        <v>320</v>
       </c>
       <c r="K89" s="1">
         <v>2</v>
@@ -4104,28 +4358,28 @@
     </row>
     <row r="90" customHeight="1" spans="3:11">
       <c r="C90" s="1">
-        <v>407</v>
+        <v>320</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="J90" s="1">
-        <v>408</v>
+        <v>321</v>
       </c>
       <c r="K90" s="1">
         <v>2</v>
@@ -4133,28 +4387,28 @@
     </row>
     <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
-        <v>408</v>
+        <v>321</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J91" s="1">
-        <v>409</v>
+        <v>322</v>
       </c>
       <c r="K91" s="1">
         <v>2</v>
@@ -4162,28 +4416,28 @@
     </row>
     <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
-        <v>409</v>
+        <v>322</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="J92" s="1">
-        <v>410</v>
+        <v>323</v>
       </c>
       <c r="K92" s="1">
         <v>2</v>
@@ -4191,28 +4445,28 @@
     </row>
     <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
-        <v>410</v>
+        <v>323</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="J93" s="1">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="K93" s="1">
         <v>2</v>
@@ -4220,28 +4474,28 @@
     </row>
     <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
-        <v>411</v>
+        <v>324</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J94" s="1">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="K94" s="1">
         <v>2</v>
@@ -4249,231 +4503,232 @@
     </row>
     <row r="95" customHeight="1" spans="3:11">
       <c r="C95" s="1">
-        <v>412</v>
+        <v>325</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="J95" s="1">
-        <v>413</v>
+        <v>326</v>
       </c>
       <c r="K95" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="3:11">
+    <row r="96" customHeight="1" spans="1:11">
+      <c r="A96" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C96" s="1">
-        <v>413</v>
+        <v>326</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="J96" s="1">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="K96" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="3:11">
+    <row r="97" customHeight="1" spans="1:11">
+      <c r="A97" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C97" s="1">
-        <v>414</v>
+        <v>327</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="J97" s="1">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="K97" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="98" customHeight="1" spans="3:11">
+    <row r="98" customHeight="1" spans="1:11">
+      <c r="A98" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C98" s="1">
-        <v>415</v>
+        <v>328</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>58</v>
+        <v>98</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="J98" s="1">
-        <v>416</v>
+        <v>329</v>
       </c>
       <c r="K98" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="99" customHeight="1" spans="3:11">
+    <row r="99" customHeight="1" spans="1:11">
+      <c r="A99" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C99" s="1">
-        <v>416</v>
+        <v>329</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>61</v>
+        <v>101</v>
       </c>
       <c r="H99" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="J99" s="1">
-        <v>417</v>
+        <v>330</v>
       </c>
       <c r="K99" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="100" customHeight="1" spans="3:11">
+    <row r="100" customHeight="1" spans="1:11">
+      <c r="A100" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>90</v>
+      </c>
       <c r="C100" s="1">
-        <v>417</v>
+        <v>330</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="E100" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="H100" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="J100" s="1">
-        <v>418</v>
+        <v>331</v>
       </c>
       <c r="K100" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:11">
-      <c r="C101" s="1">
-        <v>418</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="G101" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I101" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="J101" s="1">
-        <v>419</v>
-      </c>
-      <c r="K101" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:11">
       <c r="C102" s="1">
-        <v>419</v>
+        <v>401</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="J102" s="1">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="K102" s="1">
         <v>2</v>
@@ -4481,28 +4736,28 @@
     </row>
     <row r="103" customHeight="1" spans="3:11">
       <c r="C103" s="1">
-        <v>420</v>
+        <v>402</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="J103" s="1">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="K103" s="1">
         <v>2</v>
@@ -4510,28 +4765,28 @@
     </row>
     <row r="104" customHeight="1" spans="3:11">
       <c r="C104" s="1">
-        <v>421</v>
+        <v>403</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="J104" s="1">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="K104" s="1">
         <v>2</v>
@@ -4539,28 +4794,28 @@
     </row>
     <row r="105" customHeight="1" spans="3:11">
       <c r="C105" s="1">
-        <v>422</v>
+        <v>404</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="J105" s="1">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="K105" s="1">
         <v>2</v>
@@ -4568,28 +4823,28 @@
     </row>
     <row r="106" customHeight="1" spans="3:11">
       <c r="C106" s="1">
-        <v>423</v>
+        <v>405</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="H106" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="J106" s="1">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="K106" s="1">
         <v>2</v>
@@ -4597,59 +4852,785 @@
     </row>
     <row r="107" customHeight="1" spans="3:11">
       <c r="C107" s="1">
-        <v>424</v>
+        <v>406</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="H107" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="J107" s="1">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="K107" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:11">
+      <c r="C108" s="1">
+        <v>407</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E108" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="G108" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J108" s="1">
+        <v>408</v>
+      </c>
+      <c r="K108" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:11">
+      <c r="C109" s="1">
+        <v>408</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E109" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F109" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G109" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="J109" s="1">
+        <v>409</v>
+      </c>
+      <c r="K109" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:11">
       <c r="C110" s="1">
+        <v>409</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E110" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="G110" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H110" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="J110" s="1">
+        <v>410</v>
+      </c>
+      <c r="K110" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:11">
+      <c r="C111" s="1">
+        <v>410</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E111" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F111" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="J111" s="1">
+        <v>411</v>
+      </c>
+      <c r="K111" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:11">
+      <c r="C112" s="1">
+        <v>411</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G112" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J112" s="1">
+        <v>412</v>
+      </c>
+      <c r="K112" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:11">
+      <c r="C113" s="1">
+        <v>412</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F113" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J113" s="1">
+        <v>413</v>
+      </c>
+      <c r="K113" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:11">
+      <c r="C114" s="1">
+        <v>413</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E114" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F114" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="G114" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="J114" s="1">
+        <v>414</v>
+      </c>
+      <c r="K114" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:11">
+      <c r="C115" s="1">
+        <v>414</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E115" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="J115" s="1">
+        <v>415</v>
+      </c>
+      <c r="K115" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:11">
+      <c r="C116" s="1">
+        <v>415</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="G116" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H116" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="J116" s="1">
+        <v>416</v>
+      </c>
+      <c r="K116" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:11">
+      <c r="C117" s="1">
+        <v>416</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E117" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G117" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J117" s="1">
+        <v>417</v>
+      </c>
+      <c r="K117" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:11">
+      <c r="C118" s="1">
+        <v>417</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G118" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J118" s="1">
+        <v>418</v>
+      </c>
+      <c r="K118" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:11">
+      <c r="C119" s="1">
+        <v>418</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E119" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G119" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J119" s="1">
+        <v>419</v>
+      </c>
+      <c r="K119" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:11">
+      <c r="C120" s="1">
+        <v>419</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E120" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F120" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="G120" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H120" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="J120" s="1">
+        <v>420</v>
+      </c>
+      <c r="K120" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:11">
+      <c r="C121" s="1">
+        <v>420</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E121" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="G121" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="J121" s="1">
+        <v>421</v>
+      </c>
+      <c r="K121" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:11">
+      <c r="C122" s="1">
+        <v>421</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E122" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="G122" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H122" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J122" s="1">
+        <v>422</v>
+      </c>
+      <c r="K122" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:11">
+      <c r="C123" s="1">
+        <v>422</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G123" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J123" s="1">
+        <v>423</v>
+      </c>
+      <c r="K123" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:11">
+      <c r="C124" s="1">
+        <v>423</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E124" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G124" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H124" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="J124" s="1">
+        <v>424</v>
+      </c>
+      <c r="K124" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:11">
+      <c r="C125" s="1">
+        <v>424</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E125" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F125" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="G125" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="J125" s="1">
+        <v>425</v>
+      </c>
+      <c r="K125" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:11">
+      <c r="C126" s="1">
+        <v>425</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G126" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H126" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J126" s="1">
+        <v>426</v>
+      </c>
+      <c r="K126" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="1:11">
+      <c r="A127" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C127" s="1">
+        <v>426</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E127" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="G127" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="J127" s="1">
+        <v>427</v>
+      </c>
+      <c r="K127" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="1:11">
+      <c r="A128" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C128" s="1">
+        <v>427</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G128" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H128" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J128" s="1">
+        <v>428</v>
+      </c>
+      <c r="K128" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="1:11">
+      <c r="A129" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C129" s="1">
+        <v>428</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E129" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="G129" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J129" s="1">
+        <v>429</v>
+      </c>
+      <c r="K129" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="1:11">
+      <c r="A130" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C130" s="1">
+        <v>429</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="J130" s="1">
+        <v>430</v>
+      </c>
+      <c r="K130" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:11">
+      <c r="A131" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C131" s="1">
+        <v>430</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J131" s="1">
+        <v>431</v>
+      </c>
+      <c r="K131" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:11">
+      <c r="C138" s="1">
         <v>501</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="E110" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="G110" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="J110" s="1">
+      <c r="D138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E138" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="F138" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="G138" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="H138" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J138" s="1">
         <v>4011</v>
       </c>
-      <c r="K110" s="1">
+      <c r="K138" s="1">
         <v>5</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="295">
   <si>
     <t>Id</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>long[]</t>
   </si>
   <si>
     <t>斗笠</t>
@@ -1990,7 +1993,7 @@
         <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>11</v>
@@ -2010,22 +2013,22 @@
         <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="1">
         <v>102</v>
@@ -2039,22 +2042,22 @@
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J7" s="1">
         <v>103</v>
@@ -2068,22 +2071,22 @@
         <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J8" s="1">
         <v>104</v>
@@ -2097,22 +2100,22 @@
         <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J9" s="1">
         <v>105</v>
@@ -2126,22 +2129,22 @@
         <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J10" s="1">
         <v>106</v>
@@ -2155,22 +2158,22 @@
         <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J11" s="1">
         <v>107</v>
@@ -2184,22 +2187,22 @@
         <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J12" s="1">
         <v>108</v>
@@ -2213,22 +2216,22 @@
         <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J13" s="1">
         <v>109</v>
@@ -2242,22 +2245,22 @@
         <v>109</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J14" s="1">
         <v>110</v>
@@ -2271,22 +2274,22 @@
         <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J15" s="1">
         <v>111</v>
@@ -2300,22 +2303,22 @@
         <v>111</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J16" s="1">
         <v>112</v>
@@ -2329,22 +2332,22 @@
         <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J17" s="1">
         <v>113</v>
@@ -2358,22 +2361,22 @@
         <v>113</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J18" s="1">
         <v>114</v>
@@ -2387,22 +2390,22 @@
         <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J19" s="1">
         <v>115</v>
@@ -2416,22 +2419,22 @@
         <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J20" s="1">
         <v>116</v>
@@ -2445,22 +2448,22 @@
         <v>116</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J21" s="1">
         <v>117</v>
@@ -2474,22 +2477,22 @@
         <v>117</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J22" s="1">
         <v>118</v>
@@ -2503,22 +2506,22 @@
         <v>118</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J23" s="1">
         <v>119</v>
@@ -2532,22 +2535,22 @@
         <v>119</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J24" s="1">
         <v>120</v>
@@ -2561,22 +2564,22 @@
         <v>120</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J25" s="1">
         <v>121</v>
@@ -2590,22 +2593,22 @@
         <v>121</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J26" s="1">
         <v>122</v>
@@ -2619,22 +2622,22 @@
         <v>122</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J27" s="1">
         <v>123</v>
@@ -2648,22 +2651,22 @@
         <v>123</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J28" s="1">
         <v>124</v>
@@ -2677,22 +2680,22 @@
         <v>124</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J29" s="1">
         <v>125</v>
@@ -2706,22 +2709,22 @@
         <v>125</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J30" s="1">
         <v>126</v>
@@ -2732,31 +2735,31 @@
     </row>
     <row r="31" customHeight="1" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C31" s="1">
         <v>126</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J31" s="1">
         <v>127</v>
@@ -2767,31 +2770,31 @@
     </row>
     <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C32" s="1">
         <v>127</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J32" s="1">
         <v>128</v>
@@ -2802,31 +2805,31 @@
     </row>
     <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" s="1">
         <v>128</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J33" s="1">
         <v>129</v>
@@ -2837,31 +2840,31 @@
     </row>
     <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1">
         <v>129</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J34" s="1">
         <v>130</v>
@@ -2872,31 +2875,31 @@
     </row>
     <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C35" s="1">
         <v>130</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J35" s="1">
         <v>131</v>
@@ -2910,22 +2913,22 @@
         <v>201</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J40" s="1">
         <v>202</v>
@@ -2939,22 +2942,22 @@
         <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J41" s="1">
         <v>203</v>
@@ -2968,22 +2971,22 @@
         <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J42" s="1">
         <v>204</v>
@@ -2997,22 +3000,22 @@
         <v>204</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" s="1">
         <v>205</v>
@@ -3026,22 +3029,22 @@
         <v>205</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J44" s="1">
         <v>206</v>
@@ -3055,22 +3058,22 @@
         <v>206</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J45" s="1">
         <v>207</v>
@@ -3084,22 +3087,22 @@
         <v>207</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J46" s="1">
         <v>208</v>
@@ -3113,22 +3116,22 @@
         <v>208</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J47" s="1">
         <v>209</v>
@@ -3142,22 +3145,22 @@
         <v>209</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J48" s="1">
         <v>210</v>
@@ -3171,22 +3174,22 @@
         <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J49" s="1">
         <v>211</v>
@@ -3200,22 +3203,22 @@
         <v>211</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J50" s="1">
         <v>212</v>
@@ -3229,22 +3232,22 @@
         <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J51" s="1">
         <v>213</v>
@@ -3258,22 +3261,22 @@
         <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J52" s="1">
         <v>214</v>
@@ -3287,22 +3290,22 @@
         <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J53" s="1">
         <v>215</v>
@@ -3316,22 +3319,22 @@
         <v>215</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J54" s="1">
         <v>216</v>
@@ -3345,22 +3348,22 @@
         <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J55" s="1">
         <v>217</v>
@@ -3374,22 +3377,22 @@
         <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J56" s="1">
         <v>218</v>
@@ -3403,22 +3406,22 @@
         <v>218</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J57" s="1">
         <v>219</v>
@@ -3432,22 +3435,22 @@
         <v>219</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J58" s="1">
         <v>220</v>
@@ -3461,22 +3464,22 @@
         <v>220</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J59" s="1">
         <v>221</v>
@@ -3490,22 +3493,22 @@
         <v>221</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J60" s="1">
         <v>222</v>
@@ -3519,22 +3522,22 @@
         <v>222</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J61" s="1">
         <v>223</v>
@@ -3548,22 +3551,22 @@
         <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J62" s="1">
         <v>224</v>
@@ -3577,22 +3580,22 @@
         <v>224</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J63" s="1">
         <v>225</v>
@@ -3606,22 +3609,22 @@
         <v>225</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J64" s="1">
         <v>226</v>
@@ -3632,31 +3635,31 @@
     </row>
     <row r="65" customHeight="1" spans="1:11">
       <c r="A65" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1">
         <v>226</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J65" s="1">
         <v>227</v>
@@ -3667,31 +3670,31 @@
     </row>
     <row r="66" customHeight="1" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C66" s="1">
         <v>227</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J66" s="1">
         <v>228</v>
@@ -3702,31 +3705,31 @@
     </row>
     <row r="67" customHeight="1" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C67" s="1">
         <v>228</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J67" s="1">
         <v>229</v>
@@ -3737,31 +3740,31 @@
     </row>
     <row r="68" customHeight="1" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C68" s="1">
         <v>229</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J68" s="1">
         <v>230</v>
@@ -3772,31 +3775,31 @@
     </row>
     <row r="69" customHeight="1" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C69" s="1">
         <v>230</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J69" s="1">
         <v>231</v>
@@ -3810,22 +3813,22 @@
         <v>301</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J71" s="1">
         <v>302</v>
@@ -3839,22 +3842,22 @@
         <v>302</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J72" s="1">
         <v>303</v>
@@ -3868,22 +3871,22 @@
         <v>303</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J73" s="1">
         <v>304</v>
@@ -3897,22 +3900,22 @@
         <v>304</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J74" s="1">
         <v>305</v>
@@ -3926,22 +3929,22 @@
         <v>305</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J75" s="1">
         <v>306</v>
@@ -3955,22 +3958,22 @@
         <v>306</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J76" s="1">
         <v>307</v>
@@ -3984,22 +3987,22 @@
         <v>307</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J77" s="1">
         <v>308</v>
@@ -4013,22 +4016,22 @@
         <v>308</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J78" s="1">
         <v>309</v>
@@ -4042,22 +4045,22 @@
         <v>309</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J79" s="1">
         <v>310</v>
@@ -4071,22 +4074,22 @@
         <v>310</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J80" s="1">
         <v>311</v>
@@ -4100,22 +4103,22 @@
         <v>311</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J81" s="1">
         <v>312</v>
@@ -4129,22 +4132,22 @@
         <v>312</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J82" s="1">
         <v>313</v>
@@ -4158,22 +4161,22 @@
         <v>313</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J83" s="1">
         <v>314</v>
@@ -4187,22 +4190,22 @@
         <v>314</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J84" s="1">
         <v>315</v>
@@ -4216,22 +4219,22 @@
         <v>315</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J85" s="1">
         <v>316</v>
@@ -4245,22 +4248,22 @@
         <v>316</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J86" s="1">
         <v>317</v>
@@ -4274,22 +4277,22 @@
         <v>317</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J87" s="1">
         <v>318</v>
@@ -4303,22 +4306,22 @@
         <v>318</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J88" s="1">
         <v>319</v>
@@ -4332,22 +4335,22 @@
         <v>319</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J89" s="1">
         <v>320</v>
@@ -4361,22 +4364,22 @@
         <v>320</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J90" s="1">
         <v>321</v>
@@ -4390,22 +4393,22 @@
         <v>321</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J91" s="1">
         <v>322</v>
@@ -4419,22 +4422,22 @@
         <v>322</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J92" s="1">
         <v>323</v>
@@ -4448,22 +4451,22 @@
         <v>323</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J93" s="1">
         <v>324</v>
@@ -4477,22 +4480,22 @@
         <v>324</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J94" s="1">
         <v>325</v>
@@ -4506,22 +4509,22 @@
         <v>325</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J95" s="1">
         <v>326</v>
@@ -4532,31 +4535,31 @@
     </row>
     <row r="96" customHeight="1" spans="1:11">
       <c r="A96" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C96" s="1">
         <v>326</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J96" s="1">
         <v>327</v>
@@ -4567,31 +4570,31 @@
     </row>
     <row r="97" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C97" s="1">
         <v>327</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J97" s="1">
         <v>328</v>
@@ -4602,31 +4605,31 @@
     </row>
     <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C98" s="1">
         <v>328</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="J98" s="1">
         <v>329</v>
@@ -4637,31 +4640,31 @@
     </row>
     <row r="99" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C99" s="1">
         <v>329</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J99" s="1">
         <v>330</v>
@@ -4672,31 +4675,31 @@
     </row>
     <row r="100" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C100" s="1">
         <v>330</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="J100" s="1">
         <v>331</v>
@@ -4710,22 +4713,22 @@
         <v>401</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J102" s="1">
         <v>402</v>
@@ -4739,22 +4742,22 @@
         <v>402</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J103" s="1">
         <v>403</v>
@@ -4768,22 +4771,22 @@
         <v>403</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J104" s="1">
         <v>404</v>
@@ -4797,22 +4800,22 @@
         <v>404</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J105" s="1">
         <v>405</v>
@@ -4826,22 +4829,22 @@
         <v>405</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J106" s="1">
         <v>406</v>
@@ -4855,22 +4858,22 @@
         <v>406</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J107" s="1">
         <v>407</v>
@@ -4884,22 +4887,22 @@
         <v>407</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J108" s="1">
         <v>408</v>
@@ -4913,22 +4916,22 @@
         <v>408</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J109" s="1">
         <v>409</v>
@@ -4942,22 +4945,22 @@
         <v>409</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J110" s="1">
         <v>410</v>
@@ -4971,22 +4974,22 @@
         <v>410</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J111" s="1">
         <v>411</v>
@@ -5000,22 +5003,22 @@
         <v>411</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J112" s="1">
         <v>412</v>
@@ -5029,22 +5032,22 @@
         <v>412</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J113" s="1">
         <v>413</v>
@@ -5058,22 +5061,22 @@
         <v>413</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J114" s="1">
         <v>414</v>
@@ -5087,22 +5090,22 @@
         <v>414</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J115" s="1">
         <v>415</v>
@@ -5116,22 +5119,22 @@
         <v>415</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J116" s="1">
         <v>416</v>
@@ -5145,22 +5148,22 @@
         <v>416</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J117" s="1">
         <v>417</v>
@@ -5174,22 +5177,22 @@
         <v>417</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J118" s="1">
         <v>418</v>
@@ -5203,22 +5206,22 @@
         <v>418</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J119" s="1">
         <v>419</v>
@@ -5232,22 +5235,22 @@
         <v>419</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J120" s="1">
         <v>420</v>
@@ -5261,22 +5264,22 @@
         <v>420</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J121" s="1">
         <v>421</v>
@@ -5290,22 +5293,22 @@
         <v>421</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J122" s="1">
         <v>422</v>
@@ -5319,22 +5322,22 @@
         <v>422</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J123" s="1">
         <v>423</v>
@@ -5348,22 +5351,22 @@
         <v>423</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J124" s="1">
         <v>424</v>
@@ -5377,22 +5380,22 @@
         <v>424</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J125" s="1">
         <v>425</v>
@@ -5406,22 +5409,22 @@
         <v>425</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J126" s="1">
         <v>426</v>
@@ -5432,31 +5435,31 @@
     </row>
     <row r="127" customHeight="1" spans="1:11">
       <c r="A127" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C127" s="1">
         <v>426</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J127" s="1">
         <v>427</v>
@@ -5467,31 +5470,31 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C128" s="1">
         <v>427</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J128" s="1">
         <v>428</v>
@@ -5502,31 +5505,31 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C129" s="1">
         <v>428</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J129" s="1">
         <v>429</v>
@@ -5537,31 +5540,31 @@
     </row>
     <row r="130" customHeight="1" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C130" s="1">
         <v>429</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J130" s="1">
         <v>430</v>
@@ -5572,31 +5575,31 @@
     </row>
     <row r="131" customHeight="1" spans="1:11">
       <c r="A131" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C131" s="1">
         <v>430</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J131" s="1">
         <v>431</v>
@@ -5610,22 +5613,22 @@
         <v>501</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J138" s="1">
         <v>4011</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="295">
   <si>
     <t>Id</t>
   </si>
@@ -302,16 +302,16 @@
     <t>斗笠二六阶</t>
   </si>
   <si>
+    <t>126,4007</t>
+  </si>
+  <si>
+    <t>1,67200000</t>
+  </si>
+  <si>
+    <t>斗笠二七阶</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>126,4007</t>
-  </si>
-  <si>
-    <t>1,67200000</t>
-  </si>
-  <si>
-    <t>斗笠二七阶</t>
   </si>
   <si>
     <t>127,4007</t>
@@ -2733,13 +2733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" customHeight="1" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>91</v>
-      </c>
+    <row r="31" customHeight="1" spans="3:11">
       <c r="C31" s="1">
         <v>126</v>
       </c>
@@ -2750,16 +2744,16 @@
         <v>14</v>
       </c>
       <c r="F31" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="H31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="J31" s="1">
         <v>127</v>
@@ -2770,10 +2764,10 @@
     </row>
     <row r="32" customHeight="1" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C32" s="1">
         <v>127</v>
@@ -2805,10 +2799,10 @@
     </row>
     <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C33" s="1">
         <v>128</v>
@@ -2840,10 +2834,10 @@
     </row>
     <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C34" s="1">
         <v>129</v>
@@ -2875,10 +2869,10 @@
     </row>
     <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1">
         <v>130</v>
@@ -3633,13 +3627,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" customHeight="1" spans="1:11">
-      <c r="A65" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>91</v>
-      </c>
+    <row r="65" customHeight="1" spans="3:11">
       <c r="C65" s="1">
         <v>226</v>
       </c>
@@ -3653,7 +3641,7 @@
         <v>158</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H65" s="4" t="s">
         <v>17</v>
@@ -3670,10 +3658,10 @@
     </row>
     <row r="66" customHeight="1" spans="1:11">
       <c r="A66" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C66" s="1">
         <v>227</v>
@@ -3705,10 +3693,10 @@
     </row>
     <row r="67" customHeight="1" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C67" s="1">
         <v>228</v>
@@ -3740,10 +3728,10 @@
     </row>
     <row r="68" customHeight="1" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C68" s="1">
         <v>229</v>
@@ -3775,10 +3763,10 @@
     </row>
     <row r="69" customHeight="1" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C69" s="1">
         <v>230</v>
@@ -4533,13 +4521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="1:11">
-      <c r="A96" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>91</v>
-      </c>
+    <row r="96" customHeight="1" spans="3:11">
       <c r="C96" s="1">
         <v>326</v>
       </c>
@@ -4553,7 +4535,7 @@
         <v>219</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>17</v>
@@ -4570,10 +4552,10 @@
     </row>
     <row r="97" customHeight="1" spans="1:11">
       <c r="A97" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C97" s="1">
         <v>327</v>
@@ -4605,10 +4587,10 @@
     </row>
     <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C98" s="1">
         <v>328</v>
@@ -4640,10 +4622,10 @@
     </row>
     <row r="99" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C99" s="1">
         <v>329</v>
@@ -4675,10 +4657,10 @@
     </row>
     <row r="100" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C100" s="1">
         <v>330</v>
@@ -5433,13 +5415,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" customHeight="1" spans="1:11">
-      <c r="A127" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>91</v>
-      </c>
+    <row r="127" customHeight="1" spans="3:11">
       <c r="C127" s="1">
         <v>426</v>
       </c>
@@ -5453,7 +5429,7 @@
         <v>280</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>17</v>
@@ -5470,10 +5446,10 @@
     </row>
     <row r="128" customHeight="1" spans="1:11">
       <c r="A128" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C128" s="1">
         <v>427</v>
@@ -5505,10 +5481,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C129" s="1">
         <v>428</v>
@@ -5540,10 +5516,10 @@
     </row>
     <row r="130" customHeight="1" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C130" s="1">
         <v>429</v>
@@ -5575,10 +5551,10 @@
     </row>
     <row r="131" customHeight="1" spans="1:11">
       <c r="A131" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C131" s="1">
         <v>430</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="295">
   <si>
     <t>Id</t>
   </si>
@@ -311,16 +311,16 @@
     <t>斗笠二七阶</t>
   </si>
   <si>
+    <t>127,4007</t>
+  </si>
+  <si>
+    <t>1,134400000</t>
+  </si>
+  <si>
+    <t>斗笠二八阶</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>127,4007</t>
-  </si>
-  <si>
-    <t>1,134400000</t>
-  </si>
-  <si>
-    <t>斗笠二八阶</t>
   </si>
   <si>
     <t>128,4007</t>
@@ -2762,13 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" customHeight="1" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>94</v>
-      </c>
+    <row r="32" customHeight="1" spans="3:11">
       <c r="C32" s="1">
         <v>127</v>
       </c>
@@ -2779,16 +2773,16 @@
         <v>14</v>
       </c>
       <c r="F32" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="H32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="J32" s="1">
         <v>128</v>
@@ -2799,10 +2793,10 @@
     </row>
     <row r="33" customHeight="1" spans="1:11">
       <c r="A33" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C33" s="1">
         <v>128</v>
@@ -2834,10 +2828,10 @@
     </row>
     <row r="34" customHeight="1" spans="1:11">
       <c r="A34" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C34" s="1">
         <v>129</v>
@@ -2869,10 +2863,10 @@
     </row>
     <row r="35" customHeight="1" spans="1:11">
       <c r="A35" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C35" s="1">
         <v>130</v>
@@ -3656,13 +3650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" customHeight="1" spans="1:11">
-      <c r="A66" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>94</v>
-      </c>
+    <row r="66" customHeight="1" spans="3:11">
       <c r="C66" s="1">
         <v>227</v>
       </c>
@@ -3676,7 +3664,7 @@
         <v>160</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H66" s="4" t="s">
         <v>17</v>
@@ -3693,10 +3681,10 @@
     </row>
     <row r="67" customHeight="1" spans="1:11">
       <c r="A67" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C67" s="1">
         <v>228</v>
@@ -3728,10 +3716,10 @@
     </row>
     <row r="68" customHeight="1" spans="1:11">
       <c r="A68" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C68" s="1">
         <v>229</v>
@@ -3763,10 +3751,10 @@
     </row>
     <row r="69" customHeight="1" spans="1:11">
       <c r="A69" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C69" s="1">
         <v>230</v>
@@ -4550,13 +4538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" customHeight="1" spans="1:11">
-      <c r="A97" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>94</v>
-      </c>
+    <row r="97" customHeight="1" spans="3:11">
       <c r="C97" s="1">
         <v>327</v>
       </c>
@@ -4570,7 +4552,7 @@
         <v>221</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>17</v>
@@ -4587,10 +4569,10 @@
     </row>
     <row r="98" customHeight="1" spans="1:11">
       <c r="A98" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C98" s="1">
         <v>328</v>
@@ -4622,10 +4604,10 @@
     </row>
     <row r="99" customHeight="1" spans="1:11">
       <c r="A99" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C99" s="1">
         <v>329</v>
@@ -4657,10 +4639,10 @@
     </row>
     <row r="100" customHeight="1" spans="1:11">
       <c r="A100" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C100" s="1">
         <v>330</v>
@@ -5444,13 +5426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" customHeight="1" spans="1:11">
-      <c r="A128" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>94</v>
-      </c>
+    <row r="128" customHeight="1" spans="3:11">
       <c r="C128" s="1">
         <v>427</v>
       </c>
@@ -5464,7 +5440,7 @@
         <v>282</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>17</v>
@@ -5481,10 +5457,10 @@
     </row>
     <row r="129" customHeight="1" spans="1:11">
       <c r="A129" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C129" s="1">
         <v>428</v>
@@ -5516,10 +5492,10 @@
     </row>
     <row r="130" customHeight="1" spans="1:11">
       <c r="A130" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C130" s="1">
         <v>429</v>
@@ -5551,10 +5527,10 @@
     </row>
     <row r="131" customHeight="1" spans="1:11">
       <c r="A131" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C131" s="1">
         <v>430</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="304">
   <si>
     <t>Id</t>
   </si>
@@ -912,6 +912,33 @@
   </si>
   <si>
     <t>红装精华</t>
+  </si>
+  <si>
+    <t>4011,4201</t>
+  </si>
+  <si>
+    <t>20,10000</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>4023,4111</t>
+  </si>
+  <si>
+    <t>5,20000</t>
+  </si>
+  <si>
+    <t>红色魂心</t>
+  </si>
+  <si>
+    <t>4024,4111</t>
+  </si>
+  <si>
+    <t>5,100000</t>
+  </si>
+  <si>
+    <t>金色魂心</t>
   </si>
 </sst>
 </file>
@@ -1907,7 +1934,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K138"/>
+  <dimension ref="A3:K141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5589,6 +5616,93 @@
         <v>5</v>
       </c>
     </row>
+    <row r="139" customHeight="1" spans="3:11">
+      <c r="C139" s="1">
+        <v>502</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E139" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F139" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="G139" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J139" s="1">
+        <v>4019</v>
+      </c>
+      <c r="K139" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:11">
+      <c r="C140" s="1">
+        <v>503</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E140" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F140" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H140" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J140" s="1">
+        <v>4024</v>
+      </c>
+      <c r="K140" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:11">
+      <c r="C141" s="1">
+        <v>504</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="E141" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F141" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="G141" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J141" s="1">
+        <v>4025</v>
+      </c>
+      <c r="K141" s="1">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="304">
   <si>
     <t>Id</t>
   </si>
@@ -917,7 +917,7 @@
     <t>4011,4201</t>
   </si>
   <si>
-    <t>20,10000</t>
+    <t>20,100000</t>
   </si>
   <si>
     <t>金装精华</t>
@@ -1938,13 +1938,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
     <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.75" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.1272727272727" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5645,7 +5645,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="3:11">
+    <row r="140" customHeight="1" spans="1:11">
+      <c r="A140" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="C140" s="1">
         <v>503</v>
       </c>
@@ -5674,7 +5680,13 @@
         <v>5</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="3:11">
+    <row r="141" customHeight="1" spans="1:11">
+      <c r="A141" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>97</v>
+      </c>
       <c r="C141" s="1">
         <v>504</v>
       </c>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -917,7 +917,7 @@
     <t>4011,4201</t>
   </si>
   <si>
-    <t>20,100000</t>
+    <t>10,100000</t>
   </si>
   <si>
     <t>金装精华</t>
@@ -1938,13 +1938,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13.3727272727273" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1272727272727" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
     <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7583333333333" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="305">
   <si>
     <t>Id</t>
   </si>
@@ -56,6 +56,9 @@
     <t>TargetType</t>
   </si>
   <si>
+    <t>AutoHide</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -320,25 +323,25 @@
     <t>斗笠二八阶</t>
   </si>
   <si>
+    <t>128,4007</t>
+  </si>
+  <si>
+    <t>1,268800000</t>
+  </si>
+  <si>
+    <t>斗笠二九阶</t>
+  </si>
+  <si>
+    <t>129,4007</t>
+  </si>
+  <si>
+    <t>1,537600000</t>
+  </si>
+  <si>
+    <t>斗笠三十阶</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>128,4007</t>
-  </si>
-  <si>
-    <t>1,268800000</t>
-  </si>
-  <si>
-    <t>斗笠二九阶</t>
-  </si>
-  <si>
-    <t>129,4007</t>
-  </si>
-  <si>
-    <t>1,537600000</t>
-  </si>
-  <si>
-    <t>斗笠三十阶</t>
   </si>
   <si>
     <t>130,4007</t>
@@ -1934,7 +1937,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:K141"/>
+  <dimension ref="A3:L141"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1944,11 +1947,11 @@
     <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.7583333333333" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="1"/>
+    <col min="11" max="12" width="15.125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1976,8 +1979,11 @@
       <c r="K3" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
@@ -2005,57 +2011,63 @@
       <c r="K4" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="3:11">
+      <c r="L5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>101</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="1">
         <v>102</v>
@@ -2063,28 +2075,31 @@
       <c r="K6" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="3:11">
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>102</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J7" s="1">
         <v>103</v>
@@ -2092,28 +2107,31 @@
       <c r="K7" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" customHeight="1" spans="3:11">
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>103</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J8" s="1">
         <v>104</v>
@@ -2121,28 +2139,31 @@
       <c r="K8" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:11">
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>104</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1">
         <v>105</v>
@@ -2150,28 +2171,31 @@
       <c r="K9" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:11">
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J10" s="1">
         <v>106</v>
@@ -2179,28 +2203,31 @@
       <c r="K10" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:11">
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>106</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J11" s="1">
         <v>107</v>
@@ -2208,28 +2235,31 @@
       <c r="K11" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:11">
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>107</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J12" s="1">
         <v>108</v>
@@ -2237,28 +2267,31 @@
       <c r="K12" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:11">
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>108</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J13" s="1">
         <v>109</v>
@@ -2266,28 +2299,31 @@
       <c r="K13" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:11">
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:12">
       <c r="C14" s="1">
         <v>109</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J14" s="1">
         <v>110</v>
@@ -2295,28 +2331,31 @@
       <c r="K14" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:11">
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:12">
       <c r="C15" s="1">
         <v>110</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J15" s="1">
         <v>111</v>
@@ -2324,28 +2363,31 @@
       <c r="K15" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:11">
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:12">
       <c r="C16" s="1">
         <v>111</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J16" s="1">
         <v>112</v>
@@ -2353,28 +2395,31 @@
       <c r="K16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:11">
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1">
         <v>112</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J17" s="1">
         <v>113</v>
@@ -2382,28 +2427,31 @@
       <c r="K17" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:11">
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1">
         <v>113</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J18" s="1">
         <v>114</v>
@@ -2411,28 +2459,31 @@
       <c r="K18" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:11">
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:12">
       <c r="C19" s="1">
         <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J19" s="1">
         <v>115</v>
@@ -2440,28 +2491,31 @@
       <c r="K19" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:11">
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>115</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J20" s="1">
         <v>116</v>
@@ -2469,28 +2523,31 @@
       <c r="K20" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:11">
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>116</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J21" s="1">
         <v>117</v>
@@ -2498,28 +2555,31 @@
       <c r="K21" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:11">
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:12">
       <c r="C22" s="1">
         <v>117</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J22" s="1">
         <v>118</v>
@@ -2527,28 +2587,31 @@
       <c r="K22" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:11">
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:12">
       <c r="C23" s="1">
         <v>118</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J23" s="1">
         <v>119</v>
@@ -2556,28 +2619,31 @@
       <c r="K23" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:11">
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:12">
       <c r="C24" s="1">
         <v>119</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J24" s="1">
         <v>120</v>
@@ -2585,28 +2651,31 @@
       <c r="K24" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:11">
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
       <c r="C25" s="1">
         <v>120</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J25" s="1">
         <v>121</v>
@@ -2614,28 +2683,31 @@
       <c r="K25" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:11">
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
       <c r="C26" s="1">
         <v>121</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J26" s="1">
         <v>122</v>
@@ -2643,28 +2715,31 @@
       <c r="K26" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:11">
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:12">
       <c r="C27" s="1">
         <v>122</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J27" s="1">
         <v>123</v>
@@ -2672,28 +2747,31 @@
       <c r="K27" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:11">
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:12">
       <c r="C28" s="1">
         <v>123</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J28" s="1">
         <v>124</v>
@@ -2701,28 +2779,31 @@
       <c r="K28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:11">
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
       <c r="C29" s="1">
         <v>124</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J29" s="1">
         <v>125</v>
@@ -2730,28 +2811,31 @@
       <c r="K29" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:11">
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
       <c r="C30" s="1">
         <v>125</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J30" s="1">
         <v>126</v>
@@ -2759,28 +2843,31 @@
       <c r="K30" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:11">
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
       <c r="C31" s="1">
         <v>126</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J31" s="1">
         <v>127</v>
@@ -2788,28 +2875,31 @@
       <c r="K31" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:11">
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:12">
       <c r="C32" s="1">
         <v>127</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J32" s="1">
         <v>128</v>
@@ -2817,22 +2907,19 @@
       <c r="K32" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="33" customHeight="1" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
       <c r="C33" s="1">
         <v>128</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>98</v>
@@ -2841,7 +2928,7 @@
         <v>99</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>100</v>
@@ -2852,22 +2939,19 @@
       <c r="K33" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="34" customHeight="1" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L33" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:12">
       <c r="C34" s="1">
         <v>129</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>101</v>
@@ -2876,7 +2960,7 @@
         <v>102</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>103</v>
@@ -2887,34 +2971,37 @@
       <c r="K34" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" customHeight="1" spans="1:11">
+      <c r="L34" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:12">
       <c r="A35" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C35" s="1">
         <v>130</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" s="1">
         <v>131</v>
@@ -2922,28 +3009,31 @@
       <c r="K35" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:11">
+      <c r="L35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
       <c r="C40" s="1">
         <v>201</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J40" s="1">
         <v>202</v>
@@ -2951,28 +3041,31 @@
       <c r="K40" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:11">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
       <c r="C41" s="1">
         <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J41" s="1">
         <v>203</v>
@@ -2980,28 +3073,31 @@
       <c r="K41" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:11">
+      <c r="L41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
       <c r="C42" s="1">
         <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" s="1">
         <v>204</v>
@@ -3009,28 +3105,31 @@
       <c r="K42" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:11">
+      <c r="L42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="1">
         <v>204</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J43" s="1">
         <v>205</v>
@@ -3038,28 +3137,31 @@
       <c r="K43" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:11">
+      <c r="L43" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="3:12">
       <c r="C44" s="1">
         <v>205</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J44" s="1">
         <v>206</v>
@@ -3067,28 +3169,31 @@
       <c r="K44" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:11">
+      <c r="L44" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="3:12">
       <c r="C45" s="1">
         <v>206</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J45" s="1">
         <v>207</v>
@@ -3096,28 +3201,31 @@
       <c r="K45" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:11">
+      <c r="L45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="3:12">
       <c r="C46" s="1">
         <v>207</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J46" s="1">
         <v>208</v>
@@ -3125,28 +3233,31 @@
       <c r="K46" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:11">
+      <c r="L46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:12">
       <c r="C47" s="1">
         <v>208</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J47" s="1">
         <v>209</v>
@@ -3154,28 +3265,31 @@
       <c r="K47" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" customHeight="1" spans="3:11">
+      <c r="L47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="3:12">
       <c r="C48" s="1">
         <v>209</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J48" s="1">
         <v>210</v>
@@ -3183,28 +3297,31 @@
       <c r="K48" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="49" customHeight="1" spans="3:11">
+      <c r="L48" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="3:12">
       <c r="C49" s="1">
         <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J49" s="1">
         <v>211</v>
@@ -3212,28 +3329,31 @@
       <c r="K49" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="50" customHeight="1" spans="3:11">
+      <c r="L49" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="3:12">
       <c r="C50" s="1">
         <v>211</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J50" s="1">
         <v>212</v>
@@ -3241,28 +3361,31 @@
       <c r="K50" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="51" customHeight="1" spans="3:11">
+      <c r="L50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="3:12">
       <c r="C51" s="1">
         <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J51" s="1">
         <v>213</v>
@@ -3270,28 +3393,31 @@
       <c r="K51" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:11">
+      <c r="L51" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:12">
       <c r="C52" s="1">
         <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J52" s="1">
         <v>214</v>
@@ -3299,28 +3425,31 @@
       <c r="K52" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:11">
+      <c r="L52" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:12">
       <c r="C53" s="1">
         <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J53" s="1">
         <v>215</v>
@@ -3328,28 +3457,31 @@
       <c r="K53" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:11">
+      <c r="L53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="3:12">
       <c r="C54" s="1">
         <v>215</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J54" s="1">
         <v>216</v>
@@ -3357,28 +3489,31 @@
       <c r="K54" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:11">
+      <c r="L54" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="1">
         <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J55" s="1">
         <v>217</v>
@@ -3386,28 +3521,31 @@
       <c r="K55" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:11">
+      <c r="L55" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="1">
         <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J56" s="1">
         <v>218</v>
@@ -3415,28 +3553,31 @@
       <c r="K56" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:11">
+      <c r="L56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="1">
         <v>218</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J57" s="1">
         <v>219</v>
@@ -3444,28 +3585,31 @@
       <c r="K57" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="58" customHeight="1" spans="3:11">
+      <c r="L57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="1">
         <v>219</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J58" s="1">
         <v>220</v>
@@ -3473,28 +3617,31 @@
       <c r="K58" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="59" customHeight="1" spans="3:11">
+      <c r="L58" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="3:12">
       <c r="C59" s="1">
         <v>220</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J59" s="1">
         <v>221</v>
@@ -3502,28 +3649,31 @@
       <c r="K59" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="60" customHeight="1" spans="3:11">
+      <c r="L59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="1">
         <v>221</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J60" s="1">
         <v>222</v>
@@ -3531,28 +3681,31 @@
       <c r="K60" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="61" customHeight="1" spans="3:11">
+      <c r="L60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="1">
         <v>222</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J61" s="1">
         <v>223</v>
@@ -3560,28 +3713,31 @@
       <c r="K61" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:11">
+      <c r="L61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="1">
         <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J62" s="1">
         <v>224</v>
@@ -3589,28 +3745,31 @@
       <c r="K62" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:11">
+      <c r="L62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="1">
         <v>224</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J63" s="1">
         <v>225</v>
@@ -3618,28 +3777,31 @@
       <c r="K63" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:11">
+      <c r="L63" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="1">
         <v>225</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J64" s="1">
         <v>226</v>
@@ -3647,28 +3809,31 @@
       <c r="K64" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:11">
+      <c r="L64" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" customHeight="1" spans="3:12">
       <c r="C65" s="1">
         <v>226</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J65" s="1">
         <v>227</v>
@@ -3676,28 +3841,31 @@
       <c r="K65" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:11">
+      <c r="L65" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" customHeight="1" spans="3:12">
       <c r="C66" s="1">
         <v>227</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J66" s="1">
         <v>228</v>
@@ -3705,34 +3873,31 @@
       <c r="K66" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="67" customHeight="1" spans="1:11">
-      <c r="A67" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" customHeight="1" spans="3:12">
       <c r="C67" s="1">
         <v>228</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>99</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J67" s="1">
         <v>229</v>
@@ -3740,34 +3905,31 @@
       <c r="K67" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="68" customHeight="1" spans="1:11">
-      <c r="A68" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" customHeight="1" spans="3:12">
       <c r="C68" s="1">
         <v>229</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J68" s="1">
         <v>230</v>
@@ -3775,34 +3937,37 @@
       <c r="K68" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="69" customHeight="1" spans="1:11">
+      <c r="L68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" customHeight="1" spans="1:12">
       <c r="A69" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C69" s="1">
         <v>230</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J69" s="1">
         <v>231</v>
@@ -3810,28 +3975,31 @@
       <c r="K69" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="71" customHeight="1" spans="3:11">
+      <c r="L69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" customHeight="1" spans="3:12">
       <c r="C71" s="1">
         <v>301</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J71" s="1">
         <v>302</v>
@@ -3839,28 +4007,31 @@
       <c r="K71" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:11">
+      <c r="L71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:12">
       <c r="C72" s="1">
         <v>302</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J72" s="1">
         <v>303</v>
@@ -3868,28 +4039,31 @@
       <c r="K72" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:11">
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:12">
       <c r="C73" s="1">
         <v>303</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J73" s="1">
         <v>304</v>
@@ -3897,28 +4071,31 @@
       <c r="K73" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:11">
+      <c r="L73" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="1">
         <v>304</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J74" s="1">
         <v>305</v>
@@ -3926,28 +4103,31 @@
       <c r="K74" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:11">
+      <c r="L74" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
         <v>305</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J75" s="1">
         <v>306</v>
@@ -3955,28 +4135,31 @@
       <c r="K75" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:11">
+      <c r="L75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
         <v>306</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J76" s="1">
         <v>307</v>
@@ -3984,28 +4167,31 @@
       <c r="K76" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:11">
+      <c r="L76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
         <v>307</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J77" s="1">
         <v>308</v>
@@ -4013,28 +4199,31 @@
       <c r="K77" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="78" customHeight="1" spans="3:11">
+      <c r="L77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
         <v>308</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J78" s="1">
         <v>309</v>
@@ -4042,28 +4231,31 @@
       <c r="K78" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="79" customHeight="1" spans="3:11">
+      <c r="L78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
         <v>309</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J79" s="1">
         <v>310</v>
@@ -4071,28 +4263,31 @@
       <c r="K79" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="80" customHeight="1" spans="3:11">
+      <c r="L79" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
         <v>310</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J80" s="1">
         <v>311</v>
@@ -4100,28 +4295,31 @@
       <c r="K80" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" customHeight="1" spans="3:11">
+      <c r="L80" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
         <v>311</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J81" s="1">
         <v>312</v>
@@ -4129,28 +4327,31 @@
       <c r="K81" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="82" customHeight="1" spans="3:11">
+      <c r="L81" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
         <v>312</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J82" s="1">
         <v>313</v>
@@ -4158,28 +4359,31 @@
       <c r="K82" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="83" customHeight="1" spans="3:11">
+      <c r="L82" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
         <v>313</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J83" s="1">
         <v>314</v>
@@ -4187,28 +4391,31 @@
       <c r="K83" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="84" customHeight="1" spans="3:11">
+      <c r="L83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
         <v>314</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J84" s="1">
         <v>315</v>
@@ -4216,28 +4423,31 @@
       <c r="K84" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="85" customHeight="1" spans="3:11">
+      <c r="L84" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
         <v>315</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J85" s="1">
         <v>316</v>
@@ -4245,28 +4455,31 @@
       <c r="K85" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="86" customHeight="1" spans="3:11">
+      <c r="L85" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
         <v>316</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J86" s="1">
         <v>317</v>
@@ -4274,28 +4487,31 @@
       <c r="K86" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="87" customHeight="1" spans="3:11">
+      <c r="L86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
         <v>317</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J87" s="1">
         <v>318</v>
@@ -4303,28 +4519,31 @@
       <c r="K87" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="88" customHeight="1" spans="3:11">
+      <c r="L87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
         <v>318</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J88" s="1">
         <v>319</v>
@@ -4332,28 +4551,31 @@
       <c r="K88" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="89" customHeight="1" spans="3:11">
+      <c r="L88" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
         <v>319</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J89" s="1">
         <v>320</v>
@@ -4361,28 +4583,31 @@
       <c r="K89" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="90" customHeight="1" spans="3:11">
+      <c r="L89" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
         <v>320</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J90" s="1">
         <v>321</v>
@@ -4390,28 +4615,31 @@
       <c r="K90" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="91" customHeight="1" spans="3:11">
+      <c r="L90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
         <v>321</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J91" s="1">
         <v>322</v>
@@ -4419,28 +4647,31 @@
       <c r="K91" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="92" customHeight="1" spans="3:11">
+      <c r="L91" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
         <v>322</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J92" s="1">
         <v>323</v>
@@ -4448,28 +4679,31 @@
       <c r="K92" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="93" customHeight="1" spans="3:11">
+      <c r="L92" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
         <v>323</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J93" s="1">
         <v>324</v>
@@ -4477,28 +4711,31 @@
       <c r="K93" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="94" customHeight="1" spans="3:11">
+      <c r="L93" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
         <v>324</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J94" s="1">
         <v>325</v>
@@ -4506,28 +4743,31 @@
       <c r="K94" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="95" customHeight="1" spans="3:11">
+      <c r="L94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
         <v>325</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J95" s="1">
         <v>326</v>
@@ -4535,28 +4775,31 @@
       <c r="K95" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="96" customHeight="1" spans="3:11">
+      <c r="L95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
         <v>326</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J96" s="1">
         <v>327</v>
@@ -4564,28 +4807,31 @@
       <c r="K96" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="97" customHeight="1" spans="3:11">
+      <c r="L96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
         <v>327</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J97" s="1">
         <v>328</v>
@@ -4593,34 +4839,31 @@
       <c r="K97" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="98" customHeight="1" spans="1:11">
-      <c r="A98" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
         <v>328</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G98" s="4" t="s">
         <v>99</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J98" s="1">
         <v>329</v>
@@ -4628,34 +4871,31 @@
       <c r="K98" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="99" customHeight="1" spans="1:11">
-      <c r="A99" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
         <v>329</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G99" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J99" s="1">
         <v>330</v>
@@ -4663,34 +4903,37 @@
       <c r="K99" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:11">
+      <c r="L99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="1:12">
       <c r="A100" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C100" s="1">
         <v>330</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J100" s="1">
         <v>331</v>
@@ -4698,28 +4941,31 @@
       <c r="K100" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:11">
+      <c r="L100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
         <v>401</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J102" s="1">
         <v>402</v>
@@ -4727,28 +4973,31 @@
       <c r="K102" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="103" customHeight="1" spans="3:11">
+      <c r="L102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
         <v>402</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J103" s="1">
         <v>403</v>
@@ -4756,28 +5005,31 @@
       <c r="K103" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="104" customHeight="1" spans="3:11">
+      <c r="L103" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
         <v>403</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J104" s="1">
         <v>404</v>
@@ -4785,28 +5037,31 @@
       <c r="K104" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="105" customHeight="1" spans="3:11">
+      <c r="L104" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
         <v>404</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J105" s="1">
         <v>405</v>
@@ -4814,28 +5069,31 @@
       <c r="K105" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:11">
+      <c r="L105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
         <v>405</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J106" s="1">
         <v>406</v>
@@ -4843,28 +5101,31 @@
       <c r="K106" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:11">
+      <c r="L106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
         <v>406</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="J107" s="1">
         <v>407</v>
@@ -4872,28 +5133,31 @@
       <c r="K107" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="108" customHeight="1" spans="3:11">
+      <c r="L107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
         <v>407</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J108" s="1">
         <v>408</v>
@@ -4901,28 +5165,31 @@
       <c r="K108" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="109" customHeight="1" spans="3:11">
+      <c r="L108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
         <v>408</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J109" s="1">
         <v>409</v>
@@ -4930,28 +5197,31 @@
       <c r="K109" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="110" customHeight="1" spans="3:11">
+      <c r="L109" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
         <v>409</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J110" s="1">
         <v>410</v>
@@ -4959,28 +5229,31 @@
       <c r="K110" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="111" customHeight="1" spans="3:11">
+      <c r="L110" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
         <v>410</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="J111" s="1">
         <v>411</v>
@@ -4988,28 +5261,31 @@
       <c r="K111" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="112" customHeight="1" spans="3:11">
+      <c r="L111" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
         <v>411</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="J112" s="1">
         <v>412</v>
@@ -5017,28 +5293,31 @@
       <c r="K112" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:11">
+      <c r="L112" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
         <v>412</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J113" s="1">
         <v>413</v>
@@ -5046,28 +5325,31 @@
       <c r="K113" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="114" customHeight="1" spans="3:11">
+      <c r="L113" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
         <v>413</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="J114" s="1">
         <v>414</v>
@@ -5075,28 +5357,31 @@
       <c r="K114" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="115" customHeight="1" spans="3:11">
+      <c r="L114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
         <v>414</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J115" s="1">
         <v>415</v>
@@ -5104,28 +5389,31 @@
       <c r="K115" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="116" customHeight="1" spans="3:11">
+      <c r="L115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
         <v>415</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="J116" s="1">
         <v>416</v>
@@ -5133,28 +5421,31 @@
       <c r="K116" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="117" customHeight="1" spans="3:11">
+      <c r="L116" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
         <v>416</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="J117" s="1">
         <v>417</v>
@@ -5162,28 +5453,31 @@
       <c r="K117" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="118" customHeight="1" spans="3:11">
+      <c r="L117" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
         <v>417</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="J118" s="1">
         <v>418</v>
@@ -5191,28 +5485,31 @@
       <c r="K118" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="119" customHeight="1" spans="3:11">
+      <c r="L118" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
         <v>418</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J119" s="1">
         <v>419</v>
@@ -5220,28 +5517,31 @@
       <c r="K119" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="120" customHeight="1" spans="3:11">
+      <c r="L119" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
         <v>419</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J120" s="1">
         <v>420</v>
@@ -5249,28 +5549,31 @@
       <c r="K120" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="121" customHeight="1" spans="3:11">
+      <c r="L120" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
         <v>420</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="J121" s="1">
         <v>421</v>
@@ -5278,28 +5581,31 @@
       <c r="K121" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="122" customHeight="1" spans="3:11">
+      <c r="L121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
         <v>421</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J122" s="1">
         <v>422</v>
@@ -5307,28 +5613,31 @@
       <c r="K122" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="123" customHeight="1" spans="3:11">
+      <c r="L122" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" customHeight="1" spans="3:12">
       <c r="C123" s="1">
         <v>422</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J123" s="1">
         <v>423</v>
@@ -5336,28 +5645,31 @@
       <c r="K123" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="124" customHeight="1" spans="3:11">
+      <c r="L123" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:12">
       <c r="C124" s="1">
         <v>423</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="J124" s="1">
         <v>424</v>
@@ -5365,28 +5677,31 @@
       <c r="K124" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="125" customHeight="1" spans="3:11">
+      <c r="L124" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:12">
       <c r="C125" s="1">
         <v>424</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J125" s="1">
         <v>425</v>
@@ -5394,28 +5709,31 @@
       <c r="K125" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="126" customHeight="1" spans="3:11">
+      <c r="L125" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:12">
       <c r="C126" s="1">
         <v>425</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J126" s="1">
         <v>426</v>
@@ -5423,28 +5741,31 @@
       <c r="K126" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="127" customHeight="1" spans="3:11">
+      <c r="L126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:12">
       <c r="C127" s="1">
         <v>426</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J127" s="1">
         <v>427</v>
@@ -5452,28 +5773,31 @@
       <c r="K127" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="128" customHeight="1" spans="3:11">
+      <c r="L127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:12">
       <c r="C128" s="1">
         <v>427</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J128" s="1">
         <v>428</v>
@@ -5481,34 +5805,31 @@
       <c r="K128" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="129" customHeight="1" spans="1:11">
-      <c r="A129" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L128" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
         <v>428</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G129" s="4" t="s">
         <v>99</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J129" s="1">
         <v>429</v>
@@ -5516,34 +5837,31 @@
       <c r="K129" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="130" customHeight="1" spans="1:11">
-      <c r="A130" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>97</v>
-      </c>
+      <c r="L129" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
         <v>429</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G130" s="4" t="s">
         <v>102</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="J130" s="1">
         <v>430</v>
@@ -5551,34 +5869,37 @@
       <c r="K130" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="131" customHeight="1" spans="1:11">
+      <c r="L130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="1:12">
       <c r="A131" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C131" s="1">
         <v>430</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H131" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J131" s="1">
         <v>431</v>
@@ -5586,28 +5907,31 @@
       <c r="K131" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="138" customHeight="1" spans="3:11">
+      <c r="L131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
         <v>501</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H138" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J138" s="1">
         <v>4011</v>
@@ -5615,28 +5939,31 @@
       <c r="K138" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="139" customHeight="1" spans="3:11">
+      <c r="L138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
         <v>502</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H139" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="J139" s="1">
         <v>4019</v>
@@ -5644,34 +5971,37 @@
       <c r="K139" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="140" customHeight="1" spans="1:11">
+      <c r="L139" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:12">
       <c r="A140" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C140" s="1">
         <v>503</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H140" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I140" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="J140" s="1">
         <v>4024</v>
@@ -5679,40 +6009,46 @@
       <c r="K140" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="141" customHeight="1" spans="1:11">
+      <c r="L140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:12">
       <c r="A141" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C141" s="1">
         <v>504</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H141" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J141" s="1">
         <v>4025</v>
       </c>
       <c r="K141" s="1">
         <v>5</v>
+      </c>
+      <c r="L141" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="308">
   <si>
     <t>Id</t>
   </si>
@@ -929,7 +929,7 @@
     <t>4023,4111</t>
   </si>
   <si>
-    <t>5,20000</t>
+    <t>6,20000</t>
   </si>
   <si>
     <t>红色魂心</t>
@@ -938,10 +938,19 @@
     <t>4024,4111</t>
   </si>
   <si>
-    <t>5,100000</t>
+    <t>6,100000</t>
   </si>
   <si>
     <t>金色魂心</t>
+  </si>
+  <si>
+    <t>4028,4111</t>
+  </si>
+  <si>
+    <t>40,50000</t>
+  </si>
+  <si>
+    <t>青龙神器</t>
   </si>
 </sst>
 </file>
@@ -1937,17 +1946,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L141"/>
+  <dimension ref="A3:L142"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13.375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
     <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7583333333333" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
+    <col min="11" max="12" width="15.1272727272727" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -5975,13 +5984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" customHeight="1" spans="1:12">
-      <c r="A140" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B140" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
         <v>503</v>
       </c>
@@ -6013,13 +6016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" customHeight="1" spans="1:12">
-      <c r="A141" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
         <v>504</v>
       </c>
@@ -6048,6 +6045,38 @@
         <v>5</v>
       </c>
       <c r="L141" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:12">
+      <c r="C142" s="1">
+        <v>505</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E142" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F142" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="G142" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H142" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J142" s="1">
+        <v>35</v>
+      </c>
+      <c r="K142" s="1">
+        <v>4</v>
+      </c>
+      <c r="L142" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -947,7 +947,7 @@
     <t>4028,4111</t>
   </si>
   <si>
-    <t>40,50000</t>
+    <t>40,100000</t>
   </si>
   <si>
     <t>青龙神器</t>
@@ -1950,13 +1950,13 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13.3727272727273" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1272727272727" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3716814159292" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1238938053097" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3716814159292" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5044247787611" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15.1272727272727" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7522123893805" style="1" customWidth="1"/>
+    <col min="11" max="12" width="15.1238938053097" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="314">
   <si>
     <t>Id</t>
   </si>
@@ -920,7 +920,7 @@
     <t>4011,4201</t>
   </si>
   <si>
-    <t>10,100000</t>
+    <t>10,50000</t>
   </si>
   <si>
     <t>金装精华</t>
@@ -951,6 +951,24 @@
   </si>
   <si>
     <t>青龙神器</t>
+  </si>
+  <si>
+    <t>4029,4111</t>
+  </si>
+  <si>
+    <t>白虎神器</t>
+  </si>
+  <si>
+    <t>4030,4111</t>
+  </si>
+  <si>
+    <t>朱雀神器</t>
+  </si>
+  <si>
+    <t>4031,4111</t>
+  </si>
+  <si>
+    <t>玄武神器</t>
   </si>
 </sst>
 </file>
@@ -1946,7 +1964,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L142"/>
+  <dimension ref="A3:L145"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6080,6 +6098,114 @@
         <v>0</v>
       </c>
     </row>
+    <row r="143" customHeight="1" spans="3:12">
+      <c r="C143" s="1">
+        <v>506</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E143" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F143" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="G143" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J143" s="1">
+        <v>37</v>
+      </c>
+      <c r="K143" s="1">
+        <v>4</v>
+      </c>
+      <c r="L143" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:12">
+      <c r="A144" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C144" s="1">
+        <v>508</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E144" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F144" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H144" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J144" s="1">
+        <v>38</v>
+      </c>
+      <c r="K144" s="1">
+        <v>4</v>
+      </c>
+      <c r="L144" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="1:12">
+      <c r="A145" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C145" s="1">
+        <v>509</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E145" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J145" s="1">
+        <v>39</v>
+      </c>
+      <c r="K145" s="1">
+        <v>4</v>
+      </c>
+      <c r="L145" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="314">
   <si>
     <t>Id</t>
   </si>
@@ -6130,13 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" customHeight="1" spans="1:12">
-      <c r="A144" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
         <v>508</v>
       </c>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27952" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="321">
   <si>
     <t>Id</t>
   </si>
@@ -969,6 +969,27 @@
   </si>
   <si>
     <t>玄武神器</t>
+  </si>
+  <si>
+    <t>4005,4111</t>
+  </si>
+  <si>
+    <t>20000,1000</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
+  </si>
+  <si>
+    <t>30000,1000</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
+    <t>40000,1000</t>
+  </si>
+  <si>
+    <t>永恒精华</t>
   </si>
 </sst>
 </file>
@@ -1964,17 +1985,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L145"/>
+  <dimension ref="A3:L149"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13.3716814159292" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1238938053097" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.3716814159292" style="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5044247787611" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.3727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.1272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.3727272727273" style="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7522123893805" style="1" customWidth="1"/>
-    <col min="11" max="12" width="15.1238938053097" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
+    <col min="11" max="12" width="15.1272727272727" style="1" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -6197,6 +6218,114 @@
         <v>4</v>
       </c>
       <c r="L145" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:12">
+      <c r="C147" s="1">
+        <v>521</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E147" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G147" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="J147" s="1">
+        <v>4035</v>
+      </c>
+      <c r="K147" s="1">
+        <v>5</v>
+      </c>
+      <c r="L147" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" customHeight="1" spans="1:12">
+      <c r="A148" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C148" s="1">
+        <v>522</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G148" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="H148" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J148" s="1">
+        <v>4036</v>
+      </c>
+      <c r="K148" s="1">
+        <v>5</v>
+      </c>
+      <c r="L148" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="1:12">
+      <c r="A149" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C149" s="1">
+        <v>523</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E149" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="G149" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J149" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K149" s="1">
+        <v>5</v>
+      </c>
+      <c r="L149" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
   <si>
     <t>Id</t>
   </si>
@@ -990,6 +990,15 @@
   </si>
   <si>
     <t>永恒精华</t>
+  </si>
+  <si>
+    <t>4012,4111</t>
+  </si>
+  <si>
+    <t>10,10000</t>
+  </si>
+  <si>
+    <t>12阶技能</t>
   </si>
 </sst>
 </file>
@@ -1985,7 +1994,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L149"/>
+  <dimension ref="A3:L151"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6329,6 +6338,38 @@
         <v>0</v>
       </c>
     </row>
+    <row r="151" customHeight="1" spans="3:12">
+      <c r="C151" s="1">
+        <v>531</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G151" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H151" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J151" s="1">
+        <v>42</v>
+      </c>
+      <c r="K151" s="1">
+        <v>4</v>
+      </c>
+      <c r="L151" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -992,7 +992,7 @@
     <t>永恒精华</t>
   </si>
   <si>
-    <t>4012,4111</t>
+    <t>4112,4111</t>
   </si>
   <si>
     <t>10,10000</t>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="324">
   <si>
     <t>Id</t>
   </si>
@@ -6192,13 +6192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="1:12">
-      <c r="A145" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B145" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
         <v>509</v>
       </c>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="342">
   <si>
     <t>Id</t>
   </si>
@@ -86,7 +86,7 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>斗笠二阶</t>
+    <t>斗笠2阶</t>
   </si>
   <si>
     <t>102,4007</t>
@@ -95,7 +95,7 @@
     <t>1,4</t>
   </si>
   <si>
-    <t>斗笠三阶</t>
+    <t>斗笠3阶</t>
   </si>
   <si>
     <t>103,4007</t>
@@ -104,7 +104,7 @@
     <t>1,8</t>
   </si>
   <si>
-    <t>斗笠四阶</t>
+    <t>斗笠4阶</t>
   </si>
   <si>
     <t>104,4007</t>
@@ -113,7 +113,7 @@
     <t>1,16</t>
   </si>
   <si>
-    <t>斗笠五阶</t>
+    <t>斗笠5阶</t>
   </si>
   <si>
     <t>105,4007</t>
@@ -122,7 +122,7 @@
     <t>1,32</t>
   </si>
   <si>
-    <t>斗笠六阶</t>
+    <t>斗笠6阶</t>
   </si>
   <si>
     <t>106,4007</t>
@@ -131,7 +131,7 @@
     <t>1,64</t>
   </si>
   <si>
-    <t>斗笠七阶</t>
+    <t>斗笠7阶</t>
   </si>
   <si>
     <t>107,4007</t>
@@ -140,7 +140,7 @@
     <t>1,128</t>
   </si>
   <si>
-    <t>斗笠八阶</t>
+    <t>斗笠8阶</t>
   </si>
   <si>
     <t>108,4007</t>
@@ -149,7 +149,7 @@
     <t>1,256</t>
   </si>
   <si>
-    <t>斗笠九阶</t>
+    <t>斗笠9阶</t>
   </si>
   <si>
     <t>109,4007</t>
@@ -158,7 +158,7 @@
     <t>1,512</t>
   </si>
   <si>
-    <t>斗笠十阶</t>
+    <t>斗笠10阶</t>
   </si>
   <si>
     <t>110,4007</t>
@@ -167,7 +167,7 @@
     <t>1,1024</t>
   </si>
   <si>
-    <t>斗笠十一阶</t>
+    <t>斗笠11阶</t>
   </si>
   <si>
     <t>111,4007</t>
@@ -176,7 +176,7 @@
     <t>1,2048</t>
   </si>
   <si>
-    <t>斗笠十二阶</t>
+    <t>斗笠12阶</t>
   </si>
   <si>
     <t>112,4007</t>
@@ -185,7 +185,7 @@
     <t>1,4096</t>
   </si>
   <si>
-    <t>斗笠十三阶</t>
+    <t>斗笠13阶</t>
   </si>
   <si>
     <t>113,4007</t>
@@ -194,7 +194,7 @@
     <t>1,8192</t>
   </si>
   <si>
-    <t>斗笠十四阶</t>
+    <t>斗笠14阶</t>
   </si>
   <si>
     <t>114,4007</t>
@@ -203,7 +203,7 @@
     <t>1,16384</t>
   </si>
   <si>
-    <t>斗笠十五阶</t>
+    <t>斗笠15阶</t>
   </si>
   <si>
     <t>115,4007</t>
@@ -212,7 +212,7 @@
     <t>1,32768</t>
   </si>
   <si>
-    <t>斗笠十六阶</t>
+    <t>斗笠16阶</t>
   </si>
   <si>
     <t>116,4007</t>
@@ -221,7 +221,7 @@
     <t>1,65536</t>
   </si>
   <si>
-    <t>斗笠十七阶</t>
+    <t>斗笠17阶</t>
   </si>
   <si>
     <t>117,4007</t>
@@ -230,7 +230,7 @@
     <t>1,131072</t>
   </si>
   <si>
-    <t>斗笠十八阶</t>
+    <t>斗笠18阶</t>
   </si>
   <si>
     <t>118,4007</t>
@@ -239,7 +239,7 @@
     <t>1,262144</t>
   </si>
   <si>
-    <t>斗笠十九阶</t>
+    <t>斗笠19阶</t>
   </si>
   <si>
     <t>119,4007</t>
@@ -248,7 +248,7 @@
     <t>1,524288</t>
   </si>
   <si>
-    <t>斗笠二十阶</t>
+    <t>斗笠20阶</t>
   </si>
   <si>
     <t>120,4007</t>
@@ -257,7 +257,7 @@
     <t>1,1048576</t>
   </si>
   <si>
-    <t>斗笠二一阶</t>
+    <t>斗笠21阶</t>
   </si>
   <si>
     <t>121,4007</t>
@@ -266,7 +266,7 @@
     <t>1,2100000</t>
   </si>
   <si>
-    <t>斗笠二二阶</t>
+    <t>斗笠22阶</t>
   </si>
   <si>
     <t>122,4007</t>
@@ -275,7 +275,7 @@
     <t>1,4200000</t>
   </si>
   <si>
-    <t>斗笠二三阶</t>
+    <t>斗笠23阶</t>
   </si>
   <si>
     <t>123,4007</t>
@@ -284,7 +284,7 @@
     <t>1,8400000</t>
   </si>
   <si>
-    <t>斗笠二四阶</t>
+    <t>斗笠24阶</t>
   </si>
   <si>
     <t>124,4007</t>
@@ -293,7 +293,7 @@
     <t>1,16800000</t>
   </si>
   <si>
-    <t>斗笠二五阶</t>
+    <t>斗笠25阶</t>
   </si>
   <si>
     <t>125,4007</t>
@@ -302,7 +302,7 @@
     <t>1,33600000</t>
   </si>
   <si>
-    <t>斗笠二六阶</t>
+    <t>斗笠26阶</t>
   </si>
   <si>
     <t>126,4007</t>
@@ -311,7 +311,7 @@
     <t>1,67200000</t>
   </si>
   <si>
-    <t>斗笠二七阶</t>
+    <t>斗笠27阶</t>
   </si>
   <si>
     <t>127,4007</t>
@@ -320,7 +320,7 @@
     <t>1,134400000</t>
   </si>
   <si>
-    <t>斗笠二八阶</t>
+    <t>斗笠28阶</t>
   </si>
   <si>
     <t>128,4007</t>
@@ -329,7 +329,7 @@
     <t>1,268800000</t>
   </si>
   <si>
-    <t>斗笠二九阶</t>
+    <t>斗笠29阶</t>
   </si>
   <si>
     <t>129,4007</t>
@@ -338,646 +338,700 @@
     <t>1,537600000</t>
   </si>
   <si>
-    <t>斗笠三十阶</t>
+    <t>斗笠30阶</t>
+  </si>
+  <si>
+    <t>130,4007</t>
+  </si>
+  <si>
+    <t>1,7500000000</t>
+  </si>
+  <si>
+    <t>斗笠31阶</t>
+  </si>
+  <si>
+    <t>131,4007</t>
+  </si>
+  <si>
+    <t>1,1000000000</t>
+  </si>
+  <si>
+    <t>斗笠32阶</t>
+  </si>
+  <si>
+    <t>132,4007</t>
+  </si>
+  <si>
+    <t>1,12000000000</t>
+  </si>
+  <si>
+    <t>斗笠33阶</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>201,4007</t>
+  </si>
+  <si>
+    <t>护盾2阶</t>
+  </si>
+  <si>
+    <t>202,4007</t>
+  </si>
+  <si>
+    <t>护盾3阶</t>
+  </si>
+  <si>
+    <t>203,4007</t>
+  </si>
+  <si>
+    <t>护盾4阶</t>
+  </si>
+  <si>
+    <t>204,4007</t>
+  </si>
+  <si>
+    <t>护盾5阶</t>
+  </si>
+  <si>
+    <t>205,4007</t>
+  </si>
+  <si>
+    <t>护盾6阶</t>
+  </si>
+  <si>
+    <t>206,4007</t>
+  </si>
+  <si>
+    <t>护盾7阶</t>
+  </si>
+  <si>
+    <t>207,4007</t>
+  </si>
+  <si>
+    <t>护盾8阶</t>
+  </si>
+  <si>
+    <t>208,4007</t>
+  </si>
+  <si>
+    <t>护盾9阶</t>
+  </si>
+  <si>
+    <t>209,4007</t>
+  </si>
+  <si>
+    <t>护盾10阶</t>
+  </si>
+  <si>
+    <t>210,4007</t>
+  </si>
+  <si>
+    <t>护盾11阶</t>
+  </si>
+  <si>
+    <t>211,4007</t>
+  </si>
+  <si>
+    <t>护盾12阶</t>
+  </si>
+  <si>
+    <t>212,4007</t>
+  </si>
+  <si>
+    <t>护盾13阶</t>
+  </si>
+  <si>
+    <t>213,4007</t>
+  </si>
+  <si>
+    <t>护盾14阶</t>
+  </si>
+  <si>
+    <t>214,4007</t>
+  </si>
+  <si>
+    <t>护盾15阶</t>
+  </si>
+  <si>
+    <t>215,4007</t>
+  </si>
+  <si>
+    <t>护盾16阶</t>
+  </si>
+  <si>
+    <t>216,4007</t>
+  </si>
+  <si>
+    <t>护盾17阶</t>
+  </si>
+  <si>
+    <t>217,4007</t>
+  </si>
+  <si>
+    <t>护盾18阶</t>
+  </si>
+  <si>
+    <t>218,4007</t>
+  </si>
+  <si>
+    <t>护盾19阶</t>
+  </si>
+  <si>
+    <t>219,4007</t>
+  </si>
+  <si>
+    <t>护盾20阶</t>
+  </si>
+  <si>
+    <t>220,4007</t>
+  </si>
+  <si>
+    <t>护盾21阶</t>
+  </si>
+  <si>
+    <t>221,4007</t>
+  </si>
+  <si>
+    <t>护盾22阶</t>
+  </si>
+  <si>
+    <t>222,4007</t>
+  </si>
+  <si>
+    <t>护盾23阶</t>
+  </si>
+  <si>
+    <t>223,4007</t>
+  </si>
+  <si>
+    <t>护盾24阶</t>
+  </si>
+  <si>
+    <t>224,4007</t>
+  </si>
+  <si>
+    <t>护盾25阶</t>
+  </si>
+  <si>
+    <t>225,4007</t>
+  </si>
+  <si>
+    <t>护盾26阶</t>
+  </si>
+  <si>
+    <t>226,4007</t>
+  </si>
+  <si>
+    <t>护盾27阶</t>
+  </si>
+  <si>
+    <t>227,4007</t>
+  </si>
+  <si>
+    <t>护盾28阶</t>
+  </si>
+  <si>
+    <t>228,4007</t>
+  </si>
+  <si>
+    <t>护盾29阶</t>
+  </si>
+  <si>
+    <t>229,4007</t>
+  </si>
+  <si>
+    <t>护盾30阶</t>
+  </si>
+  <si>
+    <t>230,4007</t>
+  </si>
+  <si>
+    <t>护盾31阶</t>
+  </si>
+  <si>
+    <t>231,4007</t>
+  </si>
+  <si>
+    <t>护盾32阶</t>
+  </si>
+  <si>
+    <t>232,4007</t>
+  </si>
+  <si>
+    <t>护盾33阶</t>
+  </si>
+  <si>
+    <t>神符</t>
+  </si>
+  <si>
+    <t>301,4007</t>
+  </si>
+  <si>
+    <t>神符2阶</t>
+  </si>
+  <si>
+    <t>302,4007</t>
+  </si>
+  <si>
+    <t>神符3阶</t>
+  </si>
+  <si>
+    <t>303,4007</t>
+  </si>
+  <si>
+    <t>神符4阶</t>
+  </si>
+  <si>
+    <t>304,4007</t>
+  </si>
+  <si>
+    <t>神符5阶</t>
+  </si>
+  <si>
+    <t>305,4007</t>
+  </si>
+  <si>
+    <t>神符6阶</t>
+  </si>
+  <si>
+    <t>306,4007</t>
+  </si>
+  <si>
+    <t>神符7阶</t>
+  </si>
+  <si>
+    <t>307,4007</t>
+  </si>
+  <si>
+    <t>神符8阶</t>
+  </si>
+  <si>
+    <t>308,4007</t>
+  </si>
+  <si>
+    <t>神符9阶</t>
+  </si>
+  <si>
+    <t>309,4007</t>
+  </si>
+  <si>
+    <t>神符10阶</t>
+  </si>
+  <si>
+    <t>310,4007</t>
+  </si>
+  <si>
+    <t>神符11阶</t>
+  </si>
+  <si>
+    <t>311,4007</t>
+  </si>
+  <si>
+    <t>神符12阶</t>
+  </si>
+  <si>
+    <t>312,4007</t>
+  </si>
+  <si>
+    <t>神符13阶</t>
+  </si>
+  <si>
+    <t>313,4007</t>
+  </si>
+  <si>
+    <t>神符14阶</t>
+  </si>
+  <si>
+    <t>314,4007</t>
+  </si>
+  <si>
+    <t>神符15阶</t>
+  </si>
+  <si>
+    <t>315,4007</t>
+  </si>
+  <si>
+    <t>神符16阶</t>
+  </si>
+  <si>
+    <t>316,4007</t>
+  </si>
+  <si>
+    <t>神符17阶</t>
+  </si>
+  <si>
+    <t>317,4007</t>
+  </si>
+  <si>
+    <t>神符18阶</t>
+  </si>
+  <si>
+    <t>318,4007</t>
+  </si>
+  <si>
+    <t>神符19阶</t>
+  </si>
+  <si>
+    <t>319,4007</t>
+  </si>
+  <si>
+    <t>神符20阶</t>
+  </si>
+  <si>
+    <t>320,4007</t>
+  </si>
+  <si>
+    <t>神符21阶</t>
+  </si>
+  <si>
+    <t>321,4007</t>
+  </si>
+  <si>
+    <t>神符22阶</t>
+  </si>
+  <si>
+    <t>322,4007</t>
+  </si>
+  <si>
+    <t>神符23阶</t>
+  </si>
+  <si>
+    <t>323,4007</t>
+  </si>
+  <si>
+    <t>神符24阶</t>
+  </si>
+  <si>
+    <t>324,4007</t>
+  </si>
+  <si>
+    <t>神符25阶</t>
+  </si>
+  <si>
+    <t>325,4007</t>
+  </si>
+  <si>
+    <t>神符26阶</t>
+  </si>
+  <si>
+    <t>326,4007</t>
+  </si>
+  <si>
+    <t>神符27阶</t>
+  </si>
+  <si>
+    <t>327,4007</t>
+  </si>
+  <si>
+    <t>神符28阶</t>
+  </si>
+  <si>
+    <t>328,4007</t>
+  </si>
+  <si>
+    <t>神符29阶</t>
+  </si>
+  <si>
+    <t>329,4007</t>
+  </si>
+  <si>
+    <t>神符30阶</t>
+  </si>
+  <si>
+    <t>330,4007</t>
+  </si>
+  <si>
+    <t>神符31阶</t>
+  </si>
+  <si>
+    <t>331,4007</t>
+  </si>
+  <si>
+    <t>神符32阶</t>
+  </si>
+  <si>
+    <t>332,4007</t>
+  </si>
+  <si>
+    <t>神符33阶</t>
+  </si>
+  <si>
+    <t>魔石</t>
+  </si>
+  <si>
+    <t>401,4007</t>
+  </si>
+  <si>
+    <t>魔石2阶</t>
+  </si>
+  <si>
+    <t>402,4007</t>
+  </si>
+  <si>
+    <t>魔石3阶</t>
+  </si>
+  <si>
+    <t>403,4007</t>
+  </si>
+  <si>
+    <t>魔石4阶</t>
+  </si>
+  <si>
+    <t>404,4007</t>
+  </si>
+  <si>
+    <t>魔石5阶</t>
+  </si>
+  <si>
+    <t>405,4007</t>
+  </si>
+  <si>
+    <t>魔石6阶</t>
+  </si>
+  <si>
+    <t>406,4007</t>
+  </si>
+  <si>
+    <t>魔石7阶</t>
+  </si>
+  <si>
+    <t>407,4007</t>
+  </si>
+  <si>
+    <t>魔石8阶</t>
+  </si>
+  <si>
+    <t>408,4007</t>
+  </si>
+  <si>
+    <t>魔石9阶</t>
+  </si>
+  <si>
+    <t>409,4007</t>
+  </si>
+  <si>
+    <t>魔石10阶</t>
+  </si>
+  <si>
+    <t>410,4007</t>
+  </si>
+  <si>
+    <t>魔石11阶</t>
+  </si>
+  <si>
+    <t>411,4007</t>
+  </si>
+  <si>
+    <t>魔石12阶</t>
+  </si>
+  <si>
+    <t>412,4007</t>
+  </si>
+  <si>
+    <t>魔石13阶</t>
+  </si>
+  <si>
+    <t>413,4007</t>
+  </si>
+  <si>
+    <t>魔石14阶</t>
+  </si>
+  <si>
+    <t>414,4007</t>
+  </si>
+  <si>
+    <t>魔石15阶</t>
+  </si>
+  <si>
+    <t>415,4007</t>
+  </si>
+  <si>
+    <t>魔石16阶</t>
+  </si>
+  <si>
+    <t>416,4007</t>
+  </si>
+  <si>
+    <t>魔石17阶</t>
+  </si>
+  <si>
+    <t>417,4007</t>
+  </si>
+  <si>
+    <t>魔石18阶</t>
+  </si>
+  <si>
+    <t>418,4007</t>
+  </si>
+  <si>
+    <t>魔石19阶</t>
+  </si>
+  <si>
+    <t>419,4007</t>
+  </si>
+  <si>
+    <t>魔石20阶</t>
+  </si>
+  <si>
+    <t>420,4007</t>
+  </si>
+  <si>
+    <t>魔石21阶</t>
+  </si>
+  <si>
+    <t>421,4007</t>
+  </si>
+  <si>
+    <t>魔石22阶</t>
+  </si>
+  <si>
+    <t>422,4007</t>
+  </si>
+  <si>
+    <t>魔石23阶</t>
+  </si>
+  <si>
+    <t>423,4007</t>
+  </si>
+  <si>
+    <t>魔石24阶</t>
+  </si>
+  <si>
+    <t>424,4007</t>
+  </si>
+  <si>
+    <t>魔石25阶</t>
+  </si>
+  <si>
+    <t>425,4007</t>
+  </si>
+  <si>
+    <t>魔石26阶</t>
+  </si>
+  <si>
+    <t>426,4007</t>
+  </si>
+  <si>
+    <t>魔石27阶</t>
+  </si>
+  <si>
+    <t>427,4007</t>
+  </si>
+  <si>
+    <t>魔石28阶</t>
+  </si>
+  <si>
+    <t>428,4007</t>
+  </si>
+  <si>
+    <t>魔石29阶</t>
+  </si>
+  <si>
+    <t>429,4007</t>
+  </si>
+  <si>
+    <t>魔石30阶</t>
+  </si>
+  <si>
+    <t>430,4007</t>
+  </si>
+  <si>
+    <t>魔石31阶</t>
+  </si>
+  <si>
+    <t>431,4007</t>
+  </si>
+  <si>
+    <t>魔石32阶</t>
+  </si>
+  <si>
+    <t>432,4007</t>
+  </si>
+  <si>
+    <t>魔石33阶</t>
+  </si>
+  <si>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>4015,4201</t>
+  </si>
+  <si>
+    <t>5,10</t>
+  </si>
+  <si>
+    <t>红装精华</t>
+  </si>
+  <si>
+    <t>4011,4201</t>
+  </si>
+  <si>
+    <t>10,50000</t>
+  </si>
+  <si>
+    <t>金装精华</t>
+  </si>
+  <si>
+    <t>4023,4111</t>
+  </si>
+  <si>
+    <t>6,20000</t>
+  </si>
+  <si>
+    <t>红色魂心</t>
+  </si>
+  <si>
+    <t>4024,4111</t>
+  </si>
+  <si>
+    <t>6,100000</t>
+  </si>
+  <si>
+    <t>金色魂心</t>
+  </si>
+  <si>
+    <t>4028,4111</t>
+  </si>
+  <si>
+    <t>40,100000</t>
+  </si>
+  <si>
+    <t>青龙神器</t>
+  </si>
+  <si>
+    <t>4029,4111</t>
+  </si>
+  <si>
+    <t>白虎神器</t>
+  </si>
+  <si>
+    <t>4030,4111</t>
+  </si>
+  <si>
+    <t>朱雀神器</t>
+  </si>
+  <si>
+    <t>4031,4111</t>
+  </si>
+  <si>
+    <t>玄武神器</t>
+  </si>
+  <si>
+    <t>4005,4111</t>
+  </si>
+  <si>
+    <t>20000,1000</t>
+  </si>
+  <si>
+    <t>传奇精华</t>
   </si>
   <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>130,4007</t>
-  </si>
-  <si>
-    <t>1,1075200000</t>
-  </si>
-  <si>
-    <t>斗笠三一阶</t>
-  </si>
-  <si>
-    <t>护盾</t>
-  </si>
-  <si>
-    <t>201,4007</t>
-  </si>
-  <si>
-    <t>护盾二阶</t>
-  </si>
-  <si>
-    <t>202,4007</t>
-  </si>
-  <si>
-    <t>护盾三阶</t>
-  </si>
-  <si>
-    <t>203,4007</t>
-  </si>
-  <si>
-    <t>护盾四阶</t>
-  </si>
-  <si>
-    <t>204,4007</t>
-  </si>
-  <si>
-    <t>护盾五阶</t>
-  </si>
-  <si>
-    <t>205,4007</t>
-  </si>
-  <si>
-    <t>护盾六阶</t>
-  </si>
-  <si>
-    <t>206,4007</t>
-  </si>
-  <si>
-    <t>护盾七阶</t>
-  </si>
-  <si>
-    <t>207,4007</t>
-  </si>
-  <si>
-    <t>护盾八阶</t>
-  </si>
-  <si>
-    <t>208,4007</t>
-  </si>
-  <si>
-    <t>护盾九阶</t>
-  </si>
-  <si>
-    <t>209,4007</t>
-  </si>
-  <si>
-    <t>护盾十阶</t>
-  </si>
-  <si>
-    <t>210,4007</t>
-  </si>
-  <si>
-    <t>护盾十一阶</t>
-  </si>
-  <si>
-    <t>211,4007</t>
-  </si>
-  <si>
-    <t>护盾十二阶</t>
-  </si>
-  <si>
-    <t>212,4007</t>
-  </si>
-  <si>
-    <t>护盾十三阶</t>
-  </si>
-  <si>
-    <t>213,4007</t>
-  </si>
-  <si>
-    <t>护盾十四阶</t>
-  </si>
-  <si>
-    <t>214,4007</t>
-  </si>
-  <si>
-    <t>护盾十五阶</t>
-  </si>
-  <si>
-    <t>215,4007</t>
-  </si>
-  <si>
-    <t>护盾十六阶</t>
-  </si>
-  <si>
-    <t>216,4007</t>
-  </si>
-  <si>
-    <t>护盾十七阶</t>
-  </si>
-  <si>
-    <t>217,4007</t>
-  </si>
-  <si>
-    <t>护盾十八阶</t>
-  </si>
-  <si>
-    <t>218,4007</t>
-  </si>
-  <si>
-    <t>护盾十九阶</t>
-  </si>
-  <si>
-    <t>219,4007</t>
-  </si>
-  <si>
-    <t>护盾二十阶</t>
-  </si>
-  <si>
-    <t>220,4007</t>
-  </si>
-  <si>
-    <t>护盾二一阶</t>
-  </si>
-  <si>
-    <t>221,4007</t>
-  </si>
-  <si>
-    <t>护盾二二阶</t>
-  </si>
-  <si>
-    <t>222,4007</t>
-  </si>
-  <si>
-    <t>护盾二三阶</t>
-  </si>
-  <si>
-    <t>223,4007</t>
-  </si>
-  <si>
-    <t>护盾二四阶</t>
-  </si>
-  <si>
-    <t>224,4007</t>
-  </si>
-  <si>
-    <t>护盾二五阶</t>
-  </si>
-  <si>
-    <t>225,4007</t>
-  </si>
-  <si>
-    <t>护盾二六阶</t>
-  </si>
-  <si>
-    <t>226,4007</t>
-  </si>
-  <si>
-    <t>护盾二七阶</t>
-  </si>
-  <si>
-    <t>227,4007</t>
-  </si>
-  <si>
-    <t>护盾二八阶</t>
-  </si>
-  <si>
-    <t>228,4007</t>
-  </si>
-  <si>
-    <t>护盾二九阶</t>
-  </si>
-  <si>
-    <t>229,4007</t>
-  </si>
-  <si>
-    <t>护盾三十阶</t>
-  </si>
-  <si>
-    <t>230,4007</t>
-  </si>
-  <si>
-    <t>护盾三一阶</t>
-  </si>
-  <si>
-    <t>神符</t>
-  </si>
-  <si>
-    <t>301,4007</t>
-  </si>
-  <si>
-    <t>神符二阶</t>
-  </si>
-  <si>
-    <t>302,4007</t>
-  </si>
-  <si>
-    <t>神符三阶</t>
-  </si>
-  <si>
-    <t>303,4007</t>
-  </si>
-  <si>
-    <t>神符四阶</t>
-  </si>
-  <si>
-    <t>304,4007</t>
-  </si>
-  <si>
-    <t>神符五阶</t>
-  </si>
-  <si>
-    <t>305,4007</t>
-  </si>
-  <si>
-    <t>神符六阶</t>
-  </si>
-  <si>
-    <t>306,4007</t>
-  </si>
-  <si>
-    <t>神符七阶</t>
-  </si>
-  <si>
-    <t>307,4007</t>
-  </si>
-  <si>
-    <t>神符八阶</t>
-  </si>
-  <si>
-    <t>308,4007</t>
-  </si>
-  <si>
-    <t>神符九阶</t>
-  </si>
-  <si>
-    <t>309,4007</t>
-  </si>
-  <si>
-    <t>神符十阶</t>
-  </si>
-  <si>
-    <t>310,4007</t>
-  </si>
-  <si>
-    <t>神符十一阶</t>
-  </si>
-  <si>
-    <t>311,4007</t>
-  </si>
-  <si>
-    <t>神符十二阶</t>
-  </si>
-  <si>
-    <t>312,4007</t>
-  </si>
-  <si>
-    <t>神符十三阶</t>
-  </si>
-  <si>
-    <t>313,4007</t>
-  </si>
-  <si>
-    <t>神符十四阶</t>
-  </si>
-  <si>
-    <t>314,4007</t>
-  </si>
-  <si>
-    <t>神符十五阶</t>
-  </si>
-  <si>
-    <t>315,4007</t>
-  </si>
-  <si>
-    <t>神符十六阶</t>
-  </si>
-  <si>
-    <t>316,4007</t>
-  </si>
-  <si>
-    <t>神符十七阶</t>
-  </si>
-  <si>
-    <t>317,4007</t>
-  </si>
-  <si>
-    <t>神符十八阶</t>
-  </si>
-  <si>
-    <t>318,4007</t>
-  </si>
-  <si>
-    <t>神符十九阶</t>
-  </si>
-  <si>
-    <t>319,4007</t>
-  </si>
-  <si>
-    <t>神符二十阶</t>
-  </si>
-  <si>
-    <t>320,4007</t>
-  </si>
-  <si>
-    <t>神符二一阶</t>
-  </si>
-  <si>
-    <t>321,4007</t>
-  </si>
-  <si>
-    <t>神符二二阶</t>
-  </si>
-  <si>
-    <t>322,4007</t>
-  </si>
-  <si>
-    <t>神符二三阶</t>
-  </si>
-  <si>
-    <t>323,4007</t>
-  </si>
-  <si>
-    <t>神符二四阶</t>
-  </si>
-  <si>
-    <t>324,4007</t>
-  </si>
-  <si>
-    <t>神符二五阶</t>
-  </si>
-  <si>
-    <t>325,4007</t>
-  </si>
-  <si>
-    <t>神符二六阶</t>
-  </si>
-  <si>
-    <t>326,4007</t>
-  </si>
-  <si>
-    <t>神符二七阶</t>
-  </si>
-  <si>
-    <t>327,4007</t>
-  </si>
-  <si>
-    <t>神符二八阶</t>
-  </si>
-  <si>
-    <t>328,4007</t>
-  </si>
-  <si>
-    <t>神符二九阶</t>
-  </si>
-  <si>
-    <t>329,4007</t>
-  </si>
-  <si>
-    <t>神符三十阶</t>
-  </si>
-  <si>
-    <t>330,4007</t>
-  </si>
-  <si>
-    <t>神符三一阶</t>
-  </si>
-  <si>
-    <t>魔石</t>
-  </si>
-  <si>
-    <t>401,4007</t>
-  </si>
-  <si>
-    <t>魔石二阶</t>
-  </si>
-  <si>
-    <t>402,4007</t>
-  </si>
-  <si>
-    <t>魔石三阶</t>
-  </si>
-  <si>
-    <t>403,4007</t>
-  </si>
-  <si>
-    <t>魔石四阶</t>
-  </si>
-  <si>
-    <t>404,4007</t>
-  </si>
-  <si>
-    <t>魔石五阶</t>
-  </si>
-  <si>
-    <t>405,4007</t>
-  </si>
-  <si>
-    <t>魔石六阶</t>
-  </si>
-  <si>
-    <t>406,4007</t>
-  </si>
-  <si>
-    <t>魔石七阶</t>
-  </si>
-  <si>
-    <t>407,4007</t>
-  </si>
-  <si>
-    <t>魔石八阶</t>
-  </si>
-  <si>
-    <t>408,4007</t>
-  </si>
-  <si>
-    <t>魔石九阶</t>
-  </si>
-  <si>
-    <t>409,4007</t>
-  </si>
-  <si>
-    <t>魔石十阶</t>
-  </si>
-  <si>
-    <t>410,4007</t>
-  </si>
-  <si>
-    <t>魔石十一阶</t>
-  </si>
-  <si>
-    <t>411,4007</t>
-  </si>
-  <si>
-    <t>魔石十二阶</t>
-  </si>
-  <si>
-    <t>412,4007</t>
-  </si>
-  <si>
-    <t>魔石十三阶</t>
-  </si>
-  <si>
-    <t>413,4007</t>
-  </si>
-  <si>
-    <t>魔石十四阶</t>
-  </si>
-  <si>
-    <t>414,4007</t>
-  </si>
-  <si>
-    <t>魔石十五阶</t>
-  </si>
-  <si>
-    <t>415,4007</t>
-  </si>
-  <si>
-    <t>魔石十六阶</t>
-  </si>
-  <si>
-    <t>416,4007</t>
-  </si>
-  <si>
-    <t>魔石十七阶</t>
-  </si>
-  <si>
-    <t>417,4007</t>
-  </si>
-  <si>
-    <t>魔石十八阶</t>
-  </si>
-  <si>
-    <t>418,4007</t>
-  </si>
-  <si>
-    <t>魔石十九阶</t>
-  </si>
-  <si>
-    <t>419,4007</t>
-  </si>
-  <si>
-    <t>魔石二十阶</t>
-  </si>
-  <si>
-    <t>420,4007</t>
-  </si>
-  <si>
-    <t>魔石二一阶</t>
-  </si>
-  <si>
-    <t>421,4007</t>
-  </si>
-  <si>
-    <t>魔石二二阶</t>
-  </si>
-  <si>
-    <t>422,4007</t>
-  </si>
-  <si>
-    <t>魔石二三阶</t>
-  </si>
-  <si>
-    <t>423,4007</t>
-  </si>
-  <si>
-    <t>魔石二四阶</t>
-  </si>
-  <si>
-    <t>424,4007</t>
-  </si>
-  <si>
-    <t>魔石二五阶</t>
-  </si>
-  <si>
-    <t>425,4007</t>
-  </si>
-  <si>
-    <t>魔石二六阶</t>
-  </si>
-  <si>
-    <t>426,4007</t>
-  </si>
-  <si>
-    <t>魔石二七阶</t>
-  </si>
-  <si>
-    <t>427,4007</t>
-  </si>
-  <si>
-    <t>魔石二八阶</t>
-  </si>
-  <si>
-    <t>428,4007</t>
-  </si>
-  <si>
-    <t>魔石二九阶</t>
-  </si>
-  <si>
-    <t>429,4007</t>
-  </si>
-  <si>
-    <t>魔石三十阶</t>
-  </si>
-  <si>
-    <t>430,4007</t>
-  </si>
-  <si>
-    <t>魔石三一阶</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>5,5</t>
-  </si>
-  <si>
-    <t>4015,4201</t>
-  </si>
-  <si>
-    <t>5,10</t>
-  </si>
-  <si>
-    <t>红装精华</t>
-  </si>
-  <si>
-    <t>4011,4201</t>
-  </si>
-  <si>
-    <t>10,50000</t>
-  </si>
-  <si>
-    <t>金装精华</t>
-  </si>
-  <si>
-    <t>4023,4111</t>
-  </si>
-  <si>
-    <t>6,20000</t>
-  </si>
-  <si>
-    <t>红色魂心</t>
-  </si>
-  <si>
-    <t>4024,4111</t>
-  </si>
-  <si>
-    <t>6,100000</t>
-  </si>
-  <si>
-    <t>金色魂心</t>
-  </si>
-  <si>
-    <t>4028,4111</t>
-  </si>
-  <si>
-    <t>40,100000</t>
-  </si>
-  <si>
-    <t>青龙神器</t>
-  </si>
-  <si>
-    <t>4029,4111</t>
-  </si>
-  <si>
-    <t>白虎神器</t>
-  </si>
-  <si>
-    <t>4030,4111</t>
-  </si>
-  <si>
-    <t>朱雀神器</t>
-  </si>
-  <si>
-    <t>4031,4111</t>
-  </si>
-  <si>
-    <t>玄武神器</t>
-  </si>
-  <si>
-    <t>4005,4111</t>
-  </si>
-  <si>
-    <t>20000,1000</t>
-  </si>
-  <si>
-    <t>传奇精华</t>
   </si>
   <si>
     <t>30000,1000</t>
@@ -1994,7 +2048,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L151"/>
+  <dimension ref="A3:L157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3032,13 +3086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" customHeight="1" spans="1:12">
-      <c r="A35" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="35" customHeight="1" spans="3:12">
       <c r="C35" s="1">
         <v>130</v>
       </c>
@@ -3049,16 +3097,16 @@
         <v>15</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="H35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="J35" s="1">
         <v>131</v>
@@ -3067,6 +3115,70 @@
         <v>2</v>
       </c>
       <c r="L35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:12">
+      <c r="C36" s="1">
+        <v>131</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J36" s="1">
+        <v>132</v>
+      </c>
+      <c r="K36" s="1">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>132</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J37" s="1">
+        <v>133</v>
+      </c>
+      <c r="K37" s="1">
+        <v>2</v>
+      </c>
+      <c r="L37" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3075,13 +3187,13 @@
         <v>201</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>17</v>
@@ -3090,7 +3202,7 @@
         <v>18</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J40" s="1">
         <v>202</v>
@@ -3107,13 +3219,13 @@
         <v>202</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>21</v>
@@ -3122,7 +3234,7 @@
         <v>18</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J41" s="1">
         <v>203</v>
@@ -3139,13 +3251,13 @@
         <v>203</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>24</v>
@@ -3154,7 +3266,7 @@
         <v>18</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J42" s="1">
         <v>204</v>
@@ -3171,13 +3283,13 @@
         <v>204</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>27</v>
@@ -3186,7 +3298,7 @@
         <v>18</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J43" s="1">
         <v>205</v>
@@ -3203,13 +3315,13 @@
         <v>205</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>30</v>
@@ -3218,7 +3330,7 @@
         <v>18</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J44" s="1">
         <v>206</v>
@@ -3235,13 +3347,13 @@
         <v>206</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>33</v>
@@ -3250,7 +3362,7 @@
         <v>18</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J45" s="1">
         <v>207</v>
@@ -3267,13 +3379,13 @@
         <v>207</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>36</v>
@@ -3282,7 +3394,7 @@
         <v>18</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J46" s="1">
         <v>208</v>
@@ -3299,13 +3411,13 @@
         <v>208</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>39</v>
@@ -3314,7 +3426,7 @@
         <v>18</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J47" s="1">
         <v>209</v>
@@ -3331,13 +3443,13 @@
         <v>209</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>42</v>
@@ -3346,7 +3458,7 @@
         <v>18</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J48" s="1">
         <v>210</v>
@@ -3363,13 +3475,13 @@
         <v>210</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>45</v>
@@ -3378,7 +3490,7 @@
         <v>18</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J49" s="1">
         <v>211</v>
@@ -3395,13 +3507,13 @@
         <v>211</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>48</v>
@@ -3410,7 +3522,7 @@
         <v>18</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J50" s="1">
         <v>212</v>
@@ -3427,13 +3539,13 @@
         <v>212</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>51</v>
@@ -3442,7 +3554,7 @@
         <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J51" s="1">
         <v>213</v>
@@ -3459,13 +3571,13 @@
         <v>213</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>54</v>
@@ -3474,7 +3586,7 @@
         <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J52" s="1">
         <v>214</v>
@@ -3491,13 +3603,13 @@
         <v>214</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>57</v>
@@ -3506,7 +3618,7 @@
         <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J53" s="1">
         <v>215</v>
@@ -3523,13 +3635,13 @@
         <v>215</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>60</v>
@@ -3538,7 +3650,7 @@
         <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J54" s="1">
         <v>216</v>
@@ -3555,13 +3667,13 @@
         <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>63</v>
@@ -3570,7 +3682,7 @@
         <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J55" s="1">
         <v>217</v>
@@ -3587,13 +3699,13 @@
         <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>66</v>
@@ -3602,7 +3714,7 @@
         <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J56" s="1">
         <v>218</v>
@@ -3619,13 +3731,13 @@
         <v>218</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>69</v>
@@ -3634,7 +3746,7 @@
         <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J57" s="1">
         <v>219</v>
@@ -3651,13 +3763,13 @@
         <v>219</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>72</v>
@@ -3666,7 +3778,7 @@
         <v>18</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J58" s="1">
         <v>220</v>
@@ -3683,13 +3795,13 @@
         <v>220</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>75</v>
@@ -3698,7 +3810,7 @@
         <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J59" s="1">
         <v>221</v>
@@ -3715,13 +3827,13 @@
         <v>221</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>78</v>
@@ -3730,7 +3842,7 @@
         <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J60" s="1">
         <v>222</v>
@@ -3747,13 +3859,13 @@
         <v>222</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>81</v>
@@ -3762,7 +3874,7 @@
         <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J61" s="1">
         <v>223</v>
@@ -3779,13 +3891,13 @@
         <v>223</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>84</v>
@@ -3794,7 +3906,7 @@
         <v>18</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J62" s="1">
         <v>224</v>
@@ -3811,13 +3923,13 @@
         <v>224</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>87</v>
@@ -3826,7 +3938,7 @@
         <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J63" s="1">
         <v>225</v>
@@ -3843,13 +3955,13 @@
         <v>225</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>90</v>
@@ -3858,7 +3970,7 @@
         <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J64" s="1">
         <v>226</v>
@@ -3875,13 +3987,13 @@
         <v>226</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>93</v>
@@ -3890,7 +4002,7 @@
         <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J65" s="1">
         <v>227</v>
@@ -3907,13 +4019,13 @@
         <v>227</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>96</v>
@@ -3922,7 +4034,7 @@
         <v>18</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J66" s="1">
         <v>228</v>
@@ -3939,13 +4051,13 @@
         <v>228</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>99</v>
@@ -3954,7 +4066,7 @@
         <v>18</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J67" s="1">
         <v>229</v>
@@ -3971,13 +4083,13 @@
         <v>229</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>102</v>
@@ -3986,7 +4098,7 @@
         <v>18</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J68" s="1">
         <v>230</v>
@@ -3998,33 +4110,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" customHeight="1" spans="1:12">
-      <c r="A69" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="69" customHeight="1" spans="3:12">
       <c r="C69" s="1">
         <v>230</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H69" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J69" s="1">
         <v>231</v>
@@ -4036,158 +4142,126 @@
         <v>1</v>
       </c>
     </row>
+    <row r="70" customHeight="1" spans="3:12">
+      <c r="C70" s="1">
+        <v>231</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G70" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J70" s="1">
+        <v>232</v>
+      </c>
+      <c r="K70" s="1">
+        <v>2</v>
+      </c>
+      <c r="L70" s="1">
+        <v>1</v>
+      </c>
+    </row>
     <row r="71" customHeight="1" spans="3:12">
       <c r="C71" s="1">
-        <v>301</v>
+        <v>232</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>17</v>
+        <v>111</v>
       </c>
       <c r="H71" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J71" s="1">
-        <v>302</v>
+        <v>233</v>
       </c>
       <c r="K71" s="1">
         <v>2</v>
       </c>
       <c r="L71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" customHeight="1" spans="3:12">
-      <c r="C72" s="1">
-        <v>302</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E72" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="J72" s="1">
-        <v>303</v>
-      </c>
-      <c r="K72" s="1">
-        <v>2</v>
-      </c>
-      <c r="L72" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:12">
-      <c r="C73" s="1">
-        <v>303</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I73" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="J73" s="1">
-        <v>304</v>
-      </c>
-      <c r="K73" s="1">
-        <v>2</v>
-      </c>
-      <c r="L73" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="1">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="H74" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J74" s="1">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="K74" s="1">
         <v>2</v>
       </c>
       <c r="L74" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H75" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J75" s="1">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="K75" s="1">
         <v>2</v>
@@ -4198,28 +4272,28 @@
     </row>
     <row r="76" customHeight="1" spans="3:12">
       <c r="C76" s="1">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="H76" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J76" s="1">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K76" s="1">
         <v>2</v>
@@ -4230,28 +4304,28 @@
     </row>
     <row r="77" customHeight="1" spans="3:12">
       <c r="C77" s="1">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="H77" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J77" s="1">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="K77" s="1">
         <v>2</v>
@@ -4262,28 +4336,28 @@
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="H78" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J78" s="1">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K78" s="1">
         <v>2</v>
@@ -4294,28 +4368,28 @@
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H79" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J79" s="1">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K79" s="1">
         <v>2</v>
@@ -4326,28 +4400,28 @@
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J80" s="1">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K80" s="1">
         <v>2</v>
@@ -4358,28 +4432,28 @@
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="J81" s="1">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K81" s="1">
         <v>2</v>
@@ -4390,28 +4464,28 @@
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H82" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="J82" s="1">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K82" s="1">
         <v>2</v>
@@ -4422,28 +4496,28 @@
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H83" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J83" s="1">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="K83" s="1">
         <v>2</v>
@@ -4454,28 +4528,28 @@
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="H84" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="J84" s="1">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K84" s="1">
         <v>2</v>
@@ -4486,28 +4560,28 @@
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H85" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="J85" s="1">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="K85" s="1">
         <v>2</v>
@@ -4518,28 +4592,28 @@
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H86" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J86" s="1">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K86" s="1">
         <v>2</v>
@@ -4550,28 +4624,28 @@
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="H87" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="J87" s="1">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="K87" s="1">
         <v>2</v>
@@ -4582,28 +4656,28 @@
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="H88" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="J88" s="1">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="K88" s="1">
         <v>2</v>
@@ -4614,28 +4688,28 @@
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H89" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J89" s="1">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="K89" s="1">
         <v>2</v>
@@ -4646,28 +4720,28 @@
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="H90" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="J90" s="1">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="K90" s="1">
         <v>2</v>
@@ -4678,28 +4752,28 @@
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H91" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J91" s="1">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="K91" s="1">
         <v>2</v>
@@ -4710,28 +4784,28 @@
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="H92" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J92" s="1">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="K92" s="1">
         <v>2</v>
@@ -4742,28 +4816,28 @@
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H93" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="J93" s="1">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="K93" s="1">
         <v>2</v>
@@ -4774,28 +4848,28 @@
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E94" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="H94" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="J94" s="1">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="K94" s="1">
         <v>2</v>
@@ -4806,28 +4880,28 @@
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H95" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J95" s="1">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="K95" s="1">
         <v>2</v>
@@ -4838,28 +4912,28 @@
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H96" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="J96" s="1">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="K96" s="1">
         <v>2</v>
@@ -4870,28 +4944,28 @@
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="H97" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="J97" s="1">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K97" s="1">
         <v>2</v>
@@ -4902,28 +4976,28 @@
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="H98" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J98" s="1">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="K98" s="1">
         <v>2</v>
@@ -4934,130 +5008,156 @@
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
+        <v>326</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G99" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="J99" s="1">
+        <v>327</v>
+      </c>
+      <c r="K99" s="1">
+        <v>2</v>
+      </c>
+      <c r="L99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:12">
+      <c r="C100" s="1">
+        <v>327</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="G100" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="J100" s="1">
+        <v>328</v>
+      </c>
+      <c r="K100" s="1">
+        <v>2</v>
+      </c>
+      <c r="L100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:12">
+      <c r="C101" s="1">
+        <v>328</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="G101" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="J101" s="1">
         <v>329</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E99" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="G99" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="J99" s="1">
-        <v>330</v>
-      </c>
-      <c r="K99" s="1">
-        <v>2</v>
-      </c>
-      <c r="L99" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" customHeight="1" spans="1:12">
-      <c r="A100" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C100" s="1">
-        <v>330</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E100" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="G100" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="J100" s="1">
-        <v>331</v>
-      </c>
-      <c r="K100" s="1">
-        <v>2</v>
-      </c>
-      <c r="L100" s="1">
+      <c r="K101" s="1">
+        <v>2</v>
+      </c>
+      <c r="L101" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="J102" s="1">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="K102" s="1">
         <v>2</v>
       </c>
       <c r="L102" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>21</v>
+        <v>105</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J103" s="1">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="K103" s="1">
         <v>2</v>
@@ -5068,28 +5168,28 @@
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>403</v>
+        <v>331</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E104" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="H104" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="J104" s="1">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="K104" s="1">
         <v>2</v>
@@ -5100,156 +5200,92 @@
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>404</v>
+        <v>332</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="H105" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="J105" s="1">
-        <v>405</v>
+        <v>333</v>
       </c>
       <c r="K105" s="1">
         <v>2</v>
       </c>
       <c r="L105" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="106" customHeight="1" spans="3:12">
-      <c r="C106" s="1">
-        <v>405</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E106" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I106" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="J106" s="1">
-        <v>406</v>
-      </c>
-      <c r="K106" s="1">
-        <v>2</v>
-      </c>
-      <c r="L106" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="107" customHeight="1" spans="3:12">
-      <c r="C107" s="1">
-        <v>406</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E107" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G107" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I107" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="J107" s="1">
-        <v>407</v>
-      </c>
-      <c r="K107" s="1">
-        <v>2</v>
-      </c>
-      <c r="L107" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H108" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="J108" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="K108" s="1">
         <v>2</v>
       </c>
       <c r="L108" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H109" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J109" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="K109" s="1">
         <v>2</v>
@@ -5260,28 +5296,28 @@
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H110" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="J110" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="K110" s="1">
         <v>2</v>
@@ -5292,28 +5328,28 @@
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E111" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H111" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J111" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K111" s="1">
         <v>2</v>
@@ -5324,28 +5360,28 @@
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E112" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H112" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J112" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="K112" s="1">
         <v>2</v>
@@ -5356,28 +5392,28 @@
     </row>
     <row r="113" customHeight="1" spans="3:12">
       <c r="C113" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E113" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H113" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J113" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="K113" s="1">
         <v>2</v>
@@ -5388,28 +5424,28 @@
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E114" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H114" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="J114" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="K114" s="1">
         <v>2</v>
@@ -5420,28 +5456,28 @@
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E115" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H115" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="J115" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="K115" s="1">
         <v>2</v>
@@ -5452,28 +5488,28 @@
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E116" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H116" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J116" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="K116" s="1">
         <v>2</v>
@@ -5484,28 +5520,28 @@
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J117" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="K117" s="1">
         <v>2</v>
@@ -5516,28 +5552,28 @@
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E118" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J118" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="K118" s="1">
         <v>2</v>
@@ -5548,28 +5584,28 @@
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E119" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H119" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J119" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="K119" s="1">
         <v>2</v>
@@ -5580,28 +5616,28 @@
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E120" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H120" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J120" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="K120" s="1">
         <v>2</v>
@@ -5612,28 +5648,28 @@
     </row>
     <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="H121" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="J121" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="K121" s="1">
         <v>2</v>
@@ -5644,28 +5680,28 @@
     </row>
     <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H122" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="J122" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K122" s="1">
         <v>2</v>
@@ -5676,28 +5712,28 @@
     </row>
     <row r="123" customHeight="1" spans="3:12">
       <c r="C123" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H123" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I123" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J123" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K123" s="1">
         <v>2</v>
@@ -5708,28 +5744,28 @@
     </row>
     <row r="124" customHeight="1" spans="3:12">
       <c r="C124" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H124" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="J124" s="1">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="K124" s="1">
         <v>2</v>
@@ -5740,28 +5776,28 @@
     </row>
     <row r="125" customHeight="1" spans="3:12">
       <c r="C125" s="1">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H125" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J125" s="1">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="K125" s="1">
         <v>2</v>
@@ -5772,28 +5808,28 @@
     </row>
     <row r="126" customHeight="1" spans="3:12">
       <c r="C126" s="1">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H126" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J126" s="1">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K126" s="1">
         <v>2</v>
@@ -5804,28 +5840,28 @@
     </row>
     <row r="127" customHeight="1" spans="3:12">
       <c r="C127" s="1">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H127" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="J127" s="1">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="K127" s="1">
         <v>2</v>
@@ -5836,28 +5872,28 @@
     </row>
     <row r="128" customHeight="1" spans="3:12">
       <c r="C128" s="1">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H128" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="J128" s="1">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="K128" s="1">
         <v>2</v>
@@ -5868,28 +5904,28 @@
     </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>15</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H129" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J129" s="1">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="K129" s="1">
         <v>2</v>
@@ -5900,293 +5936,351 @@
     </row>
     <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
+        <v>423</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E130" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G130" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H130" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J130" s="1">
+        <v>424</v>
+      </c>
+      <c r="K130" s="1">
+        <v>2</v>
+      </c>
+      <c r="L130" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:12">
+      <c r="C131" s="1">
+        <v>424</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="G131" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J131" s="1">
+        <v>425</v>
+      </c>
+      <c r="K131" s="1">
+        <v>2</v>
+      </c>
+      <c r="L131" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:12">
+      <c r="C132" s="1">
+        <v>425</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E132" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G132" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H132" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="J132" s="1">
+        <v>426</v>
+      </c>
+      <c r="K132" s="1">
+        <v>2</v>
+      </c>
+      <c r="L132" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="3:12">
+      <c r="C133" s="1">
+        <v>426</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E133" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="G133" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="J133" s="1">
+        <v>427</v>
+      </c>
+      <c r="K133" s="1">
+        <v>2</v>
+      </c>
+      <c r="L133" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="3:12">
+      <c r="C134" s="1">
+        <v>427</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F134" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G134" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H134" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J134" s="1">
+        <v>428</v>
+      </c>
+      <c r="K134" s="1">
+        <v>2</v>
+      </c>
+      <c r="L134" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="3:12">
+      <c r="C135" s="1">
+        <v>428</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E135" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="G135" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J135" s="1">
         <v>429</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E130" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="G130" s="4" t="s">
+      <c r="K135" s="1">
+        <v>2</v>
+      </c>
+      <c r="L135" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" customHeight="1" spans="3:12">
+      <c r="C136" s="1">
+        <v>429</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E136" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F136" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="G136" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="H130" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I130" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="J130" s="1">
+      <c r="H136" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I136" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="J136" s="1">
         <v>430</v>
       </c>
-      <c r="K130" s="1">
-        <v>2</v>
-      </c>
-      <c r="L130" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="1:12">
-      <c r="A131" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C131" s="1">
+      <c r="K136" s="1">
+        <v>2</v>
+      </c>
+      <c r="L136" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" customHeight="1" spans="3:12">
+      <c r="C137" s="1">
         <v>430</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="E131" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="G131" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="J131" s="1">
+      <c r="D137" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E137" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I137" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J137" s="1">
         <v>431</v>
       </c>
-      <c r="K131" s="1">
-        <v>2</v>
-      </c>
-      <c r="L131" s="1">
+      <c r="K137" s="1">
+        <v>2</v>
+      </c>
+      <c r="L137" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>501</v>
+        <v>431</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>292</v>
+        <v>15</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>294</v>
+        <v>108</v>
       </c>
       <c r="H138" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I138" s="1" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="J138" s="1">
-        <v>4011</v>
+        <v>432</v>
       </c>
       <c r="K138" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L138" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>502</v>
+        <v>432</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>291</v>
+        <v>243</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>292</v>
+        <v>15</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>297</v>
+        <v>111</v>
       </c>
       <c r="H139" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="J139" s="1">
-        <v>4019</v>
+        <v>433</v>
       </c>
       <c r="K139" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L139" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" spans="3:12">
-      <c r="C140" s="1">
-        <v>503</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E140" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F140" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I140" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="J140" s="1">
-        <v>4024</v>
-      </c>
-      <c r="K140" s="1">
-        <v>5</v>
-      </c>
-      <c r="L140" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" spans="3:12">
-      <c r="C141" s="1">
-        <v>504</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E141" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G141" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I141" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="J141" s="1">
-        <v>4025</v>
-      </c>
-      <c r="K141" s="1">
-        <v>5</v>
-      </c>
-      <c r="L141" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" spans="3:12">
-      <c r="C142" s="1">
-        <v>505</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E142" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F142" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G142" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H142" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I142" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J142" s="1">
-        <v>35</v>
-      </c>
-      <c r="K142" s="1">
-        <v>4</v>
-      </c>
-      <c r="L142" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" spans="3:12">
-      <c r="C143" s="1">
-        <v>506</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E143" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="F143" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G143" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="H143" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I143" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="J143" s="1">
-        <v>37</v>
-      </c>
-      <c r="K143" s="1">
-        <v>4</v>
-      </c>
-      <c r="L143" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F144" s="4" t="s">
         <v>310</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H144" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J144" s="1">
-        <v>38</v>
+        <v>4011</v>
       </c>
       <c r="K144" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L144" s="1">
         <v>0</v>
@@ -6194,60 +6288,92 @@
     </row>
     <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="H145" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="J145" s="1">
-        <v>39</v>
+        <v>4019</v>
       </c>
       <c r="K145" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L145" s="1">
         <v>0</v>
       </c>
     </row>
+    <row r="146" customHeight="1" spans="3:12">
+      <c r="C146" s="1">
+        <v>503</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E146" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F146" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="G146" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="J146" s="1">
+        <v>4024</v>
+      </c>
+      <c r="K146" s="1">
+        <v>5</v>
+      </c>
+      <c r="L146" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="H147" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J147" s="1">
-        <v>4035</v>
+        <v>4025</v>
       </c>
       <c r="K147" s="1">
         <v>5</v>
@@ -6256,111 +6382,271 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="1:12">
-      <c r="A148" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="H148" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="J148" s="1">
-        <v>4036</v>
+        <v>35</v>
       </c>
       <c r="K148" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="1:12">
-      <c r="A149" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B149" s="1" t="s">
-        <v>104</v>
-      </c>
+    <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H149" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="J149" s="1">
-        <v>4037</v>
+        <v>37</v>
       </c>
       <c r="K149" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L149" s="1">
         <v>0</v>
       </c>
     </row>
+    <row r="150" customHeight="1" spans="3:12">
+      <c r="C150" s="1">
+        <v>508</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F150" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="G150" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="H150" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J150" s="1">
+        <v>38</v>
+      </c>
+      <c r="K150" s="1">
+        <v>4</v>
+      </c>
+      <c r="L150" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H151" s="4" t="s">
         <v>18</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="J151" s="1">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="K151" s="1">
         <v>4</v>
       </c>
       <c r="L151" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" customHeight="1" spans="3:12">
+      <c r="C153" s="1">
+        <v>521</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F153" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G153" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="H153" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="J153" s="1">
+        <v>4035</v>
+      </c>
+      <c r="K153" s="1">
+        <v>5</v>
+      </c>
+      <c r="L153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:12">
+      <c r="A154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C154" s="1">
+        <v>522</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F154" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G154" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J154" s="1">
+        <v>4036</v>
+      </c>
+      <c r="K154" s="1">
+        <v>5</v>
+      </c>
+      <c r="L154" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="1:12">
+      <c r="A155" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C155" s="1">
+        <v>523</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="G155" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="H155" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="J155" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K155" s="1">
+        <v>5</v>
+      </c>
+      <c r="L155" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:12">
+      <c r="C157" s="1">
+        <v>531</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E157" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F157" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G157" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="H157" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="J157" s="1">
+        <v>42</v>
+      </c>
+      <c r="K157" s="1">
+        <v>4</v>
+      </c>
+      <c r="L157" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -344,7 +344,7 @@
     <t>130,4007</t>
   </si>
   <si>
-    <t>1,7500000000</t>
+    <t>1,750000000</t>
   </si>
   <si>
     <t>斗笠31阶</t>
@@ -362,7 +362,7 @@
     <t>132,4007</t>
   </si>
   <si>
-    <t>1,12000000000</t>
+    <t>1,1200000000</t>
   </si>
   <si>
     <t>斗笠33阶</t>
@@ -2059,7 +2059,9 @@
     <col min="9" max="9" width="15" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.7545454545455" style="1" customWidth="1"/>
     <col min="11" max="12" width="15.1272727272727" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="9.72727272727273" style="1"/>
+    <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:12">

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="342">
   <si>
     <t>Id</t>
   </si>
@@ -1031,13 +1031,13 @@
     <t>传奇精华</t>
   </si>
   <si>
+    <t>30000,1500</t>
+  </si>
+  <si>
+    <t>不朽精华</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>30000,1000</t>
-  </si>
-  <si>
-    <t>不朽精华</t>
   </si>
   <si>
     <t>40000,1000</t>
@@ -6544,13 +6544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:12">
-      <c r="A154" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>334</v>
-      </c>
+    <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1">
         <v>522</v>
       </c>
@@ -6564,16 +6558,16 @@
         <v>331</v>
       </c>
       <c r="G154" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="H154" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H154" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="J154" s="1">
-        <v>4036</v>
+        <v>4039</v>
       </c>
       <c r="K154" s="1">
         <v>5</v>
@@ -6584,10 +6578,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C155" s="1">
         <v>523</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="350">
   <si>
     <t>Id</t>
   </si>
@@ -1053,6 +1053,30 @@
   </si>
   <si>
     <t>12阶技能</t>
+  </si>
+  <si>
+    <t>宝石</t>
+  </si>
+  <si>
+    <t>60000006,4111</t>
+  </si>
+  <si>
+    <t>1,100</t>
+  </si>
+  <si>
+    <t>魔法宝石</t>
+  </si>
+  <si>
+    <t>道术宝石</t>
+  </si>
+  <si>
+    <t>60000007,4111</t>
+  </si>
+  <si>
+    <t>物理宝石</t>
+  </si>
+  <si>
+    <t>60000008,4111</t>
   </si>
 </sst>
 </file>
@@ -1065,7 +1089,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1085,6 +1109,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1547,31 +1578,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1580,125 +1608,129 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2048,7 +2080,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L157"/>
+  <dimension ref="A3:L164"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2167,16 +2199,16 @@
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2199,16 +2231,16 @@
       <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="E7" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -2231,16 +2263,16 @@
       <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="E8" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -2263,16 +2295,16 @@
       <c r="D9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E9" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -2295,16 +2327,16 @@
       <c r="D10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -2327,16 +2359,16 @@
       <c r="D11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -2359,16 +2391,16 @@
       <c r="D12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="E12" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -2391,16 +2423,16 @@
       <c r="D13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -2423,16 +2455,16 @@
       <c r="D14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="E14" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -2455,16 +2487,16 @@
       <c r="D15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I15" s="1" t="s">
@@ -2487,16 +2519,16 @@
       <c r="D16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="E16" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -2519,16 +2551,16 @@
       <c r="D17" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I17" s="1" t="s">
@@ -2551,16 +2583,16 @@
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="E18" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I18" s="1" t="s">
@@ -2583,16 +2615,16 @@
       <c r="D19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="E19" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I19" s="1" t="s">
@@ -2615,16 +2647,16 @@
       <c r="D20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="4" t="s">
+      <c r="E20" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I20" s="1" t="s">
@@ -2647,16 +2679,16 @@
       <c r="D21" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="E21" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I21" s="1" t="s">
@@ -2679,16 +2711,16 @@
       <c r="D22" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="E22" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I22" s="1" t="s">
@@ -2711,16 +2743,16 @@
       <c r="D23" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="4" t="s">
+      <c r="E23" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I23" s="1" t="s">
@@ -2743,16 +2775,16 @@
       <c r="D24" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="E24" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -2775,16 +2807,16 @@
       <c r="D25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="E25" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I25" s="1" t="s">
@@ -2807,16 +2839,16 @@
       <c r="D26" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="E26" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I26" s="1" t="s">
@@ -2839,16 +2871,16 @@
       <c r="D27" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="E27" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -2871,16 +2903,16 @@
       <c r="D28" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="E28" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I28" s="1" t="s">
@@ -2903,16 +2935,16 @@
       <c r="D29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F29" s="4" t="s">
+      <c r="E29" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="1" t="s">
@@ -2935,16 +2967,16 @@
       <c r="D30" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="E30" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2967,16 +2999,16 @@
       <c r="D31" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="E31" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I31" s="1" t="s">
@@ -2999,16 +3031,16 @@
       <c r="D32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E32" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="E32" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I32" s="1" t="s">
@@ -3031,16 +3063,16 @@
       <c r="D33" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="4" t="s">
+      <c r="E33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I33" s="1" t="s">
@@ -3063,16 +3095,16 @@
       <c r="D34" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="4" t="s">
+      <c r="E34" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I34" s="1" t="s">
@@ -3095,16 +3127,16 @@
       <c r="D35" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="4" t="s">
+      <c r="E35" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I35" s="1" t="s">
@@ -3127,16 +3159,16 @@
       <c r="D36" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E36" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="4" t="s">
+      <c r="E36" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I36" s="1" t="s">
@@ -3159,16 +3191,16 @@
       <c r="D37" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="E37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G37" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I37" s="1" t="s">
@@ -3191,16 +3223,16 @@
       <c r="D40" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="4" t="s">
+      <c r="E40" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G40" s="4" t="s">
+      <c r="G40" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I40" s="1" t="s">
@@ -3223,16 +3255,16 @@
       <c r="D41" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E41" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="E41" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="G41" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -3255,16 +3287,16 @@
       <c r="D42" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E42" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" s="4" t="s">
+      <c r="E42" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="G42" s="4" t="s">
+      <c r="G42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="1" t="s">
@@ -3287,16 +3319,16 @@
       <c r="D43" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="E43" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I43" s="1" t="s">
@@ -3319,16 +3351,16 @@
       <c r="D44" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="4" t="s">
+      <c r="E44" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I44" s="1" t="s">
@@ -3351,16 +3383,16 @@
       <c r="D45" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="4" t="s">
+      <c r="E45" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="G45" s="4" t="s">
+      <c r="G45" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I45" s="1" t="s">
@@ -3383,16 +3415,16 @@
       <c r="D46" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" s="4" t="s">
+      <c r="E46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H46" s="4" t="s">
+      <c r="H46" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I46" s="1" t="s">
@@ -3415,16 +3447,16 @@
       <c r="D47" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" s="4" t="s">
+      <c r="E47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I47" s="1" t="s">
@@ -3447,16 +3479,16 @@
       <c r="D48" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" s="4" t="s">
+      <c r="E48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I48" s="1" t="s">
@@ -3479,16 +3511,16 @@
       <c r="D49" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="4" t="s">
+      <c r="E49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G49" s="4" t="s">
+      <c r="G49" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="H49" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I49" s="1" t="s">
@@ -3511,16 +3543,16 @@
       <c r="D50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E50" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="4" t="s">
+      <c r="E50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G50" s="4" t="s">
+      <c r="G50" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H50" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I50" s="1" t="s">
@@ -3543,16 +3575,16 @@
       <c r="D51" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="4" t="s">
+      <c r="E51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="G51" s="4" t="s">
+      <c r="G51" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
@@ -3575,16 +3607,16 @@
       <c r="D52" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E52" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" s="4" t="s">
+      <c r="E52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="G52" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
@@ -3607,16 +3639,16 @@
       <c r="D53" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="4" t="s">
+      <c r="E53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="4" t="s">
+      <c r="G53" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H53" s="4" t="s">
+      <c r="H53" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
@@ -3639,16 +3671,16 @@
       <c r="D54" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E54" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="4" t="s">
+      <c r="E54" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="G54" s="4" t="s">
+      <c r="G54" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H54" s="4" t="s">
+      <c r="H54" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
@@ -3671,16 +3703,16 @@
       <c r="D55" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="4" t="s">
+      <c r="E55" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
@@ -3703,16 +3735,16 @@
       <c r="D56" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E56" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" s="4" t="s">
+      <c r="E56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
@@ -3735,16 +3767,16 @@
       <c r="D57" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="4" t="s">
+      <c r="E57" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="G57" s="4" t="s">
+      <c r="G57" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
@@ -3767,16 +3799,16 @@
       <c r="D58" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E58" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" s="4" t="s">
+      <c r="E58" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="G58" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I58" s="1" t="s">
@@ -3799,16 +3831,16 @@
       <c r="D59" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" s="4" t="s">
+      <c r="E59" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="G59" s="4" t="s">
+      <c r="G59" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
@@ -3831,16 +3863,16 @@
       <c r="D60" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E60" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="4" t="s">
+      <c r="E60" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="G60" s="4" t="s">
+      <c r="G60" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H60" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
@@ -3863,16 +3895,16 @@
       <c r="D61" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="4" t="s">
+      <c r="E61" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="G61" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H61" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
@@ -3895,16 +3927,16 @@
       <c r="D62" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="4" t="s">
+      <c r="E62" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="G62" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H62" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I62" s="1" t="s">
@@ -3927,16 +3959,16 @@
       <c r="D63" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="4" t="s">
+      <c r="E63" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G63" s="4" t="s">
+      <c r="G63" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="H63" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
@@ -3959,16 +3991,16 @@
       <c r="D64" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="4" t="s">
+      <c r="E64" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="G64" s="4" t="s">
+      <c r="G64" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H64" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
@@ -3991,16 +4023,16 @@
       <c r="D65" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="4" t="s">
+      <c r="E65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="G65" s="4" t="s">
+      <c r="G65" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H65" s="4" t="s">
+      <c r="H65" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
@@ -4023,16 +4055,16 @@
       <c r="D66" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E66" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="4" t="s">
+      <c r="E66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="G66" s="4" t="s">
+      <c r="G66" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H66" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I66" s="1" t="s">
@@ -4055,16 +4087,16 @@
       <c r="D67" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" s="4" t="s">
+      <c r="E67" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="G67" s="4" t="s">
+      <c r="G67" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="H67" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I67" s="1" t="s">
@@ -4087,16 +4119,16 @@
       <c r="D68" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" s="4" t="s">
+      <c r="E68" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="G68" s="4" t="s">
+      <c r="G68" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H68" s="4" t="s">
+      <c r="H68" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I68" s="1" t="s">
@@ -4119,16 +4151,16 @@
       <c r="D69" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E69" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F69" s="4" t="s">
+      <c r="E69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="G69" s="4" t="s">
+      <c r="G69" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H69" s="4" t="s">
+      <c r="H69" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I69" s="1" t="s">
@@ -4151,16 +4183,16 @@
       <c r="D70" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" s="4" t="s">
+      <c r="E70" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F70" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="G70" s="4" t="s">
+      <c r="G70" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="H70" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I70" s="1" t="s">
@@ -4183,16 +4215,16 @@
       <c r="D71" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E71" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" s="4" t="s">
+      <c r="E71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="G71" s="4" t="s">
+      <c r="G71" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="H71" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I71" s="1" t="s">
@@ -4215,16 +4247,16 @@
       <c r="D74" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E74" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="4" t="s">
+      <c r="E74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G74" s="4" t="s">
+      <c r="G74" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H74" s="4" t="s">
+      <c r="H74" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
@@ -4247,16 +4279,16 @@
       <c r="D75" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F75" s="4" t="s">
+      <c r="E75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="G75" s="4" t="s">
+      <c r="G75" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H75" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I75" s="1" t="s">
@@ -4279,16 +4311,16 @@
       <c r="D76" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E76" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="4" t="s">
+      <c r="E76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="G76" s="4" t="s">
+      <c r="G76" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="H76" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I76" s="1" t="s">
@@ -4311,16 +4343,16 @@
       <c r="D77" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E77" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" s="4" t="s">
+      <c r="E77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G77" s="4" t="s">
+      <c r="G77" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H77" s="4" t="s">
+      <c r="H77" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I77" s="1" t="s">
@@ -4343,16 +4375,16 @@
       <c r="D78" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E78" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" s="4" t="s">
+      <c r="E78" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G78" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="H78" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
@@ -4375,16 +4407,16 @@
       <c r="D79" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E79" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F79" s="4" t="s">
+      <c r="E79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="G79" s="4" t="s">
+      <c r="G79" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H79" s="4" t="s">
+      <c r="H79" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I79" s="1" t="s">
@@ -4407,16 +4439,16 @@
       <c r="D80" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E80" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F80" s="4" t="s">
+      <c r="E80" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="G80" s="4" t="s">
+      <c r="G80" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H80" s="4" t="s">
+      <c r="H80" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I80" s="1" t="s">
@@ -4439,16 +4471,16 @@
       <c r="D81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E81" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="4" t="s">
+      <c r="E81" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F81" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="G81" s="4" t="s">
+      <c r="G81" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H81" s="4" t="s">
+      <c r="H81" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I81" s="1" t="s">
@@ -4471,16 +4503,16 @@
       <c r="D82" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F82" s="4" t="s">
+      <c r="E82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F82" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="G82" s="4" t="s">
+      <c r="G82" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H82" s="4" t="s">
+      <c r="H82" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I82" s="1" t="s">
@@ -4503,16 +4535,16 @@
       <c r="D83" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E83" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F83" s="4" t="s">
+      <c r="E83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F83" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="G83" s="4" t="s">
+      <c r="G83" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H83" s="4" t="s">
+      <c r="H83" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
@@ -4535,16 +4567,16 @@
       <c r="D84" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E84" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="4" t="s">
+      <c r="E84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F84" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="G84" s="4" t="s">
+      <c r="G84" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H84" s="4" t="s">
+      <c r="H84" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
@@ -4567,16 +4599,16 @@
       <c r="D85" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E85" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="4" t="s">
+      <c r="E85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="G85" s="4" t="s">
+      <c r="G85" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H85" s="4" t="s">
+      <c r="H85" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
@@ -4599,16 +4631,16 @@
       <c r="D86" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E86" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="4" t="s">
+      <c r="E86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="G86" s="4" t="s">
+      <c r="G86" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H86" s="4" t="s">
+      <c r="H86" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
@@ -4631,16 +4663,16 @@
       <c r="D87" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E87" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F87" s="4" t="s">
+      <c r="E87" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="G87" s="4" t="s">
+      <c r="G87" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H87" s="4" t="s">
+      <c r="H87" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
@@ -4663,16 +4695,16 @@
       <c r="D88" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E88" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="4" t="s">
+      <c r="E88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="G88" s="4" t="s">
+      <c r="G88" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H88" s="4" t="s">
+      <c r="H88" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
@@ -4695,16 +4727,16 @@
       <c r="D89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E89" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F89" s="4" t="s">
+      <c r="E89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G89" s="4" t="s">
+      <c r="G89" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H89" s="4" t="s">
+      <c r="H89" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
@@ -4727,16 +4759,16 @@
       <c r="D90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E90" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F90" s="4" t="s">
+      <c r="E90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G90" s="4" t="s">
+      <c r="G90" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H90" s="4" t="s">
+      <c r="H90" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
@@ -4759,16 +4791,16 @@
       <c r="D91" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E91" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F91" s="4" t="s">
+      <c r="E91" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="G91" s="4" t="s">
+      <c r="G91" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H91" s="4" t="s">
+      <c r="H91" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -4791,16 +4823,16 @@
       <c r="D92" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E92" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F92" s="4" t="s">
+      <c r="E92" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G92" s="4" t="s">
+      <c r="G92" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H92" s="4" t="s">
+      <c r="H92" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
@@ -4823,16 +4855,16 @@
       <c r="D93" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E93" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" s="4" t="s">
+      <c r="E93" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="G93" s="4" t="s">
+      <c r="G93" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H93" s="4" t="s">
+      <c r="H93" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
@@ -4855,16 +4887,16 @@
       <c r="D94" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E94" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="4" t="s">
+      <c r="E94" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G94" s="4" t="s">
+      <c r="G94" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H94" s="4" t="s">
+      <c r="H94" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -4887,16 +4919,16 @@
       <c r="D95" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E95" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="4" t="s">
+      <c r="E95" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F95" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G95" s="4" t="s">
+      <c r="G95" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H95" s="4" t="s">
+      <c r="H95" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
@@ -4919,16 +4951,16 @@
       <c r="D96" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="4" t="s">
+      <c r="E96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F96" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="G96" s="4" t="s">
+      <c r="G96" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H96" s="4" t="s">
+      <c r="H96" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
@@ -4951,16 +4983,16 @@
       <c r="D97" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F97" s="4" t="s">
+      <c r="E97" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="G97" s="4" t="s">
+      <c r="G97" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H97" s="4" t="s">
+      <c r="H97" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
@@ -4983,16 +5015,16 @@
       <c r="D98" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F98" s="4" t="s">
+      <c r="E98" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F98" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G98" s="4" t="s">
+      <c r="G98" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H98" s="4" t="s">
+      <c r="H98" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
@@ -5015,16 +5047,16 @@
       <c r="D99" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="4" t="s">
+      <c r="E99" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="G99" s="4" t="s">
+      <c r="G99" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H99" s="4" t="s">
+      <c r="H99" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
@@ -5047,16 +5079,16 @@
       <c r="D100" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E100" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" s="4" t="s">
+      <c r="E100" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F100" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="G100" s="4" t="s">
+      <c r="G100" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H100" s="4" t="s">
+      <c r="H100" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
@@ -5079,16 +5111,16 @@
       <c r="D101" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E101" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F101" s="4" t="s">
+      <c r="E101" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F101" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G101" s="4" t="s">
+      <c r="G101" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H101" s="4" t="s">
+      <c r="H101" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
@@ -5111,16 +5143,16 @@
       <c r="D102" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E102" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="4" t="s">
+      <c r="E102" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F102" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G102" s="4" t="s">
+      <c r="G102" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H102" s="4" t="s">
+      <c r="H102" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
@@ -5143,16 +5175,16 @@
       <c r="D103" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E103" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="4" t="s">
+      <c r="E103" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F103" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="G103" s="4" t="s">
+      <c r="G103" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H103" s="4" t="s">
+      <c r="H103" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
@@ -5175,16 +5207,16 @@
       <c r="D104" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E104" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="4" t="s">
+      <c r="E104" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F104" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G104" s="4" t="s">
+      <c r="G104" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H104" s="4" t="s">
+      <c r="H104" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
@@ -5207,16 +5239,16 @@
       <c r="D105" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E105" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F105" s="4" t="s">
+      <c r="E105" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F105" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G105" s="4" t="s">
+      <c r="G105" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H105" s="4" t="s">
+      <c r="H105" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
@@ -5239,16 +5271,16 @@
       <c r="D108" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E108" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F108" s="4" t="s">
+      <c r="E108" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G108" s="4" t="s">
+      <c r="G108" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H108" s="4" t="s">
+      <c r="H108" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
@@ -5271,16 +5303,16 @@
       <c r="D109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E109" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F109" s="4" t="s">
+      <c r="E109" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F109" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="G109" s="4" t="s">
+      <c r="G109" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="H109" s="4" t="s">
+      <c r="H109" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
@@ -5303,16 +5335,16 @@
       <c r="D110" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E110" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="4" t="s">
+      <c r="E110" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F110" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G110" s="4" t="s">
+      <c r="G110" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="H110" s="4" t="s">
+      <c r="H110" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
@@ -5335,16 +5367,16 @@
       <c r="D111" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E111" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F111" s="4" t="s">
+      <c r="E111" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F111" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="G111" s="4" t="s">
+      <c r="G111" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H111" s="4" t="s">
+      <c r="H111" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -5367,16 +5399,16 @@
       <c r="D112" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E112" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" s="4" t="s">
+      <c r="E112" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F112" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="G112" s="4" t="s">
+      <c r="G112" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H112" s="4" t="s">
+      <c r="H112" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
@@ -5399,16 +5431,16 @@
       <c r="D113" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E113" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" s="4" t="s">
+      <c r="E113" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="G113" s="4" t="s">
+      <c r="G113" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H113" s="4" t="s">
+      <c r="H113" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
@@ -5431,16 +5463,16 @@
       <c r="D114" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E114" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F114" s="4" t="s">
+      <c r="E114" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F114" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="G114" s="4" t="s">
+      <c r="G114" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H114" s="4" t="s">
+      <c r="H114" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
@@ -5463,16 +5495,16 @@
       <c r="D115" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E115" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F115" s="4" t="s">
+      <c r="E115" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F115" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="G115" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="H115" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
@@ -5495,16 +5527,16 @@
       <c r="D116" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E116" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F116" s="4" t="s">
+      <c r="E116" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F116" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="G116" s="4" t="s">
+      <c r="G116" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="H116" s="4" t="s">
+      <c r="H116" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
@@ -5527,16 +5559,16 @@
       <c r="D117" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E117" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F117" s="4" t="s">
+      <c r="E117" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F117" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="G117" s="4" t="s">
+      <c r="G117" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H117" s="4" t="s">
+      <c r="H117" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
@@ -5559,16 +5591,16 @@
       <c r="D118" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E118" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F118" s="4" t="s">
+      <c r="E118" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="G118" s="4" t="s">
+      <c r="G118" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H118" s="4" t="s">
+      <c r="H118" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
@@ -5591,16 +5623,16 @@
       <c r="D119" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E119" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" s="4" t="s">
+      <c r="E119" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F119" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="G119" s="4" t="s">
+      <c r="G119" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H119" s="4" t="s">
+      <c r="H119" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
@@ -5623,16 +5655,16 @@
       <c r="D120" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E120" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="4" t="s">
+      <c r="E120" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F120" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G120" s="4" t="s">
+      <c r="G120" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H120" s="4" t="s">
+      <c r="H120" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I120" s="1" t="s">
@@ -5655,16 +5687,16 @@
       <c r="D121" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E121" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F121" s="4" t="s">
+      <c r="E121" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F121" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="G121" s="4" t="s">
+      <c r="G121" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H121" s="4" t="s">
+      <c r="H121" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
@@ -5687,16 +5719,16 @@
       <c r="D122" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E122" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F122" s="4" t="s">
+      <c r="E122" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F122" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G122" s="4" t="s">
+      <c r="G122" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H122" s="4" t="s">
+      <c r="H122" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
@@ -5719,16 +5751,16 @@
       <c r="D123" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E123" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F123" s="4" t="s">
+      <c r="E123" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F123" s="5" t="s">
         <v>274</v>
       </c>
-      <c r="G123" s="4" t="s">
+      <c r="G123" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H123" s="4" t="s">
+      <c r="H123" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I123" s="1" t="s">
@@ -5751,16 +5783,16 @@
       <c r="D124" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E124" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="4" t="s">
+      <c r="E124" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F124" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="G124" s="4" t="s">
+      <c r="G124" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H124" s="4" t="s">
+      <c r="H124" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -5783,16 +5815,16 @@
       <c r="D125" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E125" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F125" s="4" t="s">
+      <c r="E125" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F125" s="5" t="s">
         <v>278</v>
       </c>
-      <c r="G125" s="4" t="s">
+      <c r="G125" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H125" s="4" t="s">
+      <c r="H125" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
@@ -5815,16 +5847,16 @@
       <c r="D126" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E126" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F126" s="4" t="s">
+      <c r="E126" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="G126" s="4" t="s">
+      <c r="G126" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H126" s="4" t="s">
+      <c r="H126" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
@@ -5847,16 +5879,16 @@
       <c r="D127" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E127" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F127" s="4" t="s">
+      <c r="E127" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F127" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="G127" s="4" t="s">
+      <c r="G127" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="H127" s="4" t="s">
+      <c r="H127" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
@@ -5879,16 +5911,16 @@
       <c r="D128" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E128" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F128" s="4" t="s">
+      <c r="E128" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F128" s="5" t="s">
         <v>284</v>
       </c>
-      <c r="G128" s="4" t="s">
+      <c r="G128" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="H128" s="4" t="s">
+      <c r="H128" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
@@ -5911,16 +5943,16 @@
       <c r="D129" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E129" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F129" s="4" t="s">
+      <c r="E129" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F129" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G129" s="4" t="s">
+      <c r="G129" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H129" s="4" t="s">
+      <c r="H129" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
@@ -5943,16 +5975,16 @@
       <c r="D130" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E130" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" s="4" t="s">
+      <c r="E130" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F130" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="G130" s="4" t="s">
+      <c r="G130" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H130" s="4" t="s">
+      <c r="H130" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
@@ -5975,16 +6007,16 @@
       <c r="D131" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E131" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F131" s="4" t="s">
+      <c r="E131" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F131" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="G131" s="4" t="s">
+      <c r="G131" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="H131" s="4" t="s">
+      <c r="H131" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I131" s="1" t="s">
@@ -6007,16 +6039,16 @@
       <c r="D132" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E132" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F132" s="4" t="s">
+      <c r="E132" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F132" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="G132" s="4" t="s">
+      <c r="G132" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H132" s="4" t="s">
+      <c r="H132" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I132" s="1" t="s">
@@ -6039,16 +6071,16 @@
       <c r="D133" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E133" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F133" s="4" t="s">
+      <c r="E133" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F133" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="G133" s="4" t="s">
+      <c r="G133" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H133" s="4" t="s">
+      <c r="H133" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I133" s="1" t="s">
@@ -6071,16 +6103,16 @@
       <c r="D134" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E134" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F134" s="4" t="s">
+      <c r="E134" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="G134" s="4" t="s">
+      <c r="G134" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H134" s="4" t="s">
+      <c r="H134" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I134" s="1" t="s">
@@ -6103,16 +6135,16 @@
       <c r="D135" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E135" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" s="4" t="s">
+      <c r="E135" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="G135" s="4" t="s">
+      <c r="G135" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H135" s="4" t="s">
+      <c r="H135" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I135" s="1" t="s">
@@ -6135,16 +6167,16 @@
       <c r="D136" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E136" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F136" s="4" t="s">
+      <c r="E136" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F136" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G136" s="4" t="s">
+      <c r="G136" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H136" s="4" t="s">
+      <c r="H136" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I136" s="1" t="s">
@@ -6167,16 +6199,16 @@
       <c r="D137" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E137" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F137" s="4" t="s">
+      <c r="E137" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F137" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="G137" s="4" t="s">
+      <c r="G137" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H137" s="4" t="s">
+      <c r="H137" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I137" s="1" t="s">
@@ -6199,16 +6231,16 @@
       <c r="D138" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E138" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F138" s="4" t="s">
+      <c r="E138" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F138" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="G138" s="4" t="s">
+      <c r="G138" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H138" s="4" t="s">
+      <c r="H138" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I138" s="1" t="s">
@@ -6231,16 +6263,16 @@
       <c r="D139" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E139" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F139" s="4" t="s">
+      <c r="E139" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F139" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="G139" s="4" t="s">
+      <c r="G139" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H139" s="4" t="s">
+      <c r="H139" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
@@ -6263,16 +6295,16 @@
       <c r="D144" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E144" s="4" t="s">
+      <c r="E144" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F144" s="4" t="s">
+      <c r="F144" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="G144" s="4" t="s">
+      <c r="G144" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="H144" s="4" t="s">
+      <c r="H144" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
@@ -6295,16 +6327,16 @@
       <c r="D145" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E145" s="4" t="s">
+      <c r="E145" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F145" s="4" t="s">
+      <c r="F145" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G145" s="4" t="s">
+      <c r="G145" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="H145" s="4" t="s">
+      <c r="H145" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -6327,16 +6359,16 @@
       <c r="D146" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E146" s="4" t="s">
+      <c r="E146" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F146" s="4" t="s">
+      <c r="F146" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="G146" s="4" t="s">
+      <c r="G146" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="H146" s="4" t="s">
+      <c r="H146" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I146" s="1" t="s">
@@ -6359,16 +6391,16 @@
       <c r="D147" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E147" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F147" s="4" t="s">
+      <c r="F147" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="G147" s="4" t="s">
+      <c r="G147" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="H147" s="4" t="s">
+      <c r="H147" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I147" s="1" t="s">
@@ -6391,16 +6423,16 @@
       <c r="D148" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E148" s="4" t="s">
+      <c r="E148" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F148" s="4" t="s">
+      <c r="F148" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G148" s="4" t="s">
+      <c r="G148" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H148" s="4" t="s">
+      <c r="H148" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I148" s="1" t="s">
@@ -6423,16 +6455,16 @@
       <c r="D149" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E149" s="4" t="s">
+      <c r="E149" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F149" s="4" t="s">
+      <c r="F149" s="5" t="s">
         <v>325</v>
       </c>
-      <c r="G149" s="4" t="s">
+      <c r="G149" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H149" s="4" t="s">
+      <c r="H149" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I149" s="1" t="s">
@@ -6455,16 +6487,16 @@
       <c r="D150" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E150" s="4" t="s">
+      <c r="E150" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F150" s="4" t="s">
+      <c r="F150" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="G150" s="4" t="s">
+      <c r="G150" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H150" s="4" t="s">
+      <c r="H150" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I150" s="1" t="s">
@@ -6487,16 +6519,16 @@
       <c r="D151" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E151" s="4" t="s">
+      <c r="E151" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F151" s="4" t="s">
+      <c r="F151" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="G151" s="4" t="s">
+      <c r="G151" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="H151" s="4" t="s">
+      <c r="H151" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I151" s="1" t="s">
@@ -6519,16 +6551,16 @@
       <c r="D153" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E153" s="4" t="s">
+      <c r="E153" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F153" s="4" t="s">
+      <c r="F153" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G153" s="4" t="s">
+      <c r="G153" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="H153" s="4" t="s">
+      <c r="H153" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I153" s="1" t="s">
@@ -6551,16 +6583,16 @@
       <c r="D154" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E154" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F154" s="4" t="s">
+      <c r="F154" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G154" s="4" t="s">
+      <c r="G154" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="H154" s="4" t="s">
+      <c r="H154" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I154" s="1" t="s">
@@ -6589,16 +6621,16 @@
       <c r="D155" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E155" s="4" t="s">
+      <c r="E155" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F155" s="4" t="s">
+      <c r="F155" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="G155" s="4" t="s">
+      <c r="G155" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="H155" s="4" t="s">
+      <c r="H155" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I155" s="1" t="s">
@@ -6621,16 +6653,16 @@
       <c r="D157" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E157" s="4" t="s">
+      <c r="E157" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F157" s="4" t="s">
+      <c r="F157" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="G157" s="4" t="s">
+      <c r="G157" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H157" s="4" t="s">
+      <c r="H157" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I157" s="1" t="s">
@@ -6643,6 +6675,198 @@
         <v>4</v>
       </c>
       <c r="L157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:12">
+      <c r="C159" s="1">
+        <v>601</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J159" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="K159" s="1">
+        <v>5</v>
+      </c>
+      <c r="L159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:12">
+      <c r="C160" s="1">
+        <v>602</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="G160" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H160" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J160" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="K160" s="1">
+        <v>5</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:12">
+      <c r="C161" s="1">
+        <v>603</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F161" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G161" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H161" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J161" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="K161" s="1">
+        <v>5</v>
+      </c>
+      <c r="L161" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:12">
+      <c r="C162" s="1">
+        <v>604</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J162" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="K162" s="1">
+        <v>5</v>
+      </c>
+      <c r="L162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:12">
+      <c r="C163" s="1">
+        <v>605</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J163" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="K163" s="1">
+        <v>5</v>
+      </c>
+      <c r="L163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:12">
+      <c r="C164" s="1">
+        <v>606</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E164" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="G164" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="J164" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="K164" s="1">
+        <v>5</v>
+      </c>
+      <c r="L164" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="352">
   <si>
     <t>Id</t>
   </si>
@@ -1020,6 +1020,12 @@
   </si>
   <si>
     <t>玄武神器</t>
+  </si>
+  <si>
+    <t>4032,4111</t>
+  </si>
+  <si>
+    <t>麒麟神器</t>
   </si>
   <si>
     <t>4005,4111</t>
@@ -2080,7 +2086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L164"/>
+  <dimension ref="A3:L165"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6320,7 +6326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="3:12">
+    <row r="145" customHeight="1" spans="1:12">
       <c r="C145" s="1">
         <v>502</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="3:12">
+    <row r="146" customHeight="1" spans="1:12">
       <c r="C146" s="1">
         <v>503</v>
       </c>
@@ -6384,7 +6390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="3:12">
+    <row r="147" customHeight="1" spans="1:12">
       <c r="C147" s="1">
         <v>504</v>
       </c>
@@ -6416,7 +6422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="3:12">
+    <row r="148" customHeight="1" spans="1:12">
       <c r="C148" s="1">
         <v>505</v>
       </c>
@@ -6448,7 +6454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="3:12">
+    <row r="149" customHeight="1" spans="1:12">
       <c r="C149" s="1">
         <v>506</v>
       </c>
@@ -6480,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="3:12">
+    <row r="150" customHeight="1" spans="1:12">
       <c r="C150" s="1">
         <v>508</v>
       </c>
@@ -6512,7 +6518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:12">
+    <row r="151" customHeight="1" spans="1:12">
       <c r="C151" s="1">
         <v>509</v>
       </c>
@@ -6544,41 +6550,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:12">
-      <c r="C153" s="1">
+    <row r="152" customHeight="1" spans="1:12">
+      <c r="C152" s="1">
+        <v>510</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="G152" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="H152" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J152" s="1">
+        <v>40</v>
+      </c>
+      <c r="K152" s="1">
+        <v>4</v>
+      </c>
+      <c r="L152" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="1:12">
+      <c r="C154" s="1">
         <v>521</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E153" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F153" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="H153" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="J153" s="1">
-        <v>4035</v>
-      </c>
-      <c r="K153" s="1">
-        <v>5</v>
-      </c>
-      <c r="L153" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" spans="3:12">
-      <c r="C154" s="1">
-        <v>522</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>308</v>
@@ -6587,7 +6593,7 @@
         <v>309</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>334</v>
@@ -6599,7 +6605,7 @@
         <v>335</v>
       </c>
       <c r="J154" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="K154" s="1">
         <v>5</v>
@@ -6609,14 +6615,8 @@
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:12">
-      <c r="A155" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="C155" s="1">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>308</v>
@@ -6625,19 +6625,19 @@
         <v>309</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G155" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H155" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I155" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="H155" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="J155" s="1">
-        <v>4037</v>
+        <v>4039</v>
       </c>
       <c r="K155" s="1">
         <v>5</v>
@@ -6646,94 +6646,100 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="3:12">
-      <c r="C157" s="1">
+    <row r="156" customHeight="1" spans="1:12">
+      <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C156" s="1">
+        <v>523</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E156" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F156" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="G156" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="H156" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="J156" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K156" s="1">
+        <v>5</v>
+      </c>
+      <c r="L156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="1:12">
+      <c r="C158" s="1">
         <v>531</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E157" s="5" t="s">
+      <c r="E158" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F157" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="G157" s="5" t="s">
-        <v>340</v>
-      </c>
-      <c r="H157" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I157" s="1" t="s">
+      <c r="F158" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="J157" s="1">
+      <c r="G158" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J158" s="1">
         <v>42</v>
       </c>
-      <c r="K157" s="1">
+      <c r="K158" s="1">
         <v>4</v>
       </c>
-      <c r="L157" s="1">
+      <c r="L158" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="3:12">
-      <c r="C159" s="1">
+    <row r="160" customHeight="1" spans="1:12">
+      <c r="C160" s="1">
         <v>601</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="G159" s="5" t="s">
+      <c r="D160" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="H159" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="J159" s="4">
-        <v>60000007</v>
-      </c>
-      <c r="K159" s="1">
-        <v>5</v>
-      </c>
-      <c r="L159" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" spans="3:12">
-      <c r="C160" s="1">
-        <v>602</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J160" s="4">
-        <v>60000008</v>
+        <v>60000007</v>
       </c>
       <c r="K160" s="1">
         <v>5</v>
@@ -6744,19 +6750,19 @@
     </row>
     <row r="161" customHeight="1" spans="3:12">
       <c r="C161" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>18</v>
@@ -6765,7 +6771,7 @@
         <v>348</v>
       </c>
       <c r="J161" s="4">
-        <v>60000006</v>
+        <v>60000008</v>
       </c>
       <c r="K161" s="1">
         <v>5</v>
@@ -6776,28 +6782,28 @@
     </row>
     <row r="162" customHeight="1" spans="3:12">
       <c r="C162" s="1">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J162" s="4">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="K162" s="1">
         <v>5</v>
@@ -6808,10 +6814,10 @@
     </row>
     <row r="163" customHeight="1" spans="3:12">
       <c r="C163" s="1">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>309</v>
@@ -6820,7 +6826,7 @@
         <v>349</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H163" s="5" t="s">
         <v>18</v>
@@ -6829,7 +6835,7 @@
         <v>348</v>
       </c>
       <c r="J163" s="4">
-        <v>60000006</v>
+        <v>60000008</v>
       </c>
       <c r="K163" s="1">
         <v>5</v>
@@ -6840,33 +6846,65 @@
     </row>
     <row r="164" customHeight="1" spans="3:12">
       <c r="C164" s="1">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J164" s="4">
-        <v>60000007</v>
+        <v>60000006</v>
       </c>
       <c r="K164" s="1">
         <v>5</v>
       </c>
       <c r="L164" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" customHeight="1" spans="3:12">
+      <c r="C165" s="1">
+        <v>606</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E165" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="J165" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="K165" s="1">
+        <v>5</v>
+      </c>
+      <c r="L165" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="355">
   <si>
     <t>Id</t>
   </si>
@@ -995,6 +995,18 @@
     <t>金色魂心</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>4025,4111</t>
+  </si>
+  <si>
+    <t>10,200000</t>
+  </si>
+  <si>
+    <t>暗金魂心</t>
+  </si>
+  <si>
     <t>4028,4111</t>
   </si>
   <si>
@@ -1043,10 +1055,7 @@
     <t>不朽精华</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>40000,1000</t>
+    <t>40000,2000</t>
   </si>
   <si>
     <t>永恒精华</t>
@@ -2086,7 +2095,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L165"/>
+  <dimension ref="A3:L167"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6423,6 +6432,12 @@
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:12">
+      <c r="A148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>322</v>
+      </c>
       <c r="C148" s="1">
         <v>505</v>
       </c>
@@ -6433,22 +6448,22 @@
         <v>309</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H148" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J148" s="1">
-        <v>35</v>
+        <v>4041</v>
       </c>
       <c r="K148" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
@@ -6465,19 +6480,19 @@
         <v>309</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H149" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="J149" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K149" s="1">
         <v>4</v>
@@ -6488,7 +6503,7 @@
     </row>
     <row r="150" customHeight="1" spans="1:12">
       <c r="C150" s="1">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>308</v>
@@ -6497,19 +6512,19 @@
         <v>309</v>
       </c>
       <c r="F150" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G150" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="G150" s="5" t="s">
-        <v>323</v>
-      </c>
       <c r="H150" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="J150" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K150" s="1">
         <v>4</v>
@@ -6520,7 +6535,7 @@
     </row>
     <row r="151" customHeight="1" spans="1:12">
       <c r="C151" s="1">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>308</v>
@@ -6529,19 +6544,19 @@
         <v>309</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H151" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J151" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K151" s="1">
         <v>4</v>
@@ -6552,7 +6567,7 @@
     </row>
     <row r="152" customHeight="1" spans="1:12">
       <c r="C152" s="1">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>308</v>
@@ -6561,19 +6576,19 @@
         <v>309</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="J152" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K152" s="1">
         <v>4</v>
@@ -6582,41 +6597,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:12">
-      <c r="C154" s="1">
-        <v>521</v>
-      </c>
-      <c r="D154" s="1" t="s">
+    <row r="153" customHeight="1" spans="1:12">
+      <c r="C153" s="1">
+        <v>510</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="E153" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F154" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="H154" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I154" s="1" t="s">
+      <c r="F153" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="J154" s="1">
-        <v>4035</v>
-      </c>
-      <c r="K154" s="1">
-        <v>5</v>
-      </c>
-      <c r="L154" s="1">
+      <c r="G153" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H153" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="J153" s="1">
+        <v>40</v>
+      </c>
+      <c r="K153" s="1">
+        <v>4</v>
+      </c>
+      <c r="L153" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="C155" s="1">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>308</v>
@@ -6625,19 +6640,19 @@
         <v>309</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="J155" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="K155" s="1">
         <v>5</v>
@@ -6647,14 +6662,8 @@
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:12">
-      <c r="A156" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>338</v>
-      </c>
       <c r="C156" s="1">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>308</v>
@@ -6663,19 +6672,19 @@
         <v>309</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="J156" s="1">
-        <v>4037</v>
+        <v>4039</v>
       </c>
       <c r="K156" s="1">
         <v>5</v>
@@ -6684,117 +6693,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:12">
-      <c r="C158" s="1">
+    <row r="157" customHeight="1" spans="1:12">
+      <c r="C157" s="1">
+        <v>523</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E157" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F157" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="G157" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H157" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="J157" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K157" s="1">
+        <v>5</v>
+      </c>
+      <c r="L157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="1:12">
+      <c r="C159" s="1">
         <v>531</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D159" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E158" s="5" t="s">
+      <c r="E159" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F158" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="G158" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="H158" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I158" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="J158" s="1">
+      <c r="F159" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="J159" s="1">
         <v>42</v>
       </c>
-      <c r="K158" s="1">
+      <c r="K159" s="1">
         <v>4</v>
       </c>
-      <c r="L158" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" customHeight="1" spans="1:12">
-      <c r="C160" s="1">
-        <v>601</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E160" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F160" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G160" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H160" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I160" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="J160" s="4">
-        <v>60000007</v>
-      </c>
-      <c r="K160" s="1">
-        <v>5</v>
-      </c>
-      <c r="L160" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" customHeight="1" spans="3:12">
-      <c r="C161" s="1">
-        <v>602</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="E161" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F161" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G161" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H161" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I161" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="J161" s="4">
-        <v>60000008</v>
-      </c>
-      <c r="K161" s="1">
-        <v>5</v>
-      </c>
-      <c r="L161" s="1">
+      <c r="L159" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="162" customHeight="1" spans="3:12">
       <c r="C162" s="1">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F162" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G162" s="5" t="s">
         <v>349</v>
-      </c>
-      <c r="G162" s="5" t="s">
-        <v>346</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>18</v>
@@ -6803,7 +6780,7 @@
         <v>350</v>
       </c>
       <c r="J162" s="4">
-        <v>60000006</v>
+        <v>60000007</v>
       </c>
       <c r="K162" s="1">
         <v>5</v>
@@ -6814,25 +6791,25 @@
     </row>
     <row r="163" customHeight="1" spans="3:12">
       <c r="C163" s="1">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F163" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="G163" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G163" s="5" t="s">
-        <v>346</v>
-      </c>
       <c r="H163" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J163" s="4">
         <v>60000008</v>
@@ -6846,25 +6823,25 @@
     </row>
     <row r="164" customHeight="1" spans="3:12">
       <c r="C164" s="1">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J164" s="4">
         <v>60000006</v>
@@ -6878,33 +6855,97 @@
     </row>
     <row r="165" customHeight="1" spans="3:12">
       <c r="C165" s="1">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F165" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="G165" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H165" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I165" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="G165" s="5" t="s">
-        <v>346</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="J165" s="4">
-        <v>60000007</v>
+        <v>60000008</v>
       </c>
       <c r="K165" s="1">
         <v>5</v>
       </c>
       <c r="L165" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" customHeight="1" spans="3:12">
+      <c r="C166" s="1">
+        <v>605</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E166" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J166" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="K166" s="1">
+        <v>5</v>
+      </c>
+      <c r="L166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="3:12">
+      <c r="C167" s="1">
+        <v>606</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F167" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="G167" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="H167" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="J167" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="K167" s="1">
+        <v>5</v>
+      </c>
+      <c r="L167" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="362">
   <si>
     <t>Id</t>
   </si>
@@ -995,49 +995,70 @@
     <t>金色魂心</t>
   </si>
   <si>
+    <t>4028,4111</t>
+  </si>
+  <si>
+    <t>40,100000</t>
+  </si>
+  <si>
+    <t>青龙神器</t>
+  </si>
+  <si>
+    <t>4029,4111</t>
+  </si>
+  <si>
+    <t>白虎神器</t>
+  </si>
+  <si>
+    <t>4030,4111</t>
+  </si>
+  <si>
+    <t>朱雀神器</t>
+  </si>
+  <si>
+    <t>4031,4111</t>
+  </si>
+  <si>
+    <t>玄武神器</t>
+  </si>
+  <si>
+    <t>4032,4111</t>
+  </si>
+  <si>
+    <t>麒麟神器</t>
+  </si>
+  <si>
+    <t>4055,4111</t>
+  </si>
+  <si>
+    <t>极龙神器</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>4025,4111</t>
-  </si>
-  <si>
-    <t>10,200000</t>
-  </si>
-  <si>
-    <t>暗金魂心</t>
-  </si>
-  <si>
-    <t>4028,4111</t>
-  </si>
-  <si>
-    <t>40,100000</t>
-  </si>
-  <si>
-    <t>青龙神器</t>
-  </si>
-  <si>
-    <t>4029,4111</t>
-  </si>
-  <si>
-    <t>白虎神器</t>
-  </si>
-  <si>
-    <t>4030,4111</t>
-  </si>
-  <si>
-    <t>朱雀神器</t>
-  </si>
-  <si>
-    <t>4031,4111</t>
-  </si>
-  <si>
-    <t>玄武神器</t>
-  </si>
-  <si>
-    <t>4032,4111</t>
-  </si>
-  <si>
-    <t>麒麟神器</t>
+    <t>4056,4111</t>
+  </si>
+  <si>
+    <t>极虎神器</t>
+  </si>
+  <si>
+    <t>4057,4111</t>
+  </si>
+  <si>
+    <t>极雀神器</t>
+  </si>
+  <si>
+    <t>4058,4111</t>
+  </si>
+  <si>
+    <t>极玄神器</t>
+  </si>
+  <si>
+    <t>4059,4111</t>
+  </si>
+  <si>
+    <t>极麟神器</t>
   </si>
   <si>
     <t>4005,4111</t>
@@ -2095,7 +2116,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L167"/>
+  <dimension ref="A3:L171"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6432,14 +6453,8 @@
       </c>
     </row>
     <row r="148" customHeight="1" spans="1:12">
-      <c r="A148" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B148" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="C148" s="1">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>308</v>
@@ -6448,22 +6463,22 @@
         <v>309</v>
       </c>
       <c r="F148" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G148" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="H148" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="H148" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="J148" s="1">
-        <v>4041</v>
+        <v>35</v>
       </c>
       <c r="K148" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
@@ -6471,7 +6486,7 @@
     </row>
     <row r="149" customHeight="1" spans="1:12">
       <c r="C149" s="1">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>308</v>
@@ -6480,19 +6495,19 @@
         <v>309</v>
       </c>
       <c r="F149" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="H149" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I149" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="G149" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="J149" s="1">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K149" s="1">
         <v>4</v>
@@ -6503,7 +6518,7 @@
     </row>
     <row r="150" customHeight="1" spans="1:12">
       <c r="C150" s="1">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>308</v>
@@ -6512,19 +6527,19 @@
         <v>309</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H150" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="J150" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K150" s="1">
         <v>4</v>
@@ -6535,7 +6550,7 @@
     </row>
     <row r="151" customHeight="1" spans="1:12">
       <c r="C151" s="1">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>308</v>
@@ -6544,19 +6559,19 @@
         <v>309</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H151" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="J151" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K151" s="1">
         <v>4</v>
@@ -6567,7 +6582,7 @@
     </row>
     <row r="152" customHeight="1" spans="1:12">
       <c r="C152" s="1">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>308</v>
@@ -6576,19 +6591,19 @@
         <v>309</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="J152" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K152" s="1">
         <v>4</v>
@@ -6599,7 +6614,7 @@
     </row>
     <row r="153" customHeight="1" spans="1:12">
       <c r="C153" s="1">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>308</v>
@@ -6608,16 +6623,16 @@
         <v>309</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="J153" s="1">
         <v>40</v>
@@ -6629,9 +6644,53 @@
         <v>0</v>
       </c>
     </row>
+    <row r="154" customHeight="1" spans="1:12">
+      <c r="A154" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="C154" s="1">
+        <v>512</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F154" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="J154" s="1">
+        <v>40</v>
+      </c>
+      <c r="K154" s="1">
+        <v>4</v>
+      </c>
+      <c r="L154" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="155" customHeight="1" spans="1:12">
+      <c r="A155" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>335</v>
+      </c>
       <c r="C155" s="1">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>308</v>
@@ -6640,10 +6699,10 @@
         <v>309</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>18</v>
@@ -6652,18 +6711,24 @@
         <v>339</v>
       </c>
       <c r="J155" s="1">
-        <v>4035</v>
+        <v>40</v>
       </c>
       <c r="K155" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L155" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="156" customHeight="1" spans="1:12">
+      <c r="A156" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>335</v>
+      </c>
       <c r="C156" s="1">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>308</v>
@@ -6672,10 +6737,10 @@
         <v>309</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>18</v>
@@ -6684,18 +6749,24 @@
         <v>341</v>
       </c>
       <c r="J156" s="1">
-        <v>4039</v>
+        <v>40</v>
       </c>
       <c r="K156" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L156" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="1:12">
+      <c r="A157" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>335</v>
+      </c>
       <c r="C157" s="1">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>308</v>
@@ -6704,10 +6775,10 @@
         <v>309</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
@@ -6716,10 +6787,10 @@
         <v>343</v>
       </c>
       <c r="J157" s="1">
-        <v>4037</v>
+        <v>40</v>
       </c>
       <c r="K157" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L157" s="1">
         <v>0</v>
@@ -6727,7 +6798,7 @@
     </row>
     <row r="159" customHeight="1" spans="1:12">
       <c r="C159" s="1">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>308</v>
@@ -6748,167 +6819,135 @@
         <v>346</v>
       </c>
       <c r="J159" s="1">
-        <v>42</v>
+        <v>4035</v>
       </c>
       <c r="K159" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L159" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="3:12">
-      <c r="C162" s="1">
-        <v>601</v>
-      </c>
-      <c r="D162" s="1" t="s">
+    <row r="160" customHeight="1" spans="1:12">
+      <c r="C160" s="1">
+        <v>522</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E160" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G160" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="E162" s="1" t="s">
+      <c r="H160" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I160" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J160" s="1">
+        <v>4039</v>
+      </c>
+      <c r="K160" s="1">
+        <v>5</v>
+      </c>
+      <c r="L160" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:12">
+      <c r="C161" s="1">
+        <v>523</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E161" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F162" s="5" t="s">
-        <v>348</v>
-      </c>
-      <c r="G162" s="5" t="s">
+      <c r="F161" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="G161" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="H162" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I162" s="1" t="s">
+      <c r="H161" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I161" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="J162" s="4">
-        <v>60000007</v>
-      </c>
-      <c r="K162" s="1">
+      <c r="J161" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K161" s="1">
         <v>5</v>
       </c>
-      <c r="L162" s="1">
+      <c r="L161" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="163" customHeight="1" spans="3:12">
       <c r="C163" s="1">
-        <v>602</v>
+        <v>531</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E163" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>309</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="H163" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="J163" s="4">
-        <v>60000008</v>
+        <v>353</v>
+      </c>
+      <c r="J163" s="1">
+        <v>42</v>
       </c>
       <c r="K163" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L163" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="3:12">
-      <c r="C164" s="1">
-        <v>603</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F164" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="G164" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H164" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="J164" s="4">
-        <v>60000006</v>
-      </c>
-      <c r="K164" s="1">
-        <v>5</v>
-      </c>
-      <c r="L164" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" customHeight="1" spans="3:12">
-      <c r="C165" s="1">
-        <v>604</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="G165" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="H165" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="J165" s="4">
-        <v>60000008</v>
-      </c>
-      <c r="K165" s="1">
-        <v>5</v>
-      </c>
-      <c r="L165" s="1">
-        <v>0</v>
-      </c>
-    </row>
     <row r="166" customHeight="1" spans="3:12">
       <c r="C166" s="1">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="H166" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J166" s="4">
-        <v>60000006</v>
+        <v>60000007</v>
       </c>
       <c r="K166" s="1">
         <v>5</v>
@@ -6919,33 +6958,161 @@
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="H167" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="J167" s="4">
-        <v>60000007</v>
+        <v>60000008</v>
       </c>
       <c r="K167" s="1">
         <v>5</v>
       </c>
       <c r="L167" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" customHeight="1" spans="3:12">
+      <c r="C168" s="1">
+        <v>603</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F168" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G168" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H168" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J168" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="K168" s="1">
+        <v>5</v>
+      </c>
+      <c r="L168" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" customHeight="1" spans="3:12">
+      <c r="C169" s="1">
+        <v>604</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H169" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I169" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J169" s="4">
+        <v>60000008</v>
+      </c>
+      <c r="K169" s="1">
+        <v>5</v>
+      </c>
+      <c r="L169" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" customHeight="1" spans="3:12">
+      <c r="C170" s="1">
+        <v>605</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H170" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I170" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J170" s="4">
+        <v>60000006</v>
+      </c>
+      <c r="K170" s="1">
+        <v>5</v>
+      </c>
+      <c r="L170" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" customHeight="1" spans="3:12">
+      <c r="C171" s="1">
+        <v>606</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="J171" s="4">
+        <v>60000007</v>
+      </c>
+      <c r="K171" s="1">
+        <v>5</v>
+      </c>
+      <c r="L171" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -6635,7 +6635,7 @@
         <v>334</v>
       </c>
       <c r="J153" s="1">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="K153" s="1">
         <v>4</v>
@@ -6673,7 +6673,7 @@
         <v>337</v>
       </c>
       <c r="J154" s="1">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K154" s="1">
         <v>4</v>
@@ -6711,7 +6711,7 @@
         <v>339</v>
       </c>
       <c r="J155" s="1">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="K155" s="1">
         <v>4</v>
@@ -6749,7 +6749,7 @@
         <v>341</v>
       </c>
       <c r="J156" s="1">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K156" s="1">
         <v>4</v>
@@ -6787,7 +6787,7 @@
         <v>343</v>
       </c>
       <c r="J157" s="1">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="K157" s="1">
         <v>4</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="368">
   <si>
     <t>Id</t>
   </si>
@@ -1113,6 +1113,24 @@
   </si>
   <si>
     <t>60000008,4111</t>
+  </si>
+  <si>
+    <t>60000016,4111</t>
+  </si>
+  <si>
+    <t>极魔法宝石</t>
+  </si>
+  <si>
+    <t>极道术宝石</t>
+  </si>
+  <si>
+    <t>60000017,4111</t>
+  </si>
+  <si>
+    <t>极物理宝石</t>
+  </si>
+  <si>
+    <t>60000018,4111</t>
   </si>
 </sst>
 </file>
@@ -2116,7 +2134,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L171"/>
+  <dimension ref="A3:L177"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -7116,6 +7134,198 @@
         <v>0</v>
       </c>
     </row>
+    <row r="172" customHeight="1" spans="3:12">
+      <c r="C172" s="1">
+        <v>607</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F172" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="G172" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H172" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J172" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="K172" s="1">
+        <v>5</v>
+      </c>
+      <c r="L172" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" customHeight="1" spans="3:12">
+      <c r="C173" s="1">
+        <v>608</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J173" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="K173" s="1">
+        <v>5</v>
+      </c>
+      <c r="L173" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" customHeight="1" spans="3:12">
+      <c r="C174" s="1">
+        <v>609</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F174" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G174" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H174" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I174" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J174" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="K174" s="1">
+        <v>5</v>
+      </c>
+      <c r="L174" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" customHeight="1" spans="3:12">
+      <c r="C175" s="1">
+        <v>610</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H175" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I175" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J175" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="K175" s="1">
+        <v>5</v>
+      </c>
+      <c r="L175" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" customHeight="1" spans="3:12">
+      <c r="C176" s="1">
+        <v>611</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="J176" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="K176" s="1">
+        <v>5</v>
+      </c>
+      <c r="L176" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" customHeight="1" spans="3:12">
+      <c r="C177" s="1">
+        <v>612</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J177" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="K177" s="1">
+        <v>5</v>
+      </c>
+      <c r="L177" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H5" errorStyle="warning">

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -7177,7 +7177,7 @@
         <v>309</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>356</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -975,6 +975,12 @@
   </si>
   <si>
     <t>金装精华</t>
+  </si>
+  <si>
+    <t>4019,4201</t>
+  </si>
+  <si>
+    <t>暗金精华</t>
   </si>
   <si>
     <t>4023,4111</t>
@@ -2134,7 +2140,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L177"/>
+  <dimension ref="A3:L178"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -6420,16 +6426,16 @@
         <v>316</v>
       </c>
       <c r="G146" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="H146" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>318</v>
-      </c>
       <c r="J146" s="1">
-        <v>4024</v>
+        <v>4026</v>
       </c>
       <c r="K146" s="1">
         <v>5</v>
@@ -6449,19 +6455,19 @@
         <v>309</v>
       </c>
       <c r="F147" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G147" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="G147" s="5" t="s">
+      <c r="H147" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="H147" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="J147" s="1">
-        <v>4025</v>
+        <v>4024</v>
       </c>
       <c r="K147" s="1">
         <v>5</v>
@@ -6472,7 +6478,7 @@
     </row>
     <row r="148" customHeight="1" spans="1:12">
       <c r="C148" s="1">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>308</v>
@@ -6481,22 +6487,22 @@
         <v>309</v>
       </c>
       <c r="F148" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G148" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="H148" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I148" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="H148" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>324</v>
-      </c>
       <c r="J148" s="1">
-        <v>35</v>
+        <v>4025</v>
       </c>
       <c r="K148" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L148" s="1">
         <v>0</v>
@@ -6504,7 +6510,7 @@
     </row>
     <row r="149" customHeight="1" spans="1:12">
       <c r="C149" s="1">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>308</v>
@@ -6513,10 +6519,10 @@
         <v>309</v>
       </c>
       <c r="F149" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="G149" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="H149" s="5" t="s">
         <v>18</v>
@@ -6525,7 +6531,7 @@
         <v>326</v>
       </c>
       <c r="J149" s="1">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K149" s="1">
         <v>4</v>
@@ -6536,7 +6542,7 @@
     </row>
     <row r="150" customHeight="1" spans="1:12">
       <c r="C150" s="1">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>308</v>
@@ -6548,7 +6554,7 @@
         <v>327</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H150" s="5" t="s">
         <v>18</v>
@@ -6557,7 +6563,7 @@
         <v>328</v>
       </c>
       <c r="J150" s="1">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K150" s="1">
         <v>4</v>
@@ -6568,7 +6574,7 @@
     </row>
     <row r="151" customHeight="1" spans="1:12">
       <c r="C151" s="1">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>308</v>
@@ -6580,7 +6586,7 @@
         <v>329</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H151" s="5" t="s">
         <v>18</v>
@@ -6589,7 +6595,7 @@
         <v>330</v>
       </c>
       <c r="J151" s="1">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K151" s="1">
         <v>4</v>
@@ -6600,7 +6606,7 @@
     </row>
     <row r="152" customHeight="1" spans="1:12">
       <c r="C152" s="1">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>308</v>
@@ -6612,7 +6618,7 @@
         <v>331</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>18</v>
@@ -6621,7 +6627,7 @@
         <v>332</v>
       </c>
       <c r="J152" s="1">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K152" s="1">
         <v>4</v>
@@ -6632,7 +6638,7 @@
     </row>
     <row r="153" customHeight="1" spans="1:12">
       <c r="C153" s="1">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>308</v>
@@ -6644,7 +6650,7 @@
         <v>333</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>18</v>
@@ -6653,7 +6659,7 @@
         <v>334</v>
       </c>
       <c r="J153" s="1">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="K153" s="1">
         <v>4</v>
@@ -6663,14 +6669,8 @@
       </c>
     </row>
     <row r="154" customHeight="1" spans="1:12">
-      <c r="A154" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B154" s="1" t="s">
-        <v>335</v>
-      </c>
       <c r="C154" s="1">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>308</v>
@@ -6679,19 +6679,19 @@
         <v>309</v>
       </c>
       <c r="F154" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="G154" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H154" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I154" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="G154" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H154" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I154" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="J154" s="1">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K154" s="1">
         <v>4</v>
@@ -6702,13 +6702,13 @@
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C155" s="1">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>308</v>
@@ -6720,7 +6720,7 @@
         <v>338</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>18</v>
@@ -6729,7 +6729,7 @@
         <v>339</v>
       </c>
       <c r="J155" s="1">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K155" s="1">
         <v>4</v>
@@ -6740,13 +6740,13 @@
     </row>
     <row r="156" customHeight="1" spans="1:12">
       <c r="A156" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C156" s="1">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>308</v>
@@ -6758,7 +6758,7 @@
         <v>340</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>18</v>
@@ -6767,7 +6767,7 @@
         <v>341</v>
       </c>
       <c r="J156" s="1">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K156" s="1">
         <v>4</v>
@@ -6778,13 +6778,13 @@
     </row>
     <row r="157" customHeight="1" spans="1:12">
       <c r="A157" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C157" s="1">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>308</v>
@@ -6796,7 +6796,7 @@
         <v>342</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
@@ -6805,7 +6805,7 @@
         <v>343</v>
       </c>
       <c r="J157" s="1">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K157" s="1">
         <v>4</v>
@@ -6814,41 +6814,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="1:12">
-      <c r="C159" s="1">
-        <v>521</v>
-      </c>
-      <c r="D159" s="1" t="s">
+    <row r="158" customHeight="1" spans="1:12">
+      <c r="A158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="C158" s="1">
+        <v>515</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E159" s="5" t="s">
+      <c r="E158" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F159" s="5" t="s">
+      <c r="F158" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="G159" s="5" t="s">
+      <c r="G158" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="H158" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I158" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="H159" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I159" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="J159" s="1">
-        <v>4035</v>
-      </c>
-      <c r="K159" s="1">
-        <v>5</v>
-      </c>
-      <c r="L159" s="1">
+      <c r="J158" s="1">
+        <v>51</v>
+      </c>
+      <c r="K158" s="1">
+        <v>4</v>
+      </c>
+      <c r="L158" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="160" customHeight="1" spans="1:12">
       <c r="C160" s="1">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>308</v>
@@ -6857,7 +6863,7 @@
         <v>309</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>347</v>
@@ -6869,7 +6875,7 @@
         <v>348</v>
       </c>
       <c r="J160" s="1">
-        <v>4039</v>
+        <v>4035</v>
       </c>
       <c r="K160" s="1">
         <v>5</v>
@@ -6880,7 +6886,7 @@
     </row>
     <row r="161" customHeight="1" spans="3:12">
       <c r="C161" s="1">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>308</v>
@@ -6889,7 +6895,7 @@
         <v>309</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>349</v>
@@ -6901,7 +6907,7 @@
         <v>350</v>
       </c>
       <c r="J161" s="1">
-        <v>4037</v>
+        <v>4039</v>
       </c>
       <c r="K161" s="1">
         <v>5</v>
@@ -6910,94 +6916,94 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" customHeight="1" spans="3:12">
-      <c r="C163" s="1">
+    <row r="162" customHeight="1" spans="3:12">
+      <c r="C162" s="1">
+        <v>523</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="F162" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="G162" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="H162" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I162" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="J162" s="1">
+        <v>4037</v>
+      </c>
+      <c r="K162" s="1">
+        <v>5</v>
+      </c>
+      <c r="L162" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="3:12">
+      <c r="C164" s="1">
         <v>531</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="D164" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E163" s="5" t="s">
+      <c r="E164" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="F163" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="G163" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="H163" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I163" s="1" t="s">
+      <c r="F164" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="J163" s="1">
+      <c r="G164" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H164" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="J164" s="1">
         <v>42</v>
       </c>
-      <c r="K163" s="1">
+      <c r="K164" s="1">
         <v>4</v>
       </c>
-      <c r="L163" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" customHeight="1" spans="3:12">
-      <c r="C166" s="1">
-        <v>601</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="G166" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="H166" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I166" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="J166" s="4">
-        <v>60000007</v>
-      </c>
-      <c r="K166" s="1">
-        <v>5</v>
-      </c>
-      <c r="L166" s="1">
+      <c r="L164" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="167" customHeight="1" spans="3:12">
       <c r="C167" s="1">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H167" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J167" s="4">
-        <v>60000008</v>
+        <v>60000007</v>
       </c>
       <c r="K167" s="1">
         <v>5</v>
@@ -7008,19 +7014,19 @@
     </row>
     <row r="168" customHeight="1" spans="3:12">
       <c r="C168" s="1">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H168" s="5" t="s">
         <v>18</v>
@@ -7029,7 +7035,7 @@
         <v>360</v>
       </c>
       <c r="J168" s="4">
-        <v>60000006</v>
+        <v>60000008</v>
       </c>
       <c r="K168" s="1">
         <v>5</v>
@@ -7040,28 +7046,28 @@
     </row>
     <row r="169" customHeight="1" spans="3:12">
       <c r="C169" s="1">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H169" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J169" s="4">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="K169" s="1">
         <v>5</v>
@@ -7072,10 +7078,10 @@
     </row>
     <row r="170" customHeight="1" spans="3:12">
       <c r="C170" s="1">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>309</v>
@@ -7084,7 +7090,7 @@
         <v>361</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H170" s="5" t="s">
         <v>18</v>
@@ -7093,7 +7099,7 @@
         <v>360</v>
       </c>
       <c r="J170" s="4">
-        <v>60000006</v>
+        <v>60000008</v>
       </c>
       <c r="K170" s="1">
         <v>5</v>
@@ -7104,28 +7110,28 @@
     </row>
     <row r="171" customHeight="1" spans="3:12">
       <c r="C171" s="1">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H171" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J171" s="4">
-        <v>60000007</v>
+        <v>60000006</v>
       </c>
       <c r="K171" s="1">
         <v>5</v>
@@ -7136,28 +7142,28 @@
     </row>
     <row r="172" customHeight="1" spans="3:12">
       <c r="C172" s="1">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H172" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I172" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="J172" s="4">
-        <v>60000017</v>
+        <v>60000007</v>
       </c>
       <c r="K172" s="1">
         <v>5</v>
@@ -7168,28 +7174,28 @@
     </row>
     <row r="173" customHeight="1" spans="3:12">
       <c r="C173" s="1">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H173" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J173" s="4">
-        <v>60000018</v>
+        <v>60000017</v>
       </c>
       <c r="K173" s="1">
         <v>5</v>
@@ -7200,19 +7206,19 @@
     </row>
     <row r="174" customHeight="1" spans="3:12">
       <c r="C174" s="1">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
@@ -7221,7 +7227,7 @@
         <v>366</v>
       </c>
       <c r="J174" s="4">
-        <v>60000016</v>
+        <v>60000018</v>
       </c>
       <c r="K174" s="1">
         <v>5</v>
@@ -7232,28 +7238,28 @@
     </row>
     <row r="175" customHeight="1" spans="3:12">
       <c r="C175" s="1">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="J175" s="4">
-        <v>60000018</v>
+        <v>60000016</v>
       </c>
       <c r="K175" s="1">
         <v>5</v>
@@ -7264,10 +7270,10 @@
     </row>
     <row r="176" customHeight="1" spans="3:12">
       <c r="C176" s="1">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>309</v>
@@ -7276,7 +7282,7 @@
         <v>367</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H176" s="5" t="s">
         <v>18</v>
@@ -7285,7 +7291,7 @@
         <v>366</v>
       </c>
       <c r="J176" s="4">
-        <v>60000016</v>
+        <v>60000018</v>
       </c>
       <c r="K176" s="1">
         <v>5</v>
@@ -7296,33 +7302,65 @@
     </row>
     <row r="177" customHeight="1" spans="3:12">
       <c r="C177" s="1">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>309</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H177" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="J177" s="4">
-        <v>60000017</v>
+        <v>60000016</v>
       </c>
       <c r="K177" s="1">
         <v>5</v>
       </c>
       <c r="L177" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" customHeight="1" spans="3:12">
+      <c r="C178" s="1">
+        <v>612</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="H178" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I178" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J178" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="K178" s="1">
+        <v>5</v>
+      </c>
+      <c r="L178" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -971,7 +971,7 @@
     <t>4011,4201</t>
   </si>
   <si>
-    <t>10,50000</t>
+    <t>10,10000</t>
   </si>
   <si>
     <t>金装精华</t>
@@ -980,6 +980,9 @@
     <t>4019,4201</t>
   </si>
   <si>
+    <t>10,20000</t>
+  </si>
+  <si>
     <t>暗金精华</t>
   </si>
   <si>
@@ -1089,9 +1092,6 @@
   </si>
   <si>
     <t>4112,4111</t>
-  </si>
-  <si>
-    <t>10,10000</t>
   </si>
   <si>
     <t>12阶技能</t>
@@ -6426,13 +6426,13 @@
         <v>316</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H146" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I146" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J146" s="1">
         <v>4026</v>
@@ -6455,16 +6455,16 @@
         <v>309</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H147" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I147" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J147" s="1">
         <v>4024</v>
@@ -6487,16 +6487,16 @@
         <v>309</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H148" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J148" s="1">
         <v>4025</v>
@@ -6519,16 +6519,16 @@
         <v>309</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H149" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="J149" s="1">
         <v>35</v>
@@ -6551,16 +6551,16 @@
         <v>309</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H150" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J150" s="1">
         <v>37</v>
@@ -6583,16 +6583,16 @@
         <v>309</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H151" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I151" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J151" s="1">
         <v>38</v>
@@ -6615,16 +6615,16 @@
         <v>309</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="J152" s="1">
         <v>39</v>
@@ -6647,16 +6647,16 @@
         <v>309</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="J153" s="1">
         <v>40</v>
@@ -6679,16 +6679,16 @@
         <v>309</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H154" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J154" s="1">
         <v>47</v>
@@ -6702,10 +6702,10 @@
     </row>
     <row r="155" customHeight="1" spans="1:12">
       <c r="A155" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C155" s="1">
         <v>512</v>
@@ -6717,16 +6717,16 @@
         <v>309</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J155" s="1">
         <v>48</v>
@@ -6740,10 +6740,10 @@
     </row>
     <row r="156" customHeight="1" spans="1:12">
       <c r="A156" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C156" s="1">
         <v>513</v>
@@ -6755,16 +6755,16 @@
         <v>309</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J156" s="1">
         <v>49</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="157" customHeight="1" spans="1:12">
       <c r="A157" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C157" s="1">
         <v>514</v>
@@ -6793,16 +6793,16 @@
         <v>309</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J157" s="1">
         <v>50</v>
@@ -6816,10 +6816,10 @@
     </row>
     <row r="158" customHeight="1" spans="1:12">
       <c r="A158" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C158" s="1">
         <v>515</v>
@@ -6831,16 +6831,16 @@
         <v>309</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J158" s="1">
         <v>51</v>
@@ -6863,16 +6863,16 @@
         <v>309</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J160" s="1">
         <v>4035</v>
@@ -6895,16 +6895,16 @@
         <v>309</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="J161" s="1">
         <v>4039</v>
@@ -6927,16 +6927,16 @@
         <v>309</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J162" s="1">
         <v>4037</v>
@@ -6959,10 +6959,10 @@
         <v>309</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>354</v>
+        <v>314</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>18</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="386">
   <si>
     <t>Id</t>
   </si>
@@ -368,6 +368,24 @@
     <t>斗笠33阶</t>
   </si>
   <si>
+    <t>133,4007</t>
+  </si>
+  <si>
+    <t>1,1400000000</t>
+  </si>
+  <si>
+    <t>斗笠34阶</t>
+  </si>
+  <si>
+    <t>134,4007</t>
+  </si>
+  <si>
+    <t>1,1600000000</t>
+  </si>
+  <si>
+    <t>斗笠35阶</t>
+  </si>
+  <si>
     <t>护盾</t>
   </si>
   <si>
@@ -563,6 +581,15 @@
     <t>护盾33阶</t>
   </si>
   <si>
+    <t>233,4007</t>
+  </si>
+  <si>
+    <t>234,4007</t>
+  </si>
+  <si>
+    <t>护盾34阶</t>
+  </si>
+  <si>
     <t>神符</t>
   </si>
   <si>
@@ -758,6 +785,15 @@
     <t>神符33阶</t>
   </si>
   <si>
+    <t>333,4007</t>
+  </si>
+  <si>
+    <t>334,4007</t>
+  </si>
+  <si>
+    <t>神符34阶</t>
+  </si>
+  <si>
     <t>魔石</t>
   </si>
   <si>
@@ -951,6 +987,18 @@
   </si>
   <si>
     <t>魔石33阶</t>
+  </si>
+  <si>
+    <t>433,4007</t>
+  </si>
+  <si>
+    <t>魔石34阶</t>
+  </si>
+  <si>
+    <t>434,4007</t>
+  </si>
+  <si>
+    <t>魔石35阶</t>
   </si>
   <si>
     <t>其他</t>
@@ -2140,7 +2188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L178"/>
+  <dimension ref="A3:L184"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -3276,126 +3324,126 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" customHeight="1" spans="3:12">
-      <c r="C40" s="1">
-        <v>201</v>
-      </c>
-      <c r="D40" s="1" t="s">
+    <row r="38" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>133</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="G40" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="1" t="s">
+      <c r="H38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J40" s="1">
-        <v>202</v>
-      </c>
-      <c r="K40" s="1">
-        <v>2</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
-      <c r="C41" s="1">
-        <v>202</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="5" t="s">
+      <c r="J38" s="1">
+        <v>134</v>
+      </c>
+      <c r="K38" s="1">
+        <v>2</v>
+      </c>
+      <c r="L38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>134</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="G41" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I41" s="1" t="s">
+      <c r="G39" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="J41" s="1">
-        <v>203</v>
-      </c>
-      <c r="K41" s="1">
-        <v>2</v>
-      </c>
-      <c r="L41" s="1">
+      <c r="H39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J39" s="1">
+        <v>135</v>
+      </c>
+      <c r="K39" s="1">
+        <v>2</v>
+      </c>
+      <c r="L39" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="42" customHeight="1" spans="3:12">
       <c r="C42" s="1">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J42" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K42" s="1">
         <v>2</v>
       </c>
       <c r="L42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" customHeight="1" spans="3:12">
       <c r="C43" s="1">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G43" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J43" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="K43" s="1">
         <v>2</v>
@@ -3406,28 +3454,28 @@
     </row>
     <row r="44" customHeight="1" spans="3:12">
       <c r="C44" s="1">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G44" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J44" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K44" s="1">
         <v>2</v>
@@ -3438,28 +3486,28 @@
     </row>
     <row r="45" customHeight="1" spans="3:12">
       <c r="C45" s="1">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G45" s="5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H45" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J45" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="K45" s="1">
         <v>2</v>
@@ -3470,28 +3518,28 @@
     </row>
     <row r="46" customHeight="1" spans="3:12">
       <c r="C46" s="1">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G46" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J46" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K46" s="1">
         <v>2</v>
@@ -3502,28 +3550,28 @@
     </row>
     <row r="47" customHeight="1" spans="3:12">
       <c r="C47" s="1">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G47" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="J47" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="K47" s="1">
         <v>2</v>
@@ -3534,28 +3582,28 @@
     </row>
     <row r="48" customHeight="1" spans="3:12">
       <c r="C48" s="1">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G48" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H48" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J48" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="K48" s="1">
         <v>2</v>
@@ -3566,28 +3614,28 @@
     </row>
     <row r="49" customHeight="1" spans="3:12">
       <c r="C49" s="1">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J49" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K49" s="1">
         <v>2</v>
@@ -3598,28 +3646,28 @@
     </row>
     <row r="50" customHeight="1" spans="3:12">
       <c r="C50" s="1">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J50" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K50" s="1">
         <v>2</v>
@@ -3630,28 +3678,28 @@
     </row>
     <row r="51" customHeight="1" spans="3:12">
       <c r="C51" s="1">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G51" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J51" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="K51" s="1">
         <v>2</v>
@@ -3662,28 +3710,28 @@
     </row>
     <row r="52" customHeight="1" spans="3:12">
       <c r="C52" s="1">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J52" s="1">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="K52" s="1">
         <v>2</v>
@@ -3694,28 +3742,28 @@
     </row>
     <row r="53" customHeight="1" spans="3:12">
       <c r="C53" s="1">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J53" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K53" s="1">
         <v>2</v>
@@ -3726,28 +3774,28 @@
     </row>
     <row r="54" customHeight="1" spans="3:12">
       <c r="C54" s="1">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G54" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="H54" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J54" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K54" s="1">
         <v>2</v>
@@ -3758,28 +3806,28 @@
     </row>
     <row r="55" customHeight="1" spans="3:12">
       <c r="C55" s="1">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G55" s="5" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H55" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J55" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K55" s="1">
         <v>2</v>
@@ -3790,28 +3838,28 @@
     </row>
     <row r="56" customHeight="1" spans="3:12">
       <c r="C56" s="1">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G56" s="5" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J56" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="K56" s="1">
         <v>2</v>
@@ -3822,28 +3870,28 @@
     </row>
     <row r="57" customHeight="1" spans="3:12">
       <c r="C57" s="1">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G57" s="5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="H57" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J57" s="1">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="K57" s="1">
         <v>2</v>
@@ -3854,28 +3902,28 @@
     </row>
     <row r="58" customHeight="1" spans="3:12">
       <c r="C58" s="1">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G58" s="5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H58" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J58" s="1">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="K58" s="1">
         <v>2</v>
@@ -3886,28 +3934,28 @@
     </row>
     <row r="59" customHeight="1" spans="3:12">
       <c r="C59" s="1">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H59" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J59" s="1">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="K59" s="1">
         <v>2</v>
@@ -3918,28 +3966,28 @@
     </row>
     <row r="60" customHeight="1" spans="3:12">
       <c r="C60" s="1">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H60" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J60" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="K60" s="1">
         <v>2</v>
@@ -3950,28 +3998,28 @@
     </row>
     <row r="61" customHeight="1" spans="3:12">
       <c r="C61" s="1">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G61" s="5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H61" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="J61" s="1">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="K61" s="1">
         <v>2</v>
@@ -3982,28 +4030,28 @@
     </row>
     <row r="62" customHeight="1" spans="3:12">
       <c r="C62" s="1">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H62" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J62" s="1">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="K62" s="1">
         <v>2</v>
@@ -4014,28 +4062,28 @@
     </row>
     <row r="63" customHeight="1" spans="3:12">
       <c r="C63" s="1">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G63" s="5" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J63" s="1">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="K63" s="1">
         <v>2</v>
@@ -4046,28 +4094,28 @@
     </row>
     <row r="64" customHeight="1" spans="3:12">
       <c r="C64" s="1">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E64" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="H64" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J64" s="1">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K64" s="1">
         <v>2</v>
@@ -4078,28 +4126,28 @@
     </row>
     <row r="65" customHeight="1" spans="3:12">
       <c r="C65" s="1">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G65" s="5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J65" s="1">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="K65" s="1">
         <v>2</v>
@@ -4110,28 +4158,28 @@
     </row>
     <row r="66" customHeight="1" spans="3:12">
       <c r="C66" s="1">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G66" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="J66" s="1">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="K66" s="1">
         <v>2</v>
@@ -4142,28 +4190,28 @@
     </row>
     <row r="67" customHeight="1" spans="3:12">
       <c r="C67" s="1">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G67" s="5" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="J67" s="1">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K67" s="1">
         <v>2</v>
@@ -4174,28 +4222,28 @@
     </row>
     <row r="68" customHeight="1" spans="3:12">
       <c r="C68" s="1">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J68" s="1">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K68" s="1">
         <v>2</v>
@@ -4206,28 +4254,28 @@
     </row>
     <row r="69" customHeight="1" spans="3:12">
       <c r="C69" s="1">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E69" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="J69" s="1">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K69" s="1">
         <v>2</v>
@@ -4238,28 +4286,28 @@
     </row>
     <row r="70" customHeight="1" spans="3:12">
       <c r="C70" s="1">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J70" s="1">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="K70" s="1">
         <v>2</v>
@@ -4270,220 +4318,220 @@
     </row>
     <row r="71" customHeight="1" spans="3:12">
       <c r="C71" s="1">
+        <v>230</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H71" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="J71" s="1">
+        <v>231</v>
+      </c>
+      <c r="K71" s="1">
+        <v>2</v>
+      </c>
+      <c r="L71" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" customHeight="1" spans="3:12">
+      <c r="C72" s="1">
+        <v>231</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G72" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J72" s="1">
         <v>232</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="G71" s="5" t="s">
+      <c r="K72" s="1">
+        <v>2</v>
+      </c>
+      <c r="L72" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" customHeight="1" spans="3:12">
+      <c r="C73" s="1">
+        <v>232</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="H71" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I71" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="J71" s="1">
+      <c r="H73" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J73" s="1">
         <v>233</v>
       </c>
-      <c r="K71" s="1">
-        <v>2</v>
-      </c>
-      <c r="L71" s="1">
+      <c r="K73" s="1">
+        <v>2</v>
+      </c>
+      <c r="L73" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="74" customHeight="1" spans="3:12">
       <c r="C74" s="1">
-        <v>301</v>
+        <v>233</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="G74" s="5" t="s">
-        <v>17</v>
+        <v>114</v>
       </c>
       <c r="H74" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J74" s="1">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="K74" s="1">
         <v>2</v>
       </c>
       <c r="L74" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" customHeight="1" spans="3:12">
       <c r="C75" s="1">
-        <v>302</v>
+        <v>234</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>178</v>
+        <v>119</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H75" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J75" s="1">
-        <v>303</v>
+        <v>235</v>
       </c>
       <c r="K75" s="1">
         <v>2</v>
       </c>
       <c r="L75" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" customHeight="1" spans="3:12">
-      <c r="C76" s="1">
-        <v>303</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H76" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I76" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J76" s="1">
-        <v>304</v>
-      </c>
-      <c r="K76" s="1">
-        <v>2</v>
-      </c>
-      <c r="L76" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customHeight="1" spans="3:12">
-      <c r="C77" s="1">
-        <v>304</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I77" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J77" s="1">
-        <v>305</v>
-      </c>
-      <c r="K77" s="1">
-        <v>2</v>
-      </c>
-      <c r="L77" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:12">
       <c r="C78" s="1">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H78" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J78" s="1">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="K78" s="1">
         <v>2</v>
       </c>
       <c r="L78" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:12">
       <c r="C79" s="1">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G79" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="H79" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J79" s="1">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="K79" s="1">
         <v>2</v>
@@ -4494,28 +4542,28 @@
     </row>
     <row r="80" customHeight="1" spans="3:12">
       <c r="C80" s="1">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E80" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G80" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="H80" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J80" s="1">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="K80" s="1">
         <v>2</v>
@@ -4526,28 +4574,28 @@
     </row>
     <row r="81" customHeight="1" spans="3:12">
       <c r="C81" s="1">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="H81" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J81" s="1">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="K81" s="1">
         <v>2</v>
@@ -4558,28 +4606,28 @@
     </row>
     <row r="82" customHeight="1" spans="3:12">
       <c r="C82" s="1">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G82" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="H82" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J82" s="1">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="K82" s="1">
         <v>2</v>
@@ -4590,28 +4638,28 @@
     </row>
     <row r="83" customHeight="1" spans="3:12">
       <c r="C83" s="1">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H83" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J83" s="1">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="K83" s="1">
         <v>2</v>
@@ -4622,28 +4670,28 @@
     </row>
     <row r="84" customHeight="1" spans="3:12">
       <c r="C84" s="1">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E84" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H84" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J84" s="1">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="K84" s="1">
         <v>2</v>
@@ -4654,28 +4702,28 @@
     </row>
     <row r="85" customHeight="1" spans="3:12">
       <c r="C85" s="1">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E85" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="H85" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J85" s="1">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K85" s="1">
         <v>2</v>
@@ -4686,28 +4734,28 @@
     </row>
     <row r="86" customHeight="1" spans="3:12">
       <c r="C86" s="1">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H86" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J86" s="1">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K86" s="1">
         <v>2</v>
@@ -4718,28 +4766,28 @@
     </row>
     <row r="87" customHeight="1" spans="3:12">
       <c r="C87" s="1">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E87" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="H87" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J87" s="1">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="K87" s="1">
         <v>2</v>
@@ -4750,28 +4798,28 @@
     </row>
     <row r="88" customHeight="1" spans="3:12">
       <c r="C88" s="1">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E88" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H88" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J88" s="1">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="K88" s="1">
         <v>2</v>
@@ -4782,28 +4830,28 @@
     </row>
     <row r="89" customHeight="1" spans="3:12">
       <c r="C89" s="1">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E89" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="H89" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J89" s="1">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K89" s="1">
         <v>2</v>
@@ -4814,28 +4862,28 @@
     </row>
     <row r="90" customHeight="1" spans="3:12">
       <c r="C90" s="1">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="H90" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J90" s="1">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="K90" s="1">
         <v>2</v>
@@ -4846,28 +4894,28 @@
     </row>
     <row r="91" customHeight="1" spans="3:12">
       <c r="C91" s="1">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E91" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H91" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J91" s="1">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="K91" s="1">
         <v>2</v>
@@ -4878,28 +4926,28 @@
     </row>
     <row r="92" customHeight="1" spans="3:12">
       <c r="C92" s="1">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H92" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J92" s="1">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="K92" s="1">
         <v>2</v>
@@ -4910,28 +4958,28 @@
     </row>
     <row r="93" customHeight="1" spans="3:12">
       <c r="C93" s="1">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H93" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J93" s="1">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="K93" s="1">
         <v>2</v>
@@ -4942,28 +4990,28 @@
     </row>
     <row r="94" customHeight="1" spans="3:12">
       <c r="C94" s="1">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E94" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="H94" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J94" s="1">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="K94" s="1">
         <v>2</v>
@@ -4974,28 +5022,28 @@
     </row>
     <row r="95" customHeight="1" spans="3:12">
       <c r="C95" s="1">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E95" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="H95" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J95" s="1">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="K95" s="1">
         <v>2</v>
@@ -5006,28 +5054,28 @@
     </row>
     <row r="96" customHeight="1" spans="3:12">
       <c r="C96" s="1">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E96" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H96" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J96" s="1">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="K96" s="1">
         <v>2</v>
@@ -5038,28 +5086,28 @@
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E97" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="H97" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I97" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J97" s="1">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="K97" s="1">
         <v>2</v>
@@ -5070,28 +5118,28 @@
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="H98" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J98" s="1">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="K98" s="1">
         <v>2</v>
@@ -5102,28 +5150,28 @@
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G99" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J99" s="1">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="K99" s="1">
         <v>2</v>
@@ -5134,28 +5182,28 @@
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E100" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G100" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H100" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J100" s="1">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="K100" s="1">
         <v>2</v>
@@ -5166,28 +5214,28 @@
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E101" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="H101" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J101" s="1">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="K101" s="1">
         <v>2</v>
@@ -5198,28 +5246,28 @@
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E102" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H102" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J102" s="1">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="K102" s="1">
         <v>2</v>
@@ -5230,28 +5278,28 @@
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E103" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G103" s="5" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="H103" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J103" s="1">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K103" s="1">
         <v>2</v>
@@ -5262,28 +5310,28 @@
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E104" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G104" s="5" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="H104" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J104" s="1">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="K104" s="1">
         <v>2</v>
@@ -5294,92 +5342,156 @@
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="E105" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G105" s="5" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H105" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J105" s="1">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="K105" s="1">
         <v>2</v>
       </c>
       <c r="L105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" customHeight="1" spans="3:12">
+      <c r="C106" s="1">
+        <v>329</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="G106" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H106" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J106" s="1">
+        <v>330</v>
+      </c>
+      <c r="K106" s="1">
+        <v>2</v>
+      </c>
+      <c r="L106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" customHeight="1" spans="3:12">
+      <c r="C107" s="1">
+        <v>330</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H107" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J107" s="1">
+        <v>331</v>
+      </c>
+      <c r="K107" s="1">
+        <v>2</v>
+      </c>
+      <c r="L107" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>401</v>
+        <v>331</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="E108" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="H108" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="J108" s="1">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="K108" s="1">
         <v>2</v>
       </c>
       <c r="L108" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>402</v>
+        <v>332</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="E109" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="H109" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J109" s="1">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="K109" s="1">
         <v>2</v>
@@ -5390,28 +5502,28 @@
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>403</v>
+        <v>333</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="E110" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="H110" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J110" s="1">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="K110" s="1">
         <v>2</v>
@@ -5422,106 +5534,42 @@
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>404</v>
+        <v>334</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="E111" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="H111" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="J111" s="1">
-        <v>405</v>
+        <v>335</v>
       </c>
       <c r="K111" s="1">
         <v>2</v>
       </c>
       <c r="L111" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="112" customHeight="1" spans="3:12">
-      <c r="C112" s="1">
-        <v>405</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H112" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I112" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J112" s="1">
-        <v>406</v>
-      </c>
-      <c r="K112" s="1">
-        <v>2</v>
-      </c>
-      <c r="L112" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="113" customHeight="1" spans="3:12">
-      <c r="C113" s="1">
-        <v>406</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E113" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F113" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="G113" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H113" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I113" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="J113" s="1">
-        <v>407</v>
-      </c>
-      <c r="K113" s="1">
-        <v>2</v>
-      </c>
-      <c r="L113" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:12">
       <c r="C114" s="1">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E114" s="5" t="s">
         <v>15</v>
@@ -5530,7 +5578,7 @@
         <v>256</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="H114" s="5" t="s">
         <v>18</v>
@@ -5539,21 +5587,21 @@
         <v>257</v>
       </c>
       <c r="J114" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="K114" s="1">
         <v>2</v>
       </c>
       <c r="L114" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:12">
       <c r="C115" s="1">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E115" s="5" t="s">
         <v>15</v>
@@ -5562,7 +5610,7 @@
         <v>258</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="H115" s="5" t="s">
         <v>18</v>
@@ -5571,7 +5619,7 @@
         <v>259</v>
       </c>
       <c r="J115" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="K115" s="1">
         <v>2</v>
@@ -5582,10 +5630,10 @@
     </row>
     <row r="116" customHeight="1" spans="3:12">
       <c r="C116" s="1">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E116" s="5" t="s">
         <v>15</v>
@@ -5594,7 +5642,7 @@
         <v>260</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="H116" s="5" t="s">
         <v>18</v>
@@ -5603,7 +5651,7 @@
         <v>261</v>
       </c>
       <c r="J116" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="K116" s="1">
         <v>2</v>
@@ -5614,10 +5662,10 @@
     </row>
     <row r="117" customHeight="1" spans="3:12">
       <c r="C117" s="1">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E117" s="5" t="s">
         <v>15</v>
@@ -5626,7 +5674,7 @@
         <v>262</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H117" s="5" t="s">
         <v>18</v>
@@ -5635,7 +5683,7 @@
         <v>263</v>
       </c>
       <c r="J117" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="K117" s="1">
         <v>2</v>
@@ -5646,10 +5694,10 @@
     </row>
     <row r="118" customHeight="1" spans="3:12">
       <c r="C118" s="1">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E118" s="5" t="s">
         <v>15</v>
@@ -5658,7 +5706,7 @@
         <v>264</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="H118" s="5" t="s">
         <v>18</v>
@@ -5667,7 +5715,7 @@
         <v>265</v>
       </c>
       <c r="J118" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="K118" s="1">
         <v>2</v>
@@ -5678,10 +5726,10 @@
     </row>
     <row r="119" customHeight="1" spans="3:12">
       <c r="C119" s="1">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E119" s="5" t="s">
         <v>15</v>
@@ -5690,7 +5738,7 @@
         <v>266</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
@@ -5699,7 +5747,7 @@
         <v>267</v>
       </c>
       <c r="J119" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="K119" s="1">
         <v>2</v>
@@ -5710,10 +5758,10 @@
     </row>
     <row r="120" customHeight="1" spans="3:12">
       <c r="C120" s="1">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>15</v>
@@ -5722,7 +5770,7 @@
         <v>268</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>18</v>
@@ -5731,7 +5779,7 @@
         <v>269</v>
       </c>
       <c r="J120" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="K120" s="1">
         <v>2</v>
@@ -5742,10 +5790,10 @@
     </row>
     <row r="121" customHeight="1" spans="3:12">
       <c r="C121" s="1">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E121" s="5" t="s">
         <v>15</v>
@@ -5754,7 +5802,7 @@
         <v>270</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="H121" s="5" t="s">
         <v>18</v>
@@ -5763,7 +5811,7 @@
         <v>271</v>
       </c>
       <c r="J121" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="K121" s="1">
         <v>2</v>
@@ -5774,10 +5822,10 @@
     </row>
     <row r="122" customHeight="1" spans="3:12">
       <c r="C122" s="1">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>15</v>
@@ -5786,7 +5834,7 @@
         <v>272</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H122" s="5" t="s">
         <v>18</v>
@@ -5795,7 +5843,7 @@
         <v>273</v>
       </c>
       <c r="J122" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="K122" s="1">
         <v>2</v>
@@ -5806,10 +5854,10 @@
     </row>
     <row r="123" customHeight="1" spans="3:12">
       <c r="C123" s="1">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E123" s="5" t="s">
         <v>15</v>
@@ -5818,7 +5866,7 @@
         <v>274</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H123" s="5" t="s">
         <v>18</v>
@@ -5827,7 +5875,7 @@
         <v>275</v>
       </c>
       <c r="J123" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="K123" s="1">
         <v>2</v>
@@ -5838,10 +5886,10 @@
     </row>
     <row r="124" customHeight="1" spans="3:12">
       <c r="C124" s="1">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E124" s="5" t="s">
         <v>15</v>
@@ -5850,7 +5898,7 @@
         <v>276</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H124" s="5" t="s">
         <v>18</v>
@@ -5859,7 +5907,7 @@
         <v>277</v>
       </c>
       <c r="J124" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="K124" s="1">
         <v>2</v>
@@ -5870,10 +5918,10 @@
     </row>
     <row r="125" customHeight="1" spans="3:12">
       <c r="C125" s="1">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>15</v>
@@ -5882,7 +5930,7 @@
         <v>278</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="H125" s="5" t="s">
         <v>18</v>
@@ -5891,7 +5939,7 @@
         <v>279</v>
       </c>
       <c r="J125" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="K125" s="1">
         <v>2</v>
@@ -5902,10 +5950,10 @@
     </row>
     <row r="126" customHeight="1" spans="3:12">
       <c r="C126" s="1">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>15</v>
@@ -5914,7 +5962,7 @@
         <v>280</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="H126" s="5" t="s">
         <v>18</v>
@@ -5923,7 +5971,7 @@
         <v>281</v>
       </c>
       <c r="J126" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="K126" s="1">
         <v>2</v>
@@ -5934,10 +5982,10 @@
     </row>
     <row r="127" customHeight="1" spans="3:12">
       <c r="C127" s="1">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E127" s="5" t="s">
         <v>15</v>
@@ -5946,7 +5994,7 @@
         <v>282</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="H127" s="5" t="s">
         <v>18</v>
@@ -5955,7 +6003,7 @@
         <v>283</v>
       </c>
       <c r="J127" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="K127" s="1">
         <v>2</v>
@@ -5966,10 +6014,10 @@
     </row>
     <row r="128" customHeight="1" spans="3:12">
       <c r="C128" s="1">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E128" s="5" t="s">
         <v>15</v>
@@ -5978,7 +6026,7 @@
         <v>284</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="H128" s="5" t="s">
         <v>18</v>
@@ -5987,7 +6035,7 @@
         <v>285</v>
       </c>
       <c r="J128" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K128" s="1">
         <v>2</v>
@@ -5998,10 +6046,10 @@
     </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E129" s="5" t="s">
         <v>15</v>
@@ -6010,7 +6058,7 @@
         <v>286</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="H129" s="5" t="s">
         <v>18</v>
@@ -6019,7 +6067,7 @@
         <v>287</v>
       </c>
       <c r="J129" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="K129" s="1">
         <v>2</v>
@@ -6030,10 +6078,10 @@
     </row>
     <row r="130" customHeight="1" spans="3:12">
       <c r="C130" s="1">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>15</v>
@@ -6042,7 +6090,7 @@
         <v>288</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="H130" s="5" t="s">
         <v>18</v>
@@ -6051,7 +6099,7 @@
         <v>289</v>
       </c>
       <c r="J130" s="1">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="K130" s="1">
         <v>2</v>
@@ -6062,10 +6110,10 @@
     </row>
     <row r="131" customHeight="1" spans="3:12">
       <c r="C131" s="1">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E131" s="5" t="s">
         <v>15</v>
@@ -6074,7 +6122,7 @@
         <v>290</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="H131" s="5" t="s">
         <v>18</v>
@@ -6083,7 +6131,7 @@
         <v>291</v>
       </c>
       <c r="J131" s="1">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="K131" s="1">
         <v>2</v>
@@ -6094,10 +6142,10 @@
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E132" s="5" t="s">
         <v>15</v>
@@ -6106,7 +6154,7 @@
         <v>292</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="H132" s="5" t="s">
         <v>18</v>
@@ -6115,7 +6163,7 @@
         <v>293</v>
       </c>
       <c r="J132" s="1">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="K132" s="1">
         <v>2</v>
@@ -6126,10 +6174,10 @@
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E133" s="5" t="s">
         <v>15</v>
@@ -6138,7 +6186,7 @@
         <v>294</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="H133" s="5" t="s">
         <v>18</v>
@@ -6147,7 +6195,7 @@
         <v>295</v>
       </c>
       <c r="J133" s="1">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="K133" s="1">
         <v>2</v>
@@ -6158,10 +6206,10 @@
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>15</v>
@@ -6170,7 +6218,7 @@
         <v>296</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="H134" s="5" t="s">
         <v>18</v>
@@ -6179,7 +6227,7 @@
         <v>297</v>
       </c>
       <c r="J134" s="1">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="K134" s="1">
         <v>2</v>
@@ -6190,10 +6238,10 @@
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E135" s="5" t="s">
         <v>15</v>
@@ -6202,7 +6250,7 @@
         <v>298</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="H135" s="5" t="s">
         <v>18</v>
@@ -6211,7 +6259,7 @@
         <v>299</v>
       </c>
       <c r="J135" s="1">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="K135" s="1">
         <v>2</v>
@@ -6222,10 +6270,10 @@
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E136" s="5" t="s">
         <v>15</v>
@@ -6234,7 +6282,7 @@
         <v>300</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H136" s="5" t="s">
         <v>18</v>
@@ -6243,7 +6291,7 @@
         <v>301</v>
       </c>
       <c r="J136" s="1">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="K136" s="1">
         <v>2</v>
@@ -6254,10 +6302,10 @@
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E137" s="5" t="s">
         <v>15</v>
@@ -6266,7 +6314,7 @@
         <v>302</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="H137" s="5" t="s">
         <v>18</v>
@@ -6275,7 +6323,7 @@
         <v>303</v>
       </c>
       <c r="J137" s="1">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="K137" s="1">
         <v>2</v>
@@ -6286,10 +6334,10 @@
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>15</v>
@@ -6298,7 +6346,7 @@
         <v>304</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H138" s="5" t="s">
         <v>18</v>
@@ -6307,7 +6355,7 @@
         <v>305</v>
       </c>
       <c r="J138" s="1">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="K138" s="1">
         <v>2</v>
@@ -6318,10 +6366,10 @@
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="E139" s="5" t="s">
         <v>15</v>
@@ -6330,7 +6378,7 @@
         <v>306</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="H139" s="5" t="s">
         <v>18</v>
@@ -6339,254 +6387,318 @@
         <v>307</v>
       </c>
       <c r="J139" s="1">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="K139" s="1">
         <v>2</v>
       </c>
       <c r="L139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="3:12">
+      <c r="C140" s="1">
+        <v>427</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E140" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="G140" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H140" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I140" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="J140" s="1">
+        <v>428</v>
+      </c>
+      <c r="K140" s="1">
+        <v>2</v>
+      </c>
+      <c r="L140" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="3:12">
+      <c r="C141" s="1">
+        <v>428</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H141" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I141" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="J141" s="1">
+        <v>429</v>
+      </c>
+      <c r="K141" s="1">
+        <v>2</v>
+      </c>
+      <c r="L141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="3:12">
+      <c r="C142" s="1">
+        <v>429</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E142" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F142" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="G142" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H142" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I142" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J142" s="1">
+        <v>430</v>
+      </c>
+      <c r="K142" s="1">
+        <v>2</v>
+      </c>
+      <c r="L142" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="3:12">
+      <c r="C143" s="1">
+        <v>430</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H143" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I143" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J143" s="1">
+        <v>431</v>
+      </c>
+      <c r="K143" s="1">
+        <v>2</v>
+      </c>
+      <c r="L143" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
+        <v>431</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E144" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F144" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G144" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H144" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I144" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="J144" s="1">
+        <v>432</v>
+      </c>
+      <c r="K144" s="1">
+        <v>2</v>
+      </c>
+      <c r="L144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" customHeight="1" spans="3:12">
+      <c r="C145" s="1">
+        <v>432</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="H145" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J145" s="1">
+        <v>433</v>
+      </c>
+      <c r="K145" s="1">
+        <v>2</v>
+      </c>
+      <c r="L145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" customHeight="1" spans="3:12">
+      <c r="C146" s="1">
+        <v>433</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="G146" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H146" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J146" s="1">
+        <v>434</v>
+      </c>
+      <c r="K146" s="1">
+        <v>2</v>
+      </c>
+      <c r="L146" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:12">
+      <c r="C147" s="1">
+        <v>434</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H147" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I147" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J147" s="1">
+        <v>435</v>
+      </c>
+      <c r="K147" s="1">
+        <v>2</v>
+      </c>
+      <c r="L147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:12">
+      <c r="C150" s="1">
         <v>501</v>
       </c>
-      <c r="D144" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E144" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F144" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="G144" s="5" t="s">
-        <v>311</v>
-      </c>
-      <c r="H144" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I144" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="J144" s="1">
+      <c r="D150" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E150" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F150" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G150" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H150" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J150" s="1">
         <v>4011</v>
       </c>
-      <c r="K144" s="1">
+      <c r="K150" s="1">
         <v>5</v>
-      </c>
-      <c r="L144" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" customHeight="1" spans="1:12">
-      <c r="C145" s="1">
-        <v>502</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F145" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="G145" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="H145" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I145" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="J145" s="1">
-        <v>4019</v>
-      </c>
-      <c r="K145" s="1">
-        <v>5</v>
-      </c>
-      <c r="L145" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" customHeight="1" spans="1:12">
-      <c r="C146" s="1">
-        <v>503</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E146" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F146" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="G146" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="H146" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="J146" s="1">
-        <v>4026</v>
-      </c>
-      <c r="K146" s="1">
-        <v>5</v>
-      </c>
-      <c r="L146" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" customHeight="1" spans="1:12">
-      <c r="C147" s="1">
-        <v>504</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="G147" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="H147" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="J147" s="1">
-        <v>4024</v>
-      </c>
-      <c r="K147" s="1">
-        <v>5</v>
-      </c>
-      <c r="L147" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" spans="1:12">
-      <c r="C148" s="1">
-        <v>505</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E148" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F148" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="G148" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="H148" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I148" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="J148" s="1">
-        <v>4025</v>
-      </c>
-      <c r="K148" s="1">
-        <v>5</v>
-      </c>
-      <c r="L148" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" spans="1:12">
-      <c r="C149" s="1">
-        <v>506</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E149" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>325</v>
-      </c>
-      <c r="G149" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="H149" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="J149" s="1">
-        <v>35</v>
-      </c>
-      <c r="K149" s="1">
-        <v>4</v>
-      </c>
-      <c r="L149" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="1:12">
-      <c r="C150" s="1">
-        <v>507</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E150" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F150" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G150" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="H150" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="J150" s="1">
-        <v>37</v>
-      </c>
-      <c r="K150" s="1">
-        <v>4</v>
       </c>
       <c r="L150" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="1:12">
+    <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F151" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="G151" s="5" t="s">
         <v>330</v>
-      </c>
-      <c r="G151" s="5" t="s">
-        <v>326</v>
       </c>
       <c r="H151" s="5" t="s">
         <v>18</v>
@@ -6595,141 +6707,135 @@
         <v>331</v>
       </c>
       <c r="J151" s="1">
-        <v>38</v>
+        <v>4019</v>
       </c>
       <c r="K151" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L151" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="1:12">
+    <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>332</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="H152" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I152" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J152" s="1">
-        <v>39</v>
+        <v>4026</v>
       </c>
       <c r="K152" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L152" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="1:12">
+    <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="H153" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I153" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="J153" s="1">
-        <v>40</v>
+        <v>4024</v>
       </c>
       <c r="K153" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L153" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="1:12">
+    <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="H154" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J154" s="1">
-        <v>47</v>
+        <v>4025</v>
       </c>
       <c r="K154" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L154" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="1:12">
-      <c r="A155" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B155" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="H155" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J155" s="1">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="K155" s="1">
         <v>4</v>
@@ -6738,36 +6844,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" customHeight="1" spans="1:12">
-      <c r="A156" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="156" customHeight="1" spans="3:12">
       <c r="C156" s="1">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="H156" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J156" s="1">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K156" s="1">
         <v>4</v>
@@ -6776,36 +6876,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="1:12">
-      <c r="A157" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B157" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="157" customHeight="1" spans="3:12">
       <c r="C157" s="1">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="H157" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J157" s="1">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="K157" s="1">
         <v>4</v>
@@ -6814,36 +6908,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="1:12">
-      <c r="A158" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="158" customHeight="1" spans="3:12">
       <c r="C158" s="1">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="H158" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J158" s="1">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="K158" s="1">
         <v>4</v>
@@ -6852,126 +6940,214 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="1:12">
+    <row r="159" customHeight="1" spans="3:12">
+      <c r="C159" s="1">
+        <v>510</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E159" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="G159" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H159" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I159" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="J159" s="1">
+        <v>40</v>
+      </c>
+      <c r="K159" s="1">
+        <v>4</v>
+      </c>
+      <c r="L159" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:12">
       <c r="C160" s="1">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J160" s="1">
-        <v>4035</v>
+        <v>47</v>
       </c>
       <c r="K160" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L160" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="161" customHeight="1" spans="3:12">
+    <row r="161" customHeight="1" spans="1:12">
+      <c r="A161" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="C161" s="1">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J161" s="1">
-        <v>4039</v>
+        <v>48</v>
       </c>
       <c r="K161" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L161" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="162" customHeight="1" spans="3:12">
+    <row r="162" customHeight="1" spans="1:12">
+      <c r="A162" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="C162" s="1">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J162" s="1">
-        <v>4037</v>
+        <v>49</v>
       </c>
       <c r="K162" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L162" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="164" customHeight="1" spans="3:12">
+    <row r="163" customHeight="1" spans="1:12">
+      <c r="A163" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C163" s="1">
+        <v>514</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F163" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="G163" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="H163" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="J163" s="1">
+        <v>50</v>
+      </c>
+      <c r="K163" s="1">
+        <v>4</v>
+      </c>
+      <c r="L163" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" customHeight="1" spans="1:12">
+      <c r="A164" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>354</v>
+      </c>
       <c r="C164" s="1">
-        <v>531</v>
+        <v>515</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="J164" s="1">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K164" s="1">
         <v>4</v>
@@ -6980,30 +7156,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" customHeight="1" spans="3:12">
+    <row r="166" customHeight="1" spans="1:12">
+      <c r="C166" s="1">
+        <v>521</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F166" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="G166" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="H166" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I166" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J166" s="1">
+        <v>4035</v>
+      </c>
+      <c r="K166" s="1">
+        <v>5</v>
+      </c>
+      <c r="L166" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" customHeight="1" spans="1:12">
       <c r="C167" s="1">
-        <v>601</v>
+        <v>522</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E167" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="H167" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="J167" s="4">
-        <v>60000007</v>
+        <v>367</v>
+      </c>
+      <c r="J167" s="1">
+        <v>4039</v>
       </c>
       <c r="K167" s="1">
         <v>5</v>
@@ -7012,30 +7220,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" customHeight="1" spans="3:12">
+    <row r="168" customHeight="1" spans="1:12">
       <c r="C168" s="1">
-        <v>602</v>
+        <v>523</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E168" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
+      </c>
+      <c r="E168" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="H168" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="J168" s="4">
-        <v>60000008</v>
+        <v>369</v>
+      </c>
+      <c r="J168" s="1">
+        <v>4037</v>
       </c>
       <c r="K168" s="1">
         <v>5</v>
@@ -7044,158 +7252,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" customHeight="1" spans="3:12">
-      <c r="C169" s="1">
-        <v>603</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I169" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="J169" s="4">
-        <v>60000006</v>
-      </c>
-      <c r="K169" s="1">
-        <v>5</v>
-      </c>
-      <c r="L169" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" customHeight="1" spans="3:12">
+    <row r="170" customHeight="1" spans="1:12">
       <c r="C170" s="1">
-        <v>604</v>
+        <v>531</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>309</v>
+        <v>324</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>325</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="H170" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="J170" s="4">
-        <v>60000008</v>
+        <v>371</v>
+      </c>
+      <c r="J170" s="1">
+        <v>42</v>
       </c>
       <c r="K170" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L170" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="171" customHeight="1" spans="3:12">
-      <c r="C171" s="1">
-        <v>605</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H171" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I171" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="J171" s="4">
-        <v>60000006</v>
-      </c>
-      <c r="K171" s="1">
-        <v>5</v>
-      </c>
-      <c r="L171" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" customHeight="1" spans="3:12">
-      <c r="C172" s="1">
-        <v>606</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F172" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="G172" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H172" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I172" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="J172" s="4">
+    <row r="173" customHeight="1" spans="1:12">
+      <c r="C173" s="1">
+        <v>601</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F173" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G173" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="J173" s="4">
         <v>60000007</v>
-      </c>
-      <c r="K172" s="1">
-        <v>5</v>
-      </c>
-      <c r="L172" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" customHeight="1" spans="3:12">
-      <c r="C173" s="1">
-        <v>607</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F173" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="G173" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I173" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="J173" s="4">
-        <v>60000017</v>
       </c>
       <c r="K173" s="1">
         <v>5</v>
@@ -7204,30 +7316,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" customHeight="1" spans="3:12">
+    <row r="174" customHeight="1" spans="1:12">
       <c r="C174" s="1">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="J174" s="4">
-        <v>60000018</v>
+        <v>60000008</v>
       </c>
       <c r="K174" s="1">
         <v>5</v>
@@ -7236,30 +7348,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" customHeight="1" spans="3:12">
+    <row r="175" customHeight="1" spans="1:12">
       <c r="C175" s="1">
-        <v>609</v>
+        <v>603</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="J175" s="4">
-        <v>60000016</v>
+        <v>60000006</v>
       </c>
       <c r="K175" s="1">
         <v>5</v>
@@ -7268,30 +7380,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" customHeight="1" spans="3:12">
+    <row r="176" customHeight="1" spans="1:12">
       <c r="C176" s="1">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="H176" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="J176" s="4">
-        <v>60000018</v>
+        <v>60000008</v>
       </c>
       <c r="K176" s="1">
         <v>5</v>
@@ -7302,28 +7414,28 @@
     </row>
     <row r="177" customHeight="1" spans="3:12">
       <c r="C177" s="1">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="H177" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="J177" s="4">
-        <v>60000016</v>
+        <v>60000006</v>
       </c>
       <c r="K177" s="1">
         <v>5</v>
@@ -7334,33 +7446,225 @@
     </row>
     <row r="178" customHeight="1" spans="3:12">
       <c r="C178" s="1">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="H178" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="J178" s="4">
-        <v>60000017</v>
+        <v>60000007</v>
       </c>
       <c r="K178" s="1">
         <v>5</v>
       </c>
       <c r="L178" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" customHeight="1" spans="3:12">
+      <c r="C179" s="1">
+        <v>607</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F179" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="G179" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H179" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I179" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J179" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="K179" s="1">
+        <v>5</v>
+      </c>
+      <c r="L179" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" customHeight="1" spans="3:12">
+      <c r="C180" s="1">
+        <v>608</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E180" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F180" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="G180" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J180" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="K180" s="1">
+        <v>5</v>
+      </c>
+      <c r="L180" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" customHeight="1" spans="3:12">
+      <c r="C181" s="1">
+        <v>609</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E181" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F181" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G181" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H181" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I181" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J181" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="K181" s="1">
+        <v>5</v>
+      </c>
+      <c r="L181" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" customHeight="1" spans="3:12">
+      <c r="C182" s="1">
+        <v>610</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E182" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F182" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J182" s="4">
+        <v>60000018</v>
+      </c>
+      <c r="K182" s="1">
+        <v>5</v>
+      </c>
+      <c r="L182" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" customHeight="1" spans="3:12">
+      <c r="C183" s="1">
+        <v>611</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F183" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J183" s="4">
+        <v>60000016</v>
+      </c>
+      <c r="K183" s="1">
+        <v>5</v>
+      </c>
+      <c r="L183" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" customHeight="1" spans="3:12">
+      <c r="C184" s="1">
+        <v>612</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F184" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="G184" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="H184" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I184" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J184" s="4">
+        <v>60000017</v>
+      </c>
+      <c r="K184" s="1">
+        <v>5</v>
+      </c>
+      <c r="L184" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="387">
   <si>
     <t>Id</t>
   </si>
@@ -1055,37 +1055,40 @@
     <t>4028,4111</t>
   </si>
   <si>
+    <t>40,30000</t>
+  </si>
+  <si>
+    <t>青龙神器</t>
+  </si>
+  <si>
+    <t>4029,4111</t>
+  </si>
+  <si>
+    <t>白虎神器</t>
+  </si>
+  <si>
+    <t>4030,4111</t>
+  </si>
+  <si>
+    <t>朱雀神器</t>
+  </si>
+  <si>
+    <t>4031,4111</t>
+  </si>
+  <si>
+    <t>玄武神器</t>
+  </si>
+  <si>
+    <t>4032,4111</t>
+  </si>
+  <si>
+    <t>麒麟神器</t>
+  </si>
+  <si>
+    <t>4055,4111</t>
+  </si>
+  <si>
     <t>40,100000</t>
-  </si>
-  <si>
-    <t>青龙神器</t>
-  </si>
-  <si>
-    <t>4029,4111</t>
-  </si>
-  <si>
-    <t>白虎神器</t>
-  </si>
-  <si>
-    <t>4030,4111</t>
-  </si>
-  <si>
-    <t>朱雀神器</t>
-  </si>
-  <si>
-    <t>4031,4111</t>
-  </si>
-  <si>
-    <t>玄武神器</t>
-  </si>
-  <si>
-    <t>4032,4111</t>
-  </si>
-  <si>
-    <t>麒麟神器</t>
-  </si>
-  <si>
-    <t>4055,4111</t>
   </si>
   <si>
     <t>极龙神器</t>
@@ -6986,13 +6989,13 @@
         <v>352</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J160" s="1">
         <v>47</v>
@@ -7006,10 +7009,10 @@
     </row>
     <row r="161" customHeight="1" spans="1:12">
       <c r="A161" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C161" s="1">
         <v>512</v>
@@ -7021,16 +7024,16 @@
         <v>325</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H161" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="J161" s="1">
         <v>48</v>
@@ -7044,10 +7047,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C162" s="1">
         <v>513</v>
@@ -7059,16 +7062,16 @@
         <v>325</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H162" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J162" s="1">
         <v>49</v>
@@ -7082,10 +7085,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C163" s="1">
         <v>514</v>
@@ -7097,16 +7100,16 @@
         <v>325</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H163" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J163" s="1">
         <v>50</v>
@@ -7120,10 +7123,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C164" s="1">
         <v>515</v>
@@ -7135,16 +7138,16 @@
         <v>325</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="H164" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J164" s="1">
         <v>51</v>
@@ -7167,16 +7170,16 @@
         <v>325</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H166" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I166" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J166" s="1">
         <v>4035</v>
@@ -7199,16 +7202,16 @@
         <v>325</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H167" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J167" s="1">
         <v>4039</v>
@@ -7231,16 +7234,16 @@
         <v>325</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H168" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="J168" s="1">
         <v>4037</v>
@@ -7263,7 +7266,7 @@
         <v>325</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>330</v>
@@ -7272,7 +7275,7 @@
         <v>18</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J170" s="1">
         <v>42</v>
@@ -7289,22 +7292,22 @@
         <v>601</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H173" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J173" s="4">
         <v>60000007</v>
@@ -7321,22 +7324,22 @@
         <v>602</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J174" s="4">
         <v>60000008</v>
@@ -7353,22 +7356,22 @@
         <v>603</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="J175" s="4">
         <v>60000006</v>
@@ -7385,22 +7388,22 @@
         <v>604</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F176" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H176" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I176" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="G176" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H176" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>376</v>
       </c>
       <c r="J176" s="4">
         <v>60000008</v>
@@ -7417,22 +7420,22 @@
         <v>605</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F177" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H177" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I177" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="G177" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H177" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>378</v>
       </c>
       <c r="J177" s="4">
         <v>60000006</v>
@@ -7449,22 +7452,22 @@
         <v>606</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H178" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="J178" s="4">
         <v>60000007</v>
@@ -7481,22 +7484,22 @@
         <v>607</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H179" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J179" s="4">
         <v>60000017</v>
@@ -7513,22 +7516,22 @@
         <v>608</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H180" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="J180" s="4">
         <v>60000018</v>
@@ -7545,22 +7548,22 @@
         <v>609</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H181" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J181" s="4">
         <v>60000016</v>
@@ -7577,22 +7580,22 @@
         <v>610</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F182" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="G182" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H182" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I182" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="G182" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H182" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>382</v>
       </c>
       <c r="J182" s="4">
         <v>60000018</v>
@@ -7609,22 +7612,22 @@
         <v>611</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F183" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G183" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="H183" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I183" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="G183" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="H183" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>384</v>
       </c>
       <c r="J183" s="4">
         <v>60000016</v>
@@ -7641,22 +7644,22 @@
         <v>612</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H184" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J184" s="4">
         <v>60000017</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="387">
   <si>
     <t>Id</t>
   </si>
@@ -1094,13 +1094,13 @@
     <t>极龙神器</t>
   </si>
   <si>
+    <t>4056,4111</t>
+  </si>
+  <si>
+    <t>极虎神器</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>4056,4111</t>
-  </si>
-  <si>
-    <t>极虎神器</t>
   </si>
   <si>
     <t>4057,4111</t>
@@ -7008,12 +7008,6 @@
       </c>
     </row>
     <row r="161" customHeight="1" spans="1:12">
-      <c r="A161" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>355</v>
-      </c>
       <c r="C161" s="1">
         <v>512</v>
       </c>
@@ -7024,7 +7018,7 @@
         <v>325</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G161" s="5" t="s">
         <v>353</v>
@@ -7033,7 +7027,7 @@
         <v>18</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="J161" s="1">
         <v>48</v>
@@ -7047,10 +7041,10 @@
     </row>
     <row r="162" customHeight="1" spans="1:12">
       <c r="A162" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C162" s="1">
         <v>513</v>
@@ -7085,10 +7079,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C163" s="1">
         <v>514</v>
@@ -7123,10 +7117,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C164" s="1">
         <v>515</v>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1148,6 +1148,12 @@
     <t>12阶技能</t>
   </si>
   <si>
+    <t>4052,4111</t>
+  </si>
+  <si>
+    <t>暗金兽魂</t>
+  </si>
+  <si>
     <t>宝石</t>
   </si>
   <si>
@@ -1188,6 +1194,24 @@
   </si>
   <si>
     <t>60000018,4111</t>
+  </si>
+  <si>
+    <t>60000021,4111</t>
+  </si>
+  <si>
+    <t>极魔伤宝石</t>
+  </si>
+  <si>
+    <t>极道伤宝石</t>
+  </si>
+  <si>
+    <t>60000022,4111</t>
+  </si>
+  <si>
+    <t>极物伤宝石</t>
+  </si>
+  <si>
+    <t>60000023,4111</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2215,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L184"/>
+  <dimension ref="A3:L190"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -7281,27 +7305,59 @@
         <v>0</v>
       </c>
     </row>
+    <row r="171" customHeight="1" spans="1:12">
+      <c r="C171" s="1">
+        <v>532</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="H171" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I171" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="J171" s="1">
+        <v>4053</v>
+      </c>
+      <c r="K171" s="1">
+        <v>5</v>
+      </c>
+      <c r="L171" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="173" customHeight="1" spans="1:12">
       <c r="C173" s="1">
         <v>601</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H173" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J173" s="4">
         <v>60000007</v>
@@ -7318,22 +7374,22 @@
         <v>602</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J174" s="4">
         <v>60000008</v>
@@ -7350,22 +7406,22 @@
         <v>603</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J175" s="4">
         <v>60000006</v>
@@ -7382,22 +7438,22 @@
         <v>604</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H176" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J176" s="4">
         <v>60000008</v>
@@ -7414,22 +7470,22 @@
         <v>605</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H177" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J177" s="4">
         <v>60000006</v>
@@ -7446,22 +7502,22 @@
         <v>606</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H178" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="J178" s="4">
         <v>60000007</v>
@@ -7478,22 +7534,22 @@
         <v>607</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H179" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J179" s="4">
         <v>60000017</v>
@@ -7510,22 +7566,22 @@
         <v>608</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H180" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J180" s="4">
         <v>60000018</v>
@@ -7542,22 +7598,22 @@
         <v>609</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H181" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J181" s="4">
         <v>60000016</v>
@@ -7574,22 +7630,22 @@
         <v>610</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H182" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="J182" s="4">
         <v>60000018</v>
@@ -7606,22 +7662,22 @@
         <v>611</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G183" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H183" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="J183" s="4">
         <v>60000016</v>
@@ -7638,22 +7694,22 @@
         <v>612</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>325</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G184" s="5" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="H184" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="J184" s="4">
         <v>60000017</v>
@@ -7662,6 +7718,198 @@
         <v>5</v>
       </c>
       <c r="L184" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" customHeight="1" spans="3:12">
+      <c r="C185" s="1">
+        <v>613</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E185" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F185" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G185" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H185" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I185" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J185" s="4">
+        <v>60000022</v>
+      </c>
+      <c r="K185" s="1">
+        <v>5</v>
+      </c>
+      <c r="L185" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" customHeight="1" spans="3:12">
+      <c r="C186" s="1">
+        <v>614</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F186" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G186" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H186" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I186" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J186" s="4">
+        <v>60000023</v>
+      </c>
+      <c r="K186" s="1">
+        <v>5</v>
+      </c>
+      <c r="L186" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" customHeight="1" spans="3:12">
+      <c r="C187" s="1">
+        <v>615</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E187" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H187" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I187" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J187" s="4">
+        <v>60000021</v>
+      </c>
+      <c r="K187" s="1">
+        <v>5</v>
+      </c>
+      <c r="L187" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" customHeight="1" spans="3:12">
+      <c r="C188" s="1">
+        <v>616</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F188" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="G188" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H188" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I188" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="J188" s="4">
+        <v>60000023</v>
+      </c>
+      <c r="K188" s="1">
+        <v>5</v>
+      </c>
+      <c r="L188" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" customHeight="1" spans="3:12">
+      <c r="C189" s="1">
+        <v>617</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F189" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G189" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H189" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I189" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J189" s="4">
+        <v>60000021</v>
+      </c>
+      <c r="K189" s="1">
+        <v>5</v>
+      </c>
+      <c r="L189" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" customHeight="1" spans="3:12">
+      <c r="C190" s="1">
+        <v>618</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="F190" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="G190" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="H190" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="J190" s="4">
+        <v>60000022</v>
+      </c>
+      <c r="K190" s="1">
+        <v>5</v>
+      </c>
+      <c r="L190" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/CompositeConfig.xlsx
+++ b/Excel/CompositeConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1100,13 +1105,13 @@
     <t>极虎神器</t>
   </si>
   <si>
+    <t>4057,4111</t>
+  </si>
+  <si>
+    <t>极雀神器</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>4057,4111</t>
-  </si>
-  <si>
-    <t>极雀神器</t>
   </si>
   <si>
     <t>4058,4111</t>
@@ -7064,12 +7069,6 @@
       </c>
     </row>
     <row r="162" customHeight="1" spans="1:12">
-      <c r="A162" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="C162" s="1">
         <v>513</v>
       </c>
@@ -7080,7 +7079,7 @@
         <v>325</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G162" s="5" t="s">
         <v>353</v>
@@ -7089,7 +7088,7 @@
         <v>18</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J162" s="1">
         <v>49</v>
@@ -7103,10 +7102,10 @@
     </row>
     <row r="163" customHeight="1" spans="1:12">
       <c r="A163" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C163" s="1">
         <v>514</v>
@@ -7141,10 +7140,10 @@
     </row>
     <row r="164" customHeight="1" spans="1:12">
       <c r="A164" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C164" s="1">
         <v>515</v>
